--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Verified Aliases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$292</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="662">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -928,9 +928,6 @@
   </si>
   <si>
     <t>Sivaganesh Manivannan</t>
-  </si>
-  <si>
-    <t>Hafis</t>
   </si>
   <si>
     <t>Sarath Sasi</t>
@@ -2429,7 +2426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D342"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -2454,10 +2451,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>497</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>498</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -2468,10 +2465,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>364</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>365</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -2482,10 +2479,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -2496,10 +2493,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -2510,10 +2507,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -2524,10 +2521,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6</v>
@@ -2552,10 +2549,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6</v>
@@ -2608,10 +2605,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
@@ -2650,10 +2647,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
@@ -2692,10 +2689,10 @@
     </row>
     <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
@@ -2706,10 +2703,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -2762,10 +2759,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>413</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>414</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6</v>
@@ -2776,10 +2773,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>495</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>496</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>6</v>
@@ -2846,10 +2843,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>441</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>442</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -2874,10 +2871,10 @@
     </row>
     <row r="32" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6</v>
@@ -2891,7 +2888,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>6</v>
@@ -2930,10 +2927,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>443</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>444</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
@@ -2944,10 +2941,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>6</v>
@@ -2958,10 +2955,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>6</v>
@@ -2972,10 +2969,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>425</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6</v>
@@ -3000,10 +2997,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>615</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>616</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -3028,10 +3025,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>334</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>335</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6</v>
@@ -3042,10 +3039,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>6</v>
@@ -3056,10 +3053,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6</v>
@@ -3112,10 +3109,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>6</v>
@@ -3196,10 +3193,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>501</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -3219,15 +3216,15 @@
         <v>6</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
@@ -3252,10 +3249,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>473</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>474</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -3322,10 +3319,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="B64" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>500</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>6</v>
@@ -3378,10 +3375,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="B68" s="12" t="s">
         <v>493</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>494</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>6</v>
@@ -3462,10 +3459,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="B74" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>504</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>6</v>
@@ -3476,10 +3473,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B75" s="12" t="s">
         <v>360</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>361</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>6</v>
@@ -3518,10 +3515,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -3532,10 +3529,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>505</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>506</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>6</v>
@@ -3546,10 +3543,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -3574,10 +3571,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -3616,10 +3613,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -3630,10 +3627,10 @@
     </row>
     <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B86" s="12" t="s">
         <v>446</v>
-      </c>
-      <c r="B86" s="12" t="s">
-        <v>447</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -3644,10 +3641,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -3672,10 +3669,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -3686,10 +3683,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -3700,10 +3697,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>6</v>
@@ -3714,10 +3711,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>6</v>
@@ -3756,10 +3753,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>566</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>567</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -3770,10 +3767,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -3784,10 +3781,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>507</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>508</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>6</v>
@@ -3798,10 +3795,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="B98" s="12" t="s">
         <v>322</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>323</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>6</v>
@@ -3812,10 +3809,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
+        <v>551</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>552</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>553</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -3826,10 +3823,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>6</v>
@@ -3854,10 +3851,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="B102" s="12" t="s">
         <v>448</v>
-      </c>
-      <c r="B102" s="12" t="s">
-        <v>449</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -3868,10 +3865,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" s="12" t="s">
         <v>450</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>451</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -3882,10 +3879,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -3910,7 +3907,7 @@
     </row>
     <row r="106" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>41</v>
@@ -3924,7 +3921,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>41</v>
@@ -3966,7 +3963,7 @@
     </row>
     <row r="110" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>134</v>
@@ -3994,7 +3991,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>302</v>
+        <v>254</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>255</v>
@@ -4007,11 +4004,11 @@
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>255</v>
+      <c r="A113" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>362</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>6</v>
@@ -4021,11 +4018,11 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="B114" s="12" t="s">
-        <v>363</v>
+      <c r="A114" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>620</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -4035,11 +4032,11 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
-        <v>622</v>
-      </c>
-      <c r="B115" s="17" t="s">
-        <v>621</v>
+      <c r="A115" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>556</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -4049,11 +4046,11 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
-        <v>558</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>557</v>
+      <c r="A116" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>6</v>
@@ -4063,11 +4060,11 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>206</v>
+      <c r="A117" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>618</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -4077,11 +4074,11 @@
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="s">
-        <v>620</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>619</v>
+      <c r="A118" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>452</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -4092,10 +4089,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>452</v>
+        <v>332</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>453</v>
+        <v>337</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>6</v>
@@ -4105,11 +4102,11 @@
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="11" t="s">
-        <v>333</v>
+      <c r="A120" s="15" t="s">
+        <v>658</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>338</v>
+        <v>657</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>6</v>
@@ -4119,13 +4116,13 @@
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="15" t="s">
-        <v>659</v>
+      <c r="A121" s="11" t="s">
+        <v>516</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>658</v>
-      </c>
-      <c r="C121" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C121" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D121" s="2" t="s">
@@ -4134,10 +4131,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>6</v>
@@ -4148,10 +4145,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>6</v>
@@ -4162,10 +4159,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>6</v>
@@ -4176,10 +4173,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>6</v>
@@ -4189,13 +4186,13 @@
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
-        <v>509</v>
+      <c r="A126" s="15" t="s">
+        <v>563</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>510</v>
-      </c>
-      <c r="C126" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D126" s="2" t="s">
@@ -4203,11 +4200,11 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="15" t="s">
-        <v>564</v>
+      <c r="A127" s="11" t="s">
+        <v>432</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>565</v>
+        <v>433</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>6</v>
@@ -4218,10 +4215,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -4231,11 +4228,11 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>418</v>
+      <c r="A129" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -4245,11 +4242,11 @@
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>215</v>
+      <c r="A130" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>6</v>
@@ -4260,7 +4257,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>417</v>
+        <v>195</v>
       </c>
       <c r="B131" s="12" t="s">
         <v>196</v>
@@ -4274,10 +4271,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>195</v>
+        <v>511</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>196</v>
+        <v>554</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -4288,10 +4285,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>555</v>
+        <v>454</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -4301,11 +4298,11 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="B134" s="12" t="s">
-        <v>455</v>
+      <c r="A134" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>632</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -4315,11 +4312,11 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="15" t="s">
-        <v>634</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>633</v>
+      <c r="A135" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -4329,11 +4326,11 @@
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>377</v>
+      <c r="A136" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -4344,10 +4341,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>24</v>
+        <v>286</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -4357,11 +4354,11 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>286</v>
+      <c r="A138" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -4371,11 +4368,11 @@
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>244</v>
+      <c r="A139" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -4386,10 +4383,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -4400,10 +4397,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -4413,11 +4410,11 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>290</v>
+      <c r="A142" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>429</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -4427,11 +4424,11 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>430</v>
+      <c r="A143" s="15" t="s">
+        <v>599</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>598</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -4441,11 +4438,11 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>599</v>
+      <c r="A144" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -4455,11 +4452,11 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>109</v>
+      <c r="A145" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>636</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>6</v>
@@ -4469,28 +4466,28 @@
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="15" t="s">
-        <v>638</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>637</v>
+      <c r="A146" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>49</v>
+      <c r="A147" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B147" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>7</v>
@@ -4498,10 +4495,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -4511,11 +4508,11 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>351</v>
+      <c r="A149" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -4525,11 +4522,11 @@
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>232</v>
+      <c r="A150" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -4540,10 +4537,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>6</v>
@@ -4554,10 +4551,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>393</v>
+        <v>661</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -4568,10 +4565,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>662</v>
+        <v>340</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -4582,10 +4579,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>341</v>
+        <v>455</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -4596,10 +4593,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>457</v>
+        <v>430</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>6</v>
@@ -4609,39 +4606,39 @@
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>431</v>
+      <c r="A156" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>88</v>
+      <c r="A157" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>587</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="B158" s="17" t="s">
-        <v>588</v>
+      <c r="A158" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>6</v>
@@ -4651,13 +4648,13 @@
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="A159" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="B159" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C159" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D159" s="2" t="s">
@@ -4666,12 +4663,12 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>519</v>
+        <v>382</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C160" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D160" s="2" t="s">
@@ -4680,10 +4677,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -4693,11 +4690,11 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="B162" s="12" t="s">
-        <v>402</v>
+      <c r="A162" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>585</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -4707,11 +4704,11 @@
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="B163" s="17" t="s">
-        <v>586</v>
+      <c r="A163" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B163" s="14" t="s">
+        <v>419</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -4722,10 +4719,10 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="16" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>6</v>
@@ -4736,12 +4733,12 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="16" t="s">
-        <v>390</v>
+        <v>519</v>
       </c>
       <c r="B165" s="14" t="s">
-        <v>401</v>
-      </c>
-      <c r="C165" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D165" s="2" t="s">
@@ -4749,13 +4746,13 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="16" t="s">
-        <v>520</v>
-      </c>
-      <c r="B166" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="C166" s="4" t="s">
+      <c r="A166" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D166" s="2" t="s">
@@ -4763,13 +4760,13 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="C167" s="2" t="s">
+      <c r="A167" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="B167" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="C167" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D167" s="2" t="s">
@@ -4777,67 +4774,67 @@
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="16" t="s">
-        <v>490</v>
-      </c>
-      <c r="B168" s="14" t="s">
-        <v>489</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>6</v>
+      <c r="A168" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>7</v>
+        <v>307</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="B169" s="9" t="s">
-        <v>307</v>
+      <c r="A169" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>610</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>312</v>
+        <v>6</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>308</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>611</v>
+      <c r="A170" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>313</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>7</v>
+        <v>314</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B171" s="9" t="s">
-        <v>314</v>
+      <c r="A171" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>602</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>312</v>
+        <v>6</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="6" t="s">
-        <v>604</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>603</v>
+      <c r="A172" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>204</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -4848,10 +4845,10 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>6</v>
@@ -4862,68 +4859,68 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B175" s="9" t="s">
-        <v>180</v>
+      <c r="A175" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B175" s="14" t="s">
+        <v>336</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="B176" s="14" t="s">
-        <v>337</v>
+      <c r="A176" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>553</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="B177" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>312</v>
+      <c r="A177" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="B177" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>313</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
-        <v>311</v>
+        <v>457</v>
       </c>
       <c r="B178" s="14" t="s">
-        <v>554</v>
-      </c>
-      <c r="C178" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D178" s="2" t="s">
@@ -4931,12 +4928,12 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="16" t="s">
+      <c r="A179" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B179" s="18" t="s">
         <v>458</v>
       </c>
-      <c r="B179" s="14" t="s">
-        <v>459</v>
-      </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
       </c>
@@ -4945,11 +4942,11 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="B180" s="18" t="s">
-        <v>459</v>
+      <c r="A180" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="B180" s="14" t="s">
+        <v>339</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>6</v>
@@ -4960,13 +4957,13 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="B181" s="14" t="s">
-        <v>340</v>
+        <v>323</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>7</v>
@@ -4974,13 +4971,13 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="B182" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>16</v>
+        <v>521</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>7</v>
@@ -4988,10 +4985,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="B183" s="14" t="s">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>6</v>
@@ -5001,13 +4998,13 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="16" t="s">
-        <v>492</v>
-      </c>
-      <c r="B184" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="C184" s="4" t="s">
+      <c r="A184" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B184" t="s">
+        <v>623</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D184" s="2" t="s">
@@ -5015,11 +5012,11 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="B185" t="s">
-        <v>624</v>
+      <c r="A185" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="B185" s="14" t="s">
+        <v>468</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -5030,10 +5027,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="16" t="s">
-        <v>468</v>
+        <v>353</v>
       </c>
       <c r="B186" s="14" t="s">
-        <v>469</v>
+        <v>354</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>6</v>
@@ -5043,39 +5040,39 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="B187" s="14" t="s">
-        <v>355</v>
+      <c r="A187" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B188" s="9" t="s">
-        <v>78</v>
+      <c r="A188" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B188" s="14" t="s">
+        <v>434</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="B189" s="14" t="s">
-        <v>435</v>
+      <c r="A189" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -5085,11 +5082,11 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B190" s="9" t="s">
-        <v>240</v>
+      <c r="A190" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B190" t="s">
+        <v>628</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>6</v>
@@ -5099,13 +5096,13 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="B191" t="s">
-        <v>629</v>
-      </c>
-      <c r="C191" s="2" t="s">
+      <c r="A191" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="B191" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="C191" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D191" s="2" t="s">
@@ -5114,12 +5111,12 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="16" t="s">
-        <v>524</v>
+        <v>342</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>525</v>
-      </c>
-      <c r="C192" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D192" s="2" t="s">
@@ -5127,11 +5124,11 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="B193" s="14" t="s">
-        <v>344</v>
+      <c r="A193" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -5142,10 +5139,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="8" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -5155,11 +5152,11 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B195" s="9" t="s">
-        <v>202</v>
+      <c r="A195" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B195" s="14" t="s">
+        <v>409</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>6</v>
@@ -5169,98 +5166,98 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="16" t="s">
-        <v>409</v>
-      </c>
-      <c r="B196" s="14" t="s">
-        <v>410</v>
+      <c r="A196" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>164</v>
+      <c r="A197" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>460</v>
       </c>
       <c r="C197" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="B198" s="3" t="s">
+      <c r="D198" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B199" s="9" t="s">
-        <v>28</v>
+      <c r="B199" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="C199" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="13" t="s">
-        <v>462</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A202" s="13" t="s">
-        <v>526</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>7</v>
@@ -5268,13 +5265,13 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>7</v>
@@ -5282,10 +5279,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -5295,11 +5292,11 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>57</v>
+      <c r="A205" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>604</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>6</v>
@@ -5309,13 +5306,13 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="6" t="s">
-        <v>606</v>
+      <c r="A206" s="13" t="s">
+        <v>527</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="C206" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C206" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D206" s="2" t="s">
@@ -5323,13 +5320,13 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A207" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="C207" s="4" t="s">
+      <c r="A207" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D207" s="2" t="s">
@@ -5338,10 +5335,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -5351,11 +5348,11 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B209" s="9" t="s">
-        <v>66</v>
+      <c r="A209" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -5365,11 +5362,11 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>614</v>
+      <c r="A210" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B210" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -5379,11 +5376,11 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>105</v>
+      <c r="A211" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B211" t="s">
+        <v>638</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>6</v>
@@ -5393,14 +5390,14 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A212" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="B212" t="s">
-        <v>639</v>
+      <c r="A212" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B212" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>7</v>
@@ -5408,10 +5405,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>16</v>
@@ -5422,10 +5419,10 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" s="8" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>16</v>
@@ -5435,27 +5432,27 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>16</v>
+      <c r="A215" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A216" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="B216" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C216" s="4" t="s">
+      <c r="A216" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D216" s="2" t="s">
@@ -5464,10 +5461,10 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -5478,10 +5475,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -5491,11 +5488,11 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A219" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B219" s="9" t="s">
-        <v>55</v>
+      <c r="A219" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -5506,10 +5503,10 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="13" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -5520,10 +5517,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" s="13" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -5533,11 +5530,11 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A222" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>359</v>
+      <c r="A222" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>275</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>6</v>
@@ -5548,27 +5545,27 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="8" t="s">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A224" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>76</v>
+      <c r="A224" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>7</v>
@@ -5576,10 +5573,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>357</v>
+        <v>474</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -5590,10 +5587,10 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="13" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>475</v>
+        <v>397</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>6</v>
@@ -5604,12 +5601,12 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" s="13" t="s">
-        <v>387</v>
+        <v>528</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C227" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C227" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D227" s="2" t="s">
@@ -5617,13 +5614,13 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="C228" s="4" t="s">
+      <c r="A228" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B228" t="s">
+        <v>402</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D228" s="2" t="s">
@@ -5631,11 +5628,11 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="B229" t="s">
-        <v>403</v>
+      <c r="A229" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="B229" s="14" t="s">
+        <v>562</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -5645,11 +5642,11 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A230" s="13" t="s">
-        <v>562</v>
-      </c>
-      <c r="B230" s="14" t="s">
-        <v>563</v>
+      <c r="A230" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -5660,10 +5657,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -5673,11 +5670,11 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>124</v>
+      <c r="A232" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -5687,11 +5684,11 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A233" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>423</v>
+      <c r="A233" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>278</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -5702,10 +5699,10 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>278</v>
+        <v>64</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>6</v>
@@ -5716,13 +5713,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B235" s="10" t="s">
-        <v>318</v>
+        <v>100</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>7</v>
@@ -5730,13 +5727,13 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>7</v>
@@ -5744,10 +5741,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -5758,10 +5755,10 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" s="8" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -5771,11 +5768,11 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B239" s="9" t="s">
-        <v>207</v>
+      <c r="A239" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -5785,11 +5782,11 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A240" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>465</v>
+      <c r="A240" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>284</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -5799,11 +5796,11 @@
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="B241" s="9" t="s">
-        <v>284</v>
+      <c r="A241" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B241" s="14" t="s">
+        <v>581</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -5813,11 +5810,11 @@
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="B242" s="14" t="s">
-        <v>582</v>
+      <c r="A242" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -5827,28 +5824,28 @@
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>251</v>
+      <c r="A243" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B244" s="9" t="s">
-        <v>210</v>
+      <c r="A244" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>7</v>
@@ -5856,10 +5853,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>408</v>
+        <v>466</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>407</v>
+        <v>465</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>6</v>
@@ -5870,12 +5867,12 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="13" t="s">
-        <v>467</v>
+        <v>536</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C246" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C246" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D246" s="2" t="s">
@@ -5883,13 +5880,13 @@
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C247" s="4" t="s">
+      <c r="A247" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D247" s="2" t="s">
@@ -5898,10 +5895,10 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="B248" s="9" t="s">
-        <v>126</v>
+        <v>238</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>6</v>
@@ -5911,13 +5908,13 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B249" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C249" s="2" t="s">
+      <c r="A249" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C249" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
@@ -5925,13 +5922,13 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C250" s="4" t="s">
+      <c r="A250" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B250" t="s">
+        <v>640</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
@@ -5939,14 +5936,14 @@
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="B251" t="s">
-        <v>641</v>
+      <c r="A251" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>7</v>
@@ -5954,26 +5951,26 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>51</v>
+        <v>273</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C253" s="2" t="s">
+      <c r="A253" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C253" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D253" s="2" t="s">
@@ -5981,13 +5978,13 @@
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="C254" s="4" t="s">
+      <c r="A254" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B254" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D254" s="2" t="s">
@@ -5995,11 +5992,11 @@
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="B255" s="9" t="s">
-        <v>304</v>
+      <c r="A255" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -6010,10 +6007,10 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" s="13" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -6023,11 +6020,11 @@
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>325</v>
+      <c r="A257" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B257" t="s">
+        <v>642</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -6037,11 +6034,11 @@
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="6" t="s">
-        <v>644</v>
-      </c>
-      <c r="B258" t="s">
-        <v>643</v>
+      <c r="A258" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -6051,11 +6048,11 @@
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A259" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>269</v>
+      <c r="A259" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -6065,11 +6062,11 @@
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>330</v>
+      <c r="A260" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B260" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -6079,11 +6076,11 @@
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>38</v>
+      <c r="A261" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B261" t="s">
+        <v>649</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -6093,11 +6090,11 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A262" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="B262" t="s">
-        <v>650</v>
+      <c r="A262" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B262" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -6108,10 +6105,10 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>6</v>
@@ -6122,38 +6119,38 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="8" t="s">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B265" s="9" t="s">
-        <v>221</v>
+      <c r="A265" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>558</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>559</v>
+      <c r="A266" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>6</v>
@@ -6163,13 +6160,13 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C267" s="2" t="s">
+      <c r="A267" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C267" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D267" s="2" t="s">
@@ -6177,13 +6174,13 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="B268" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C268" s="4" t="s">
+      <c r="A268" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D268" s="2" t="s">
@@ -6191,13 +6188,13 @@
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C269" s="2" t="s">
+      <c r="A269" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C269" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D269" s="2" t="s">
@@ -6205,13 +6202,13 @@
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A270" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="B270" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C270" s="4" t="s">
+      <c r="A270" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B270" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D270" s="2" t="s">
@@ -6220,10 +6217,10 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="B271" s="14" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -6233,11 +6230,11 @@
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="B272" s="14" t="s">
-        <v>561</v>
+      <c r="A272" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>6</v>
@@ -6247,13 +6244,13 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C273" s="2" t="s">
+      <c r="A273" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C273" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D273" s="2" t="s">
@@ -6261,13 +6258,13 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B274" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C274" s="4" t="s">
+      <c r="A274" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B274" s="14" t="s">
+        <v>577</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D274" s="2" t="s">
@@ -6275,11 +6272,11 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="B275" s="14" t="s">
-        <v>578</v>
+      <c r="A275" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>6</v>
@@ -6289,8 +6286,8 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="8" t="s">
-        <v>125</v>
+      <c r="A276" s="13" t="s">
+        <v>471</v>
       </c>
       <c r="B276" s="9" t="s">
         <v>126</v>
@@ -6303,11 +6300,11 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A277" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="B277" s="9" t="s">
-        <v>126</v>
+      <c r="A277" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="B277" s="14" t="s">
+        <v>572</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>6</v>
@@ -6318,109 +6315,109 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="B278" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="B278" t="s">
+        <v>644</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B281" t="s">
+        <v>579</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B285" s="14" t="s">
         <v>573</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B279" t="s">
-        <v>645</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B280" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="B282" t="s">
-        <v>580</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B284" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
       </c>
@@ -6429,11 +6426,11 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A286" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="B286" s="14" t="s">
-        <v>574</v>
+      <c r="A286" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>6</v>
@@ -6444,66 +6441,66 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="8" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B288" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C288" s="2" t="s">
+      <c r="A288" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="13" t="s">
-        <v>538</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="D289" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B290" s="9" t="s">
-        <v>182</v>
+      <c r="A290" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>365</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A291" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>366</v>
+      <c r="A291" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -6514,10 +6511,10 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="8" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -6527,11 +6524,11 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B293" s="9" t="s">
-        <v>53</v>
+      <c r="A293" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>6</v>
@@ -6541,13 +6538,13 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="6" t="s">
-        <v>608</v>
+      <c r="A294" s="13" t="s">
+        <v>539</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C294" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C294" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D294" s="2" t="s">
@@ -6555,41 +6552,41 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="B295" s="3" t="s">
+      <c r="A295" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B295" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="B296" t="s">
+        <v>595</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="C295" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B296" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="B297" t="s">
-        <v>596</v>
-      </c>
-      <c r="C297" s="2" t="s">
+      <c r="B297" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C297" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D297" s="2" t="s">
@@ -6597,13 +6594,13 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A298" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="C298" s="4" t="s">
+      <c r="A298" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B298" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D298" s="2" t="s">
@@ -6612,27 +6609,27 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="8" t="s">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A300" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B300" s="9" t="s">
-        <v>20</v>
+      <c r="A300" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B300" t="s">
+        <v>624</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>7</v>
@@ -6640,10 +6637,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="B301" t="s">
-        <v>625</v>
+        <v>654</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>653</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -6654,10 +6651,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>654</v>
+        <v>601</v>
+      </c>
+      <c r="B302" t="s">
+        <v>600</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -6667,11 +6664,11 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A303" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="B303" t="s">
-        <v>601</v>
+      <c r="A303" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B303" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -6682,10 +6679,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -6696,10 +6693,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>261</v>
+        <v>212</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -6710,10 +6707,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="8" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -6723,11 +6720,11 @@
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A307" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B307" s="9" t="s">
-        <v>188</v>
+      <c r="A307" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>6</v>
@@ -6738,12 +6735,12 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="13" t="s">
-        <v>372</v>
+        <v>543</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C308" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C308" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D308" s="2" t="s">
@@ -6752,12 +6749,12 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="13" t="s">
-        <v>544</v>
+        <v>438</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C309" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D309" s="2" t="s">
@@ -6765,11 +6762,11 @@
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>440</v>
+      <c r="A310" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B310" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -6779,11 +6776,11 @@
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A311" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B311" s="9" t="s">
-        <v>30</v>
+      <c r="A311" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B311" t="s">
+        <v>647</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -6794,10 +6791,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="B312" t="s">
-        <v>648</v>
+        <v>660</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>659</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -6807,11 +6804,11 @@
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A313" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="B313" s="3" t="s">
-        <v>660</v>
+      <c r="A313" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B313" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -6822,10 +6819,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -6836,10 +6833,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="B315" s="9" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -6850,10 +6847,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B316" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>6</v>
@@ -6863,13 +6860,13 @@
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A317" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B317" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C317" s="2" t="s">
+      <c r="A317" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C317" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D317" s="2" t="s">
@@ -6877,14 +6874,14 @@
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A318" s="13" t="s">
-        <v>546</v>
-      </c>
-      <c r="B318" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>6</v>
+      <c r="A318" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B318" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>7</v>
@@ -6892,26 +6889,26 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="8" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B319" s="9" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A320" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B320" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C320" s="2" t="s">
+      <c r="A320" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C320" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D320" s="2" t="s">
@@ -6920,12 +6917,12 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="13" t="s">
-        <v>316</v>
+        <v>388</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C321" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D321" s="2" t="s">
@@ -6933,11 +6930,11 @@
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A322" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="B322" s="3" t="s">
-        <v>400</v>
+      <c r="A322" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B322" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -6948,10 +6945,10 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="B323" s="9" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>6</v>
@@ -6962,13 +6959,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>7</v>
@@ -6976,13 +6973,13 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B325" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>7</v>
@@ -6990,10 +6987,10 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B326" s="9" t="s">
-        <v>192</v>
+        <v>93</v>
+      </c>
+      <c r="B326" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -7003,11 +7000,11 @@
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A327" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B327" s="10" t="s">
-        <v>319</v>
+      <c r="A327" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B327" s="14" t="s">
+        <v>575</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>6</v>
@@ -7017,13 +7014,13 @@
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A328" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="B328" s="14" t="s">
-        <v>576</v>
-      </c>
-      <c r="C328" s="2" t="s">
+      <c r="A328" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D328" s="2" t="s">
@@ -7032,12 +7029,12 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
-        <v>488</v>
+        <v>379</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C329" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C329" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D329" s="2" t="s">
@@ -7046,10 +7043,10 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="13" t="s">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -7059,11 +7056,11 @@
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A331" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="B331" s="3" t="s">
-        <v>411</v>
+      <c r="A331" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B331" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>6</v>
@@ -7074,13 +7071,13 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>7</v>
@@ -7088,10 +7085,10 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B333" s="9" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>16</v>
@@ -7101,27 +7098,27 @@
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B334" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>16</v>
+      <c r="A334" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D334" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="B335" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="C335" s="4" t="s">
+      <c r="A335" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B335" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D335" s="2" t="s">
@@ -7129,11 +7126,11 @@
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A336" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B336" s="9" t="s">
-        <v>11</v>
+      <c r="A336" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -7144,10 +7141,10 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>609</v>
+        <v>617</v>
+      </c>
+      <c r="B337" t="s">
+        <v>616</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>6</v>
@@ -7157,13 +7154,13 @@
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A338" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="B338" t="s">
-        <v>617</v>
-      </c>
-      <c r="C338" s="2" t="s">
+      <c r="A338" s="13" t="s">
+        <v>550</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C338" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D338" s="2" t="s">
@@ -7172,12 +7169,12 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="13" t="s">
-        <v>551</v>
+        <v>475</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="C339" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D339" s="2" t="s">
@@ -7185,11 +7182,11 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="13" t="s">
-        <v>476</v>
+      <c r="A340" s="6" t="s">
+        <v>655</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>477</v>
+        <v>656</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -7199,11 +7196,11 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="6" t="s">
-        <v>656</v>
-      </c>
-      <c r="B341" s="3" t="s">
-        <v>657</v>
+      <c r="A341" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B341" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>6</v>
@@ -7212,22 +7209,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B342" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D342" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D293"/>
+  <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">
     <sortCondition ref="A2:A342"/>
   </sortState>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="665">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2008,6 +2008,15 @@
   </si>
   <si>
     <t>Karthik Jyothy Puthoor</t>
+  </si>
+  <si>
+    <t>Pawan Kumar</t>
+  </si>
+  <si>
+    <t>Pawan Thakur</t>
+  </si>
+  <si>
+    <t>Pavan Thakur</t>
   </si>
 </sst>
 </file>
@@ -2426,7 +2435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -7209,6 +7218,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="662">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2008,15 +2008,6 @@
   </si>
   <si>
     <t>Karthik Jyothy Puthoor</t>
-  </si>
-  <si>
-    <t>Pawan Kumar</t>
-  </si>
-  <si>
-    <t>Pawan Thakur</t>
-  </si>
-  <si>
-    <t>Pavan Thakur</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D343"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -7218,34 +7209,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A342" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="B342" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D342" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A343" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="B343" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C343" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D343" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Verified Aliases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$291</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="660">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -1318,12 +1318,6 @@
   </si>
   <si>
     <t>Kris McNeill</t>
-  </si>
-  <si>
-    <t>Jack Kirkpatrick jnr</t>
-  </si>
-  <si>
-    <t>Jack Kirkpatrick</t>
   </si>
   <si>
     <t>Muhammad Hussain</t>
@@ -2426,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D340"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -2451,10 +2445,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -2479,10 +2473,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6</v>
@@ -2493,10 +2487,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
@@ -2507,10 +2501,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6</v>
@@ -2605,10 +2599,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6</v>
@@ -2647,10 +2641,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6</v>
@@ -2689,10 +2683,10 @@
     </row>
     <row r="19" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>6</v>
@@ -2703,10 +2697,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -2773,10 +2767,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>6</v>
@@ -2843,10 +2837,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>6</v>
@@ -2927,10 +2921,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>6</v>
@@ -2941,7 +2935,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>394</v>
@@ -2997,10 +2991,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -3193,10 +3187,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>6</v>
@@ -3221,10 +3215,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>6</v>
@@ -3249,10 +3243,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>6</v>
@@ -3319,10 +3313,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>6</v>
@@ -3375,10 +3369,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>6</v>
@@ -3459,10 +3453,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>6</v>
@@ -3529,10 +3523,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>6</v>
@@ -3543,10 +3537,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
@@ -3571,10 +3565,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
@@ -3627,10 +3621,10 @@
     </row>
     <row r="86" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -3641,10 +3635,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>6</v>
@@ -3669,10 +3663,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>6</v>
@@ -3683,10 +3677,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>6</v>
@@ -3697,10 +3691,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>6</v>
@@ -3753,10 +3747,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>6</v>
@@ -3767,10 +3761,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>6</v>
@@ -3781,10 +3775,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>6</v>
@@ -3809,10 +3803,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>6</v>
@@ -3851,10 +3845,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>6</v>
@@ -3865,10 +3859,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>6</v>
@@ -3879,10 +3873,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="15" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>6</v>
@@ -3963,7 +3957,7 @@
     </row>
     <row r="110" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>134</v>
@@ -4019,10 +4013,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="15" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>6</v>
@@ -4033,10 +4027,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>6</v>
@@ -4061,10 +4055,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="15" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>6</v>
@@ -4075,10 +4069,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>6</v>
@@ -4103,10 +4097,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="15" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>6</v>
@@ -4117,10 +4111,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B121" s="12" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>6</v>
@@ -4131,10 +4125,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>6</v>
@@ -4145,10 +4139,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B123" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>6</v>
@@ -4159,10 +4153,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>6</v>
@@ -4173,10 +4167,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>6</v>
@@ -4187,10 +4181,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="15" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>6</v>
@@ -4201,10 +4195,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>6</v>
@@ -4214,11 +4208,11 @@
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>417</v>
+      <c r="A128" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>6</v>
@@ -4228,11 +4222,11 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>215</v>
+      <c r="A129" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>6</v>
@@ -4243,7 +4237,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>416</v>
+        <v>195</v>
       </c>
       <c r="B130" s="12" t="s">
         <v>196</v>
@@ -4257,10 +4251,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>195</v>
+        <v>509</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>196</v>
+        <v>552</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -4271,10 +4265,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>511</v>
+        <v>451</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>554</v>
+        <v>452</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>6</v>
@@ -4284,11 +4278,11 @@
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>454</v>
+      <c r="A133" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>630</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>6</v>
@@ -4298,11 +4292,11 @@
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="B134" s="17" t="s">
-        <v>632</v>
+      <c r="A134" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>6</v>
@@ -4312,11 +4306,11 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>376</v>
+      <c r="A135" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>6</v>
@@ -4327,10 +4321,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="s">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>24</v>
+        <v>286</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>6</v>
@@ -4340,11 +4334,11 @@
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>286</v>
+      <c r="A137" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>244</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>6</v>
@@ -4354,11 +4348,11 @@
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B138" s="12" t="s">
-        <v>244</v>
+      <c r="A138" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>6</v>
@@ -4369,10 +4363,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>6</v>
@@ -4383,10 +4377,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>6</v>
@@ -4396,11 +4390,11 @@
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>290</v>
+      <c r="A141" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>429</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>6</v>
@@ -4410,11 +4404,11 @@
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="B142" s="12" t="s">
-        <v>429</v>
+      <c r="A142" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>596</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>6</v>
@@ -4424,11 +4418,11 @@
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="15" t="s">
-        <v>599</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>598</v>
+      <c r="A143" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>6</v>
@@ -4438,11 +4432,11 @@
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>109</v>
+      <c r="A144" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>634</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>6</v>
@@ -4452,28 +4446,28 @@
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>636</v>
+      <c r="A145" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>49</v>
+      <c r="A146" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>347</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>7</v>
@@ -4481,10 +4475,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>6</v>
@@ -4494,11 +4488,11 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B148" s="12" t="s">
-        <v>350</v>
+      <c r="A148" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>232</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>6</v>
@@ -4508,11 +4502,11 @@
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>232</v>
+      <c r="A149" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="B149" s="12" t="s">
+        <v>375</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>6</v>
@@ -4523,10 +4517,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>6</v>
@@ -4537,7 +4531,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>392</v>
+        <v>659</v>
       </c>
       <c r="B151" s="12" t="s">
         <v>403</v>
@@ -4551,10 +4545,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>661</v>
+        <v>340</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>403</v>
+        <v>341</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>6</v>
@@ -4565,10 +4559,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>340</v>
+        <v>453</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>341</v>
+        <v>454</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>6</v>
@@ -4579,10 +4573,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>6</v>
@@ -4592,39 +4586,39 @@
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="11" t="s">
-        <v>431</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>430</v>
+      <c r="A155" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>88</v>
+      <c r="A156" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>585</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="B157" s="17" t="s">
-        <v>587</v>
+      <c r="A157" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>246</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>6</v>
@@ -4634,13 +4628,13 @@
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C158" s="2" t="s">
+      <c r="A158" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D158" s="2" t="s">
@@ -4649,12 +4643,12 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>518</v>
+        <v>382</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="C159" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D159" s="2" t="s">
@@ -4663,10 +4657,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>6</v>
@@ -4676,11 +4670,11 @@
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="B161" s="12" t="s">
-        <v>401</v>
+      <c r="A161" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>583</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>6</v>
@@ -4690,11 +4684,11 @@
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="B162" s="17" t="s">
-        <v>585</v>
+      <c r="A162" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B162" s="14" t="s">
+        <v>419</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>6</v>
@@ -4705,10 +4699,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="16" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="B163" s="14" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>6</v>
@@ -4719,12 +4713,12 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="16" t="s">
-        <v>389</v>
+        <v>517</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="C164" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D164" s="2" t="s">
@@ -4732,13 +4726,13 @@
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="16" t="s">
-        <v>519</v>
-      </c>
-      <c r="B165" s="14" t="s">
-        <v>520</v>
-      </c>
-      <c r="C165" s="4" t="s">
+      <c r="A165" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D165" s="2" t="s">
@@ -4746,13 +4740,13 @@
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="B166" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="C166" s="2" t="s">
+      <c r="A166" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="B166" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D166" s="2" t="s">
@@ -4760,67 +4754,67 @@
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="B167" s="14" t="s">
-        <v>488</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>6</v>
+      <c r="A167" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>7</v>
+        <v>307</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="B168" s="9" t="s">
-        <v>306</v>
+      <c r="A168" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="C168" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D168" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="6" t="s">
-        <v>611</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="D169" s="2" t="s">
-        <v>7</v>
+        <v>314</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="B170" s="9" t="s">
-        <v>313</v>
+      <c r="A170" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>311</v>
+        <v>6</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>314</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>602</v>
+      <c r="A171" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>204</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>6</v>
@@ -4831,10 +4825,10 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
-        <v>203</v>
+        <v>91</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>6</v>
@@ -4845,68 +4839,68 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>92</v>
+        <v>180</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B174" s="9" t="s">
-        <v>180</v>
+      <c r="A174" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B174" s="14" t="s">
+        <v>336</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="B175" s="14" t="s">
-        <v>336</v>
+      <c r="A175" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>551</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>7</v>
+        <v>312</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="B176" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>311</v>
+      <c r="B176" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>312</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
-        <v>310</v>
+        <v>455</v>
       </c>
       <c r="B177" s="14" t="s">
-        <v>553</v>
-      </c>
-      <c r="C177" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D177" s="2" t="s">
@@ -4914,11 +4908,11 @@
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="B178" s="14" t="s">
-        <v>458</v>
+      <c r="A178" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B178" s="18" t="s">
+        <v>456</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>6</v>
@@ -4928,11 +4922,11 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="B179" s="18" t="s">
-        <v>458</v>
+      <c r="A179" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="B179" s="14" t="s">
+        <v>339</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>6</v>
@@ -4943,13 +4937,13 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="B180" s="14" t="s">
-        <v>339</v>
+        <v>323</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>7</v>
@@ -4957,13 +4951,13 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>16</v>
+        <v>519</v>
+      </c>
+      <c r="B181" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>7</v>
@@ -4971,10 +4965,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="B182" s="14" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>6</v>
@@ -4984,13 +4978,13 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="B183" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="C183" s="4" t="s">
+      <c r="A183" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B183" t="s">
+        <v>621</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D183" s="2" t="s">
@@ -4998,11 +4992,11 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="B184" t="s">
-        <v>623</v>
+      <c r="A184" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="B184" s="14" t="s">
+        <v>466</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -5013,10 +5007,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
-        <v>467</v>
+        <v>353</v>
       </c>
       <c r="B185" s="14" t="s">
-        <v>468</v>
+        <v>354</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>6</v>
@@ -5026,39 +5020,39 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="B186" s="14" t="s">
-        <v>354</v>
+      <c r="A186" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B187" s="9" t="s">
-        <v>78</v>
+      <c r="A187" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="B187" s="14" t="s">
+        <v>432</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="B188" s="14" t="s">
-        <v>434</v>
+      <c r="A188" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>240</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>6</v>
@@ -5068,11 +5062,11 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B189" s="9" t="s">
-        <v>240</v>
+      <c r="A189" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B189" t="s">
+        <v>626</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -5082,13 +5076,13 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="B190" t="s">
-        <v>628</v>
-      </c>
-      <c r="C190" s="2" t="s">
+      <c r="A190" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="B190" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D190" s="2" t="s">
@@ -5097,12 +5091,12 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="16" t="s">
-        <v>523</v>
+        <v>342</v>
       </c>
       <c r="B191" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="C191" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D191" s="2" t="s">
@@ -5110,11 +5104,11 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="B192" s="14" t="s">
-        <v>343</v>
+      <c r="A192" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -5125,10 +5119,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>6</v>
@@ -5138,11 +5132,11 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B194" s="9" t="s">
-        <v>202</v>
+      <c r="A194" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B194" s="14" t="s">
+        <v>409</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>6</v>
@@ -5152,98 +5146,98 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="B195" s="14" t="s">
-        <v>409</v>
+      <c r="A195" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B196" s="9" t="s">
-        <v>164</v>
+      <c r="A196" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>458</v>
       </c>
       <c r="C196" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D196" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="13" t="s">
+      <c r="D197" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B198" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B198" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="C198" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="B199" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B200" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="13" t="s">
-        <v>525</v>
-      </c>
-      <c r="B201" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>6</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>7</v>
@@ -5251,13 +5245,13 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>107</v>
+        <v>234</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>7</v>
@@ -5265,10 +5259,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>234</v>
+        <v>57</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>6</v>
@@ -5278,11 +5272,11 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B204" s="9" t="s">
-        <v>57</v>
+      <c r="A204" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>602</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>6</v>
@@ -5292,13 +5286,13 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="6" t="s">
-        <v>605</v>
+      <c r="A205" s="13" t="s">
+        <v>525</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C205" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C205" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D205" s="2" t="s">
@@ -5306,13 +5300,13 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="13" t="s">
-        <v>527</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C206" s="4" t="s">
+      <c r="A206" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B206" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D206" s="2" t="s">
@@ -5321,10 +5315,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>6</v>
@@ -5334,11 +5328,11 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B208" s="9" t="s">
-        <v>66</v>
+      <c r="A208" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>611</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>6</v>
@@ -5348,11 +5342,11 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>613</v>
+      <c r="A209" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>6</v>
@@ -5362,11 +5356,11 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B210" s="9" t="s">
-        <v>105</v>
+      <c r="A210" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B210" t="s">
+        <v>636</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>6</v>
@@ -5376,14 +5370,14 @@
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="B211" t="s">
-        <v>638</v>
+      <c r="A211" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -5391,10 +5385,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>16</v>
@@ -5405,10 +5399,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>16</v>
@@ -5418,27 +5412,27 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B214" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>16</v>
+      <c r="A214" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C215" s="4" t="s">
+      <c r="A215" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D215" s="2" t="s">
@@ -5447,10 +5441,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -5461,10 +5455,10 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>6</v>
@@ -5474,11 +5468,11 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B218" s="9" t="s">
-        <v>55</v>
+      <c r="A218" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>331</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -5489,10 +5483,10 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="13" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -5503,10 +5497,10 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="13" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>6</v>
@@ -5516,11 +5510,11 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>358</v>
+      <c r="A221" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>275</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -5531,27 +5525,27 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
-        <v>274</v>
+        <v>75</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>76</v>
+      <c r="A223" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
@@ -5559,10 +5553,10 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="13" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>356</v>
+        <v>472</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -5573,10 +5567,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>474</v>
+        <v>397</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -5587,12 +5581,12 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="13" t="s">
-        <v>386</v>
+        <v>526</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C226" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D226" s="2" t="s">
@@ -5600,13 +5594,13 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A227" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C227" s="4" t="s">
+      <c r="A227" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B227" t="s">
+        <v>402</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D227" s="2" t="s">
@@ -5614,11 +5608,11 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B228" t="s">
-        <v>402</v>
+      <c r="A228" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="B228" s="14" t="s">
+        <v>560</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>6</v>
@@ -5628,11 +5622,11 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="13" t="s">
-        <v>561</v>
-      </c>
-      <c r="B229" s="14" t="s">
-        <v>562</v>
+      <c r="A229" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -5643,10 +5637,10 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>6</v>
@@ -5656,11 +5650,11 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B231" s="9" t="s">
-        <v>124</v>
+      <c r="A231" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>6</v>
@@ -5670,11 +5664,11 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>422</v>
+      <c r="A232" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="B232" s="9" t="s">
+        <v>278</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -5685,10 +5679,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="B233" s="9" t="s">
-        <v>278</v>
+        <v>64</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -5699,13 +5693,13 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B234" s="10" t="s">
-        <v>317</v>
+        <v>100</v>
+      </c>
+      <c r="B234" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>7</v>
@@ -5713,13 +5707,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>7</v>
@@ -5727,10 +5721,10 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -5741,10 +5735,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>130</v>
+        <v>207</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>6</v>
@@ -5754,11 +5748,11 @@
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B238" s="9" t="s">
-        <v>207</v>
+      <c r="A238" s="13" t="s">
+        <v>461</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>6</v>
@@ -5768,11 +5762,11 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>464</v>
+      <c r="A239" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>284</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>6</v>
@@ -5782,11 +5776,11 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A240" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="B240" s="9" t="s">
-        <v>284</v>
+      <c r="A240" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="B240" s="14" t="s">
+        <v>579</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>6</v>
@@ -5796,11 +5790,11 @@
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="B241" s="14" t="s">
-        <v>581</v>
+      <c r="A241" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>6</v>
@@ -5810,28 +5804,28 @@
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>251</v>
+      <c r="A242" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B243" s="9" t="s">
-        <v>210</v>
+      <c r="A243" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
@@ -5839,10 +5833,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="13" t="s">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>406</v>
+        <v>463</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -5853,12 +5847,12 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
-        <v>466</v>
+        <v>534</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C245" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C245" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D245" s="2" t="s">
@@ -5866,13 +5860,13 @@
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C246" s="4" t="s">
+      <c r="A246" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B246" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D246" s="2" t="s">
@@ -5881,10 +5875,10 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
-        <v>295</v>
+        <v>237</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>126</v>
+        <v>238</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>6</v>
@@ -5894,13 +5888,13 @@
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B248" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C248" s="2" t="s">
+      <c r="A248" s="13" t="s">
+        <v>528</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D248" s="2" t="s">
@@ -5908,13 +5902,13 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C249" s="4" t="s">
+      <c r="A249" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B249" t="s">
+        <v>638</v>
+      </c>
+      <c r="C249" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D249" s="2" t="s">
@@ -5922,14 +5916,14 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="B250" t="s">
-        <v>640</v>
+      <c r="A250" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>7</v>
@@ -5937,26 +5931,26 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>51</v>
+        <v>273</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D251" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B252" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C252" s="2" t="s">
+      <c r="A252" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C252" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D252" s="2" t="s">
@@ -5964,13 +5958,13 @@
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="B253" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="C253" s="4" t="s">
+      <c r="A253" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D253" s="2" t="s">
@@ -5978,11 +5972,11 @@
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B254" s="9" t="s">
-        <v>303</v>
+      <c r="A254" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -5993,10 +5987,10 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>6</v>
@@ -6006,11 +6000,11 @@
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>324</v>
+      <c r="A256" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B256" t="s">
+        <v>640</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>6</v>
@@ -6020,11 +6014,11 @@
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="B257" t="s">
-        <v>642</v>
+      <c r="A257" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>6</v>
@@ -6034,11 +6028,11 @@
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>269</v>
+      <c r="A258" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>6</v>
@@ -6048,11 +6042,11 @@
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A259" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>329</v>
+      <c r="A259" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>6</v>
@@ -6062,11 +6056,11 @@
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>38</v>
+      <c r="A260" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B260" t="s">
+        <v>647</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>6</v>
@@ -6076,11 +6070,11 @@
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="6" t="s">
-        <v>650</v>
-      </c>
-      <c r="B261" t="s">
-        <v>649</v>
+      <c r="A261" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -6091,10 +6085,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -6105,38 +6099,38 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
-        <v>287</v>
+        <v>220</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D263" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>221</v>
+      <c r="A264" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>556</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>558</v>
+      <c r="A265" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>6</v>
@@ -6146,13 +6140,13 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C266" s="2" t="s">
+      <c r="A266" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C266" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D266" s="2" t="s">
@@ -6160,13 +6154,13 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="C267" s="4" t="s">
+      <c r="A267" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D267" s="2" t="s">
@@ -6174,13 +6168,13 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C268" s="2" t="s">
+      <c r="A268" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C268" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D268" s="2" t="s">
@@ -6188,13 +6182,13 @@
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="B269" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C269" s="4" t="s">
+      <c r="A269" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B269" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D269" s="2" t="s">
@@ -6203,10 +6197,10 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="B270" s="14" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>6</v>
@@ -6216,11 +6210,11 @@
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A271" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="B271" s="14" t="s">
-        <v>560</v>
+      <c r="A271" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>6</v>
@@ -6230,13 +6224,13 @@
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C272" s="2" t="s">
+      <c r="A272" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D272" s="2" t="s">
@@ -6244,13 +6238,13 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="B273" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C273" s="4" t="s">
+      <c r="A273" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B273" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D273" s="2" t="s">
@@ -6258,11 +6252,11 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="B274" s="14" t="s">
-        <v>577</v>
+      <c r="A274" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>6</v>
@@ -6272,8 +6266,8 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="8" t="s">
-        <v>125</v>
+      <c r="A275" s="13" t="s">
+        <v>469</v>
       </c>
       <c r="B275" s="9" t="s">
         <v>126</v>
@@ -6286,11 +6280,11 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>126</v>
+      <c r="A276" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B276" s="14" t="s">
+        <v>570</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -6301,109 +6295,109 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B277" t="s">
+        <v>642</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B278" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B280" t="s">
+        <v>577</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B282" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B284" s="14" t="s">
         <v>571</v>
       </c>
-      <c r="B277" s="14" t="s">
-        <v>572</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="B278" t="s">
-        <v>644</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B279" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B281" t="s">
-        <v>579</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B283" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="C284" s="2" t="s">
         <v>6</v>
       </c>
@@ -6412,11 +6406,11 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="B285" s="14" t="s">
-        <v>573</v>
+      <c r="A285" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>228</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -6427,66 +6421,66 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B287" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C287" s="2" t="s">
+      <c r="A287" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B288" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D287" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="B288" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>6</v>
-      </c>
       <c r="D288" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B289" s="9" t="s">
-        <v>182</v>
+      <c r="A289" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>365</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B290" s="3" t="s">
-        <v>365</v>
+      <c r="A290" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B290" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -6497,10 +6491,10 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
-        <v>151</v>
+        <v>52</v>
       </c>
       <c r="B291" s="9" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>6</v>
@@ -6510,11 +6504,11 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B292" s="9" t="s">
-        <v>53</v>
+      <c r="A292" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>604</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>6</v>
@@ -6524,13 +6518,13 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="6" t="s">
-        <v>607</v>
+      <c r="A293" s="13" t="s">
+        <v>537</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C293" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C293" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D293" s="2" t="s">
@@ -6538,41 +6532,41 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="13" t="s">
+      <c r="A294" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B294" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="B295" t="s">
+        <v>593</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="B294" s="3" t="s">
+      <c r="B296" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="C294" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B295" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="B296" t="s">
-        <v>595</v>
-      </c>
-      <c r="C296" s="2" t="s">
+      <c r="C296" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D296" s="2" t="s">
@@ -6580,13 +6574,13 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C297" s="4" t="s">
+      <c r="A297" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B297" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D297" s="2" t="s">
@@ -6595,27 +6589,27 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
-        <v>225</v>
+        <v>19</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B299" s="9" t="s">
-        <v>20</v>
+      <c r="A299" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="B299" t="s">
+        <v>622</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>7</v>
@@ -6623,10 +6617,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
-        <v>625</v>
-      </c>
-      <c r="B300" t="s">
-        <v>624</v>
+        <v>652</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>651</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -6637,10 +6631,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>653</v>
+        <v>599</v>
+      </c>
+      <c r="B301" t="s">
+        <v>598</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>6</v>
@@ -6650,11 +6644,11 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="B302" t="s">
-        <v>600</v>
+      <c r="A302" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B302" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -6665,10 +6659,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="B303" s="9" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -6679,10 +6673,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>261</v>
+        <v>212</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -6693,10 +6687,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>6</v>
@@ -6706,11 +6700,11 @@
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A306" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="B306" s="9" t="s">
-        <v>188</v>
+      <c r="A306" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -6721,12 +6715,12 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="13" t="s">
-        <v>371</v>
+        <v>541</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C307" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C307" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D307" s="2" t="s">
@@ -6735,12 +6729,12 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="13" t="s">
-        <v>543</v>
+        <v>436</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C308" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D308" s="2" t="s">
@@ -6748,11 +6742,11 @@
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A309" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="B309" s="3" t="s">
-        <v>439</v>
+      <c r="A309" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B309" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>6</v>
@@ -6762,11 +6756,11 @@
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B310" s="9" t="s">
-        <v>30</v>
+      <c r="A310" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B310" t="s">
+        <v>645</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -6777,10 +6771,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="B311" t="s">
-        <v>647</v>
+        <v>658</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>657</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>6</v>
@@ -6790,11 +6784,11 @@
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A312" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="B312" s="3" t="s">
-        <v>659</v>
+      <c r="A312" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B312" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -6805,10 +6799,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -6819,10 +6813,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>17</v>
+        <v>149</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -6833,10 +6827,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B315" s="9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>6</v>
@@ -6846,13 +6840,13 @@
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A316" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B316" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C316" s="2" t="s">
+      <c r="A316" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D316" s="2" t="s">
@@ -6860,14 +6854,14 @@
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A317" s="13" t="s">
-        <v>545</v>
-      </c>
-      <c r="B317" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="C317" s="4" t="s">
-        <v>6</v>
+      <c r="A317" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>7</v>
@@ -6875,26 +6869,26 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B318" s="9" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A319" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B319" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C319" s="2" t="s">
+      <c r="A319" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C319" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D319" s="2" t="s">
@@ -6903,12 +6897,12 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="13" t="s">
-        <v>315</v>
+        <v>388</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="C320" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D320" s="2" t="s">
@@ -6916,11 +6910,11 @@
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A321" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="B321" s="3" t="s">
-        <v>399</v>
+      <c r="A321" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B321" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -6931,10 +6925,10 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -6945,13 +6939,13 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B323" s="9" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>7</v>
@@ -6959,13 +6953,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>7</v>
@@ -6973,10 +6967,10 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B325" s="9" t="s">
-        <v>192</v>
+        <v>93</v>
+      </c>
+      <c r="B325" s="10" t="s">
+        <v>318</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>6</v>
@@ -6986,11 +6980,11 @@
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A326" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B326" s="10" t="s">
-        <v>318</v>
+      <c r="A326" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B326" s="14" t="s">
+        <v>573</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>6</v>
@@ -7000,13 +6994,13 @@
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A327" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="B327" s="14" t="s">
-        <v>575</v>
-      </c>
-      <c r="C327" s="2" t="s">
+      <c r="A327" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C327" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D327" s="2" t="s">
@@ -7015,12 +7009,12 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="13" t="s">
-        <v>487</v>
+        <v>379</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C328" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C328" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D328" s="2" t="s">
@@ -7029,10 +7023,10 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>6</v>
@@ -7042,11 +7036,11 @@
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A330" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="B330" s="3" t="s">
-        <v>410</v>
+      <c r="A330" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -7057,13 +7051,13 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>7</v>
@@ -7071,10 +7065,10 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>16</v>
@@ -7084,27 +7078,27 @@
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A333" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B333" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>16</v>
+      <c r="A333" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="13" t="s">
-        <v>547</v>
-      </c>
-      <c r="B334" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C334" s="4" t="s">
+      <c r="A334" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B334" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C334" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D334" s="2" t="s">
@@ -7112,11 +7106,11 @@
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B335" s="9" t="s">
-        <v>11</v>
+      <c r="A335" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -7127,10 +7121,10 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
-        <v>609</v>
-      </c>
-      <c r="B336" s="3" t="s">
-        <v>608</v>
+        <v>615</v>
+      </c>
+      <c r="B336" t="s">
+        <v>614</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>6</v>
@@ -7140,13 +7134,13 @@
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="6" t="s">
-        <v>617</v>
-      </c>
-      <c r="B337" t="s">
-        <v>616</v>
-      </c>
-      <c r="C337" s="2" t="s">
+      <c r="A337" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C337" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D337" s="2" t="s">
@@ -7155,12 +7149,12 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="13" t="s">
-        <v>550</v>
+        <v>473</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="C338" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C338" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D338" s="2" t="s">
@@ -7168,11 +7162,11 @@
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="13" t="s">
-        <v>475</v>
+      <c r="A339" s="6" t="s">
+        <v>653</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>476</v>
+        <v>654</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>6</v>
@@ -7182,11 +7176,11 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="B340" s="3" t="s">
-        <v>656</v>
+      <c r="A340" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B340" s="9" t="s">
+        <v>144</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>6</v>
@@ -7195,22 +7189,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A341" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B341" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D341" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D292"/>
+  <autoFilter ref="A1:D291"/>
   <sortState ref="A2:D342">
     <sortCondition ref="A2:A342"/>
   </sortState>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -2001,7 +2001,7 @@
     <t>Tom Stevenson</t>
   </si>
   <si>
-    <t>Karthik Jyothy Puthoor</t>
+    <t>Karthik Puthoor Jyothy</t>
   </si>
 </sst>
 </file>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Verified Aliases" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Verified Aliases'!$A$1:$D$292</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="661">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2002,6 +2002,9 @@
   </si>
   <si>
     <t>Karthik Puthoor Jyothy</t>
+  </si>
+  <si>
+    <t>Mohan Vijayakumar</t>
   </si>
 </sst>
 </file>
@@ -2420,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D340"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -4978,25 +4981,25 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="6" t="s">
+      <c r="A183" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="B183" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>621</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="B184" s="14" t="s">
-        <v>466</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>6</v>
@@ -5007,82 +5010,82 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="B185" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="B185" s="14" t="s">
+      <c r="B186" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="8" t="s">
+      <c r="C186" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B187" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C186" s="2" t="s">
+      <c r="C187" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D186" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="16" t="s">
+      <c r="D187" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="16" t="s">
         <v>433</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B188" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="8" t="s">
+      <c r="C188" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B188" s="9" t="s">
+      <c r="B189" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="6" t="s">
+      <c r="C189" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="B189" t="s">
+      <c r="B190" t="s">
         <v>626</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="B190" s="14" t="s">
-        <v>522</v>
-      </c>
-      <c r="C190" s="4" t="s">
+      <c r="C190" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D190" s="2" t="s">
@@ -5091,24 +5094,24 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="B191" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="16" t="s">
         <v>342</v>
       </c>
-      <c r="B191" s="14" t="s">
+      <c r="B192" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B192" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>6</v>
@@ -5119,125 +5122,125 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B194" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="16" t="s">
+      <c r="C194" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B195" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="8" t="s">
+      <c r="C195" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B196" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C195" s="2" t="s">
+      <c r="C196" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="13" t="s">
+      <c r="D196" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B197" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="8" t="s">
+      <c r="C197" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B198" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C197" s="2" t="s">
+      <c r="C198" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D197" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="13" t="s">
+      <c r="D198" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B199" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="8" t="s">
+      <c r="C199" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B199" s="9" t="s">
+      <c r="B200" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="13" t="s">
+      <c r="C200" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B201" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C200" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B201" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>16</v>
+      <c r="C201" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>7</v>
@@ -5245,13 +5248,13 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
-        <v>233</v>
+        <v>106</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>234</v>
+        <v>107</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>7</v>
@@ -5259,54 +5262,54 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="B204" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C203" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A204" s="6" t="s">
+      <c r="C204" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B205" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A205" s="13" t="s">
+      <c r="C205" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B206" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C205" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A206" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B206" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C206" s="2" t="s">
+      <c r="C206" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D206" s="2" t="s">
@@ -5315,69 +5318,69 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B207" s="9" t="s">
+      <c r="B208" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C207" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A208" s="6" t="s">
+      <c r="C208" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B209" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="C208" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A209" s="8" t="s">
+      <c r="C209" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B209" s="9" t="s">
+      <c r="B210" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C209" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A210" s="6" t="s">
+      <c r="C210" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="B210" t="s">
+      <c r="B211" t="s">
         <v>636</v>
       </c>
-      <c r="C210" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A211" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B211" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="C211" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -5385,10 +5388,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" s="8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>16</v>
@@ -5399,10 +5402,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" s="8" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>16</v>
@@ -5412,27 +5415,27 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A214" s="13" t="s">
+      <c r="A214" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B215" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C214" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A215" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B215" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C215" s="2" t="s">
+      <c r="C215" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D215" s="2" t="s">
@@ -5441,10 +5444,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>6</v>
@@ -5455,24 +5458,24 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B218" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A218" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>6</v>
@@ -5483,10 +5486,10 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" s="13" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>6</v>
@@ -5497,24 +5500,24 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B221" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A221" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>6</v>
@@ -5525,27 +5528,27 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B223" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C222" s="2" t="s">
+      <c r="C223" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A223" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>7</v>
@@ -5553,10 +5556,10 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" s="13" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>472</v>
+        <v>356</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>6</v>
@@ -5567,10 +5570,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="13" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>397</v>
+        <v>472</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>6</v>
@@ -5581,52 +5584,52 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B227" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C226" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A227" s="6" t="s">
+      <c r="C227" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="B227" t="s">
+      <c r="B228" t="s">
         <v>402</v>
       </c>
-      <c r="C227" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A228" s="13" t="s">
+      <c r="C228" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="B228" s="14" t="s">
+      <c r="B229" s="14" t="s">
         <v>560</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A229" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B229" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>6</v>
@@ -5637,38 +5640,38 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B230" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B230" s="9" t="s">
+      <c r="B231" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="C230" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A231" s="13" t="s">
+      <c r="C231" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="13" t="s">
         <v>421</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B232" s="3" t="s">
         <v>422</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A232" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="B232" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>6</v>
@@ -5679,10 +5682,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>317</v>
+        <v>348</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>278</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>6</v>
@@ -5693,13 +5696,13 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>101</v>
+        <v>64</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>317</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>7</v>
@@ -5707,13 +5710,13 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="8" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>7</v>
@@ -5721,10 +5724,10 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>6</v>
@@ -5735,97 +5738,97 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B237" s="9" t="s">
+      <c r="B238" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C237" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A238" s="13" t="s">
+      <c r="C238" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B239" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="C238" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
+      <c r="C239" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B239" s="9" t="s">
+      <c r="B240" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="C239" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A240" s="6" t="s">
+      <c r="C240" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="6" t="s">
         <v>580</v>
       </c>
-      <c r="B240" s="14" t="s">
+      <c r="B241" s="14" t="s">
         <v>579</v>
       </c>
-      <c r="C240" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" s="13" t="s">
+      <c r="C241" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B242" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C241" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" s="8" t="s">
+      <c r="C242" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="B242" s="9" t="s">
+      <c r="B243" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C243" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D243" s="2" t="s">
         <v>7</v>
@@ -5833,10 +5836,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" s="13" t="s">
-        <v>464</v>
+        <v>407</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>463</v>
+        <v>406</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>6</v>
@@ -5847,26 +5850,26 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B246" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C245" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C246" s="2" t="s">
+      <c r="C246" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D246" s="2" t="s">
@@ -5875,55 +5878,55 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="B248" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C247" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" s="13" t="s">
+      <c r="C248" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B249" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="C248" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" s="6" t="s">
+      <c r="C249" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="B249" t="s">
+      <c r="B250" t="s">
         <v>638</v>
       </c>
-      <c r="C249" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B250" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="C250" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>7</v>
@@ -5931,52 +5934,52 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B252" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C251" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" s="13" t="s">
+      <c r="C252" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="13" t="s">
         <v>530</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B253" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C252" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="8" t="s">
+      <c r="C253" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="B254" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>6</v>
@@ -5987,94 +5990,94 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="B256" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C255" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" s="6" t="s">
+      <c r="C256" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B257" t="s">
         <v>640</v>
       </c>
-      <c r="C256" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" s="8" t="s">
+      <c r="C257" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B257" s="9" t="s">
+      <c r="B258" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C257" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="13" t="s">
+      <c r="C258" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B259" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C258" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A259" s="8" t="s">
+      <c r="C259" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B259" s="9" t="s">
+      <c r="B260" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C259" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A260" s="6" t="s">
+      <c r="C260" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B261" t="s">
         <v>647</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A261" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B261" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>6</v>
@@ -6085,10 +6088,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="8" t="s">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="C262" s="2" t="s">
         <v>6</v>
@@ -6099,96 +6102,96 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="B264" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C263" s="2" t="s">
+      <c r="C264" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A264" s="13" t="s">
+      <c r="D264" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="B264" s="3" t="s">
+      <c r="B265" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="C264" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A265" s="8" t="s">
+      <c r="C265" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B265" s="9" t="s">
+      <c r="B266" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C265" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A266" s="13" t="s">
+      <c r="C266" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="13" t="s">
         <v>532</v>
       </c>
-      <c r="B266" s="3" t="s">
+      <c r="B267" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C266" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A267" s="8" t="s">
+      <c r="C267" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="B267" s="9" t="s">
+      <c r="B268" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="C267" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A268" s="13" t="s">
+      <c r="C268" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="B268" s="3" t="s">
+      <c r="B269" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C268" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A269" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="B269" s="14" t="s">
-        <v>567</v>
-      </c>
-      <c r="C269" s="2" t="s">
+      <c r="C269" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D269" s="2" t="s">
@@ -6197,77 +6200,77 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B270" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="6" t="s">
         <v>557</v>
       </c>
-      <c r="B270" s="14" t="s">
+      <c r="B271" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="C270" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A271" s="8" t="s">
+      <c r="C271" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B271" s="9" t="s">
+      <c r="B272" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C271" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="13" t="s">
+      <c r="C272" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="B272" s="3" t="s">
+      <c r="B273" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C272" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="6" t="s">
+      <c r="C273" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="B273" s="14" t="s">
+      <c r="B274" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C273" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A274" s="8" t="s">
+      <c r="C274" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A275" s="13" t="s">
-        <v>469</v>
       </c>
       <c r="B275" s="9" t="s">
         <v>126</v>
@@ -6280,11 +6283,11 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="B276" s="14" t="s">
-        <v>570</v>
+      <c r="A276" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B276" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>6</v>
@@ -6295,122 +6298,122 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B277" s="14" t="s">
+        <v>570</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="B277" t="s">
+      <c r="B278" t="s">
         <v>642</v>
       </c>
-      <c r="C277" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A278" s="8" t="s">
+      <c r="C278" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B278" s="9" t="s">
+      <c r="B279" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="C278" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A279" s="13" t="s">
+      <c r="C279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="B279" s="3" t="s">
+      <c r="B280" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C279" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A280" s="6" t="s">
+      <c r="C280" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="6" t="s">
         <v>644</v>
       </c>
-      <c r="B280" t="s">
+      <c r="B281" t="s">
         <v>577</v>
       </c>
-      <c r="C280" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A281" s="13" t="s">
+      <c r="C281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="B282" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C281" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A282" s="8" t="s">
+      <c r="C282" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B282" s="9" t="s">
+      <c r="B283" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="C282" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A283" s="13" t="s">
+      <c r="C283" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="B284" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C283" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A284" s="6" t="s">
+      <c r="C284" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="B284" s="14" t="s">
+      <c r="B285" s="14" t="s">
         <v>571</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B285" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>6</v>
@@ -6421,66 +6424,66 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B286" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="B287" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="C286" s="2" t="s">
+      <c r="C287" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D286" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A287" s="13" t="s">
+      <c r="D287" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="B287" s="3" t="s">
+      <c r="B288" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="C287" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A288" s="8" t="s">
+      <c r="C288" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B289" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C288" s="2" t="s">
+      <c r="C289" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="13" t="s">
+      <c r="D289" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B289" s="3" t="s">
+      <c r="B290" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A290" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B290" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>6</v>
@@ -6491,96 +6494,96 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B291" s="9" t="s">
+      <c r="B292" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C291" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A292" s="6" t="s">
+      <c r="C292" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="B292" s="3" t="s">
+      <c r="B293" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="C292" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A293" s="13" t="s">
+      <c r="C293" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="B293" s="3" t="s">
+      <c r="B294" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C293" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A294" s="8" t="s">
+      <c r="C294" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B294" s="9" t="s">
+      <c r="B295" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C294" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="6" t="s">
+      <c r="C295" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="6" t="s">
         <v>592</v>
       </c>
-      <c r="B295" t="s">
+      <c r="B296" t="s">
         <v>593</v>
       </c>
-      <c r="C295" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A296" s="13" t="s">
+      <c r="C296" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="13" t="s">
         <v>539</v>
       </c>
-      <c r="B296" s="3" t="s">
+      <c r="B297" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="C296" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A297" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="B297" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C297" s="2" t="s">
+      <c r="C297" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D297" s="2" t="s">
@@ -6589,27 +6592,27 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B298" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B298" s="9" t="s">
+      <c r="B299" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C298" s="2" t="s">
+      <c r="C299" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="B299" t="s">
-        <v>622</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>7</v>
@@ -6617,10 +6620,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
-        <v>652</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>651</v>
+        <v>623</v>
+      </c>
+      <c r="B300" t="s">
+        <v>622</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>6</v>
@@ -6631,24 +6634,24 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="6" t="s">
         <v>599</v>
       </c>
-      <c r="B301" t="s">
+      <c r="B302" t="s">
         <v>598</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B302" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>6</v>
@@ -6659,10 +6662,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="8" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="B303" s="9" t="s">
-        <v>261</v>
+        <v>212</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>6</v>
@@ -6673,10 +6676,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="8" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>6</v>
@@ -6687,24 +6690,24 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="B305" s="9" t="s">
+      <c r="B306" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A306" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="B306" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>6</v>
@@ -6715,12 +6718,12 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="13" t="s">
-        <v>541</v>
+        <v>371</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C307" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D307" s="2" t="s">
@@ -6729,38 +6732,38 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="13" t="s">
+        <v>541</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="B308" s="3" t="s">
+      <c r="B309" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="C308" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A309" s="8" t="s">
+      <c r="C309" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B309" s="9" t="s">
+      <c r="B310" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D309" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A310" s="6" t="s">
-        <v>646</v>
-      </c>
-      <c r="B310" t="s">
-        <v>645</v>
       </c>
       <c r="C310" s="2" t="s">
         <v>6</v>
@@ -6771,24 +6774,24 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B311" t="s">
+        <v>645</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="6" t="s">
         <v>658</v>
       </c>
-      <c r="B311" s="3" t="s">
+      <c r="B312" s="3" t="s">
         <v>657</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A312" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B312" s="9" t="s">
-        <v>267</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>6</v>
@@ -6799,10 +6802,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="8" t="s">
-        <v>17</v>
+        <v>266</v>
       </c>
       <c r="B313" s="9" t="s">
-        <v>18</v>
+        <v>267</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>6</v>
@@ -6813,10 +6816,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="8" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="B314" s="9" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>6</v>
@@ -6827,41 +6830,41 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B315" s="9" t="s">
+      <c r="B316" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C315" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A316" s="13" t="s">
+      <c r="C316" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="B316" s="3" t="s">
+      <c r="B317" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C316" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A317" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B317" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>16</v>
+      <c r="C317" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="D317" s="2" t="s">
         <v>7</v>
@@ -6869,26 +6872,26 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B318" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B318" s="9" t="s">
+      <c r="B319" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C318" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A319" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="B319" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C319" s="4" t="s">
+      <c r="C319" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D319" s="2" t="s">
@@ -6897,24 +6900,24 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="B320" s="3" t="s">
+      <c r="B321" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A321" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B321" s="9" t="s">
-        <v>132</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>6</v>
@@ -6925,10 +6928,10 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="8" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>6</v>
@@ -6939,13 +6942,13 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="8" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="B323" s="9" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>7</v>
@@ -6953,13 +6956,13 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B324" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>7</v>
@@ -6967,40 +6970,40 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B325" s="10" t="s">
+      <c r="B326" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="C325" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D325" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A326" s="6" t="s">
+      <c r="C326" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="6" t="s">
         <v>574</v>
       </c>
-      <c r="B326" s="14" t="s">
+      <c r="B327" s="14" t="s">
         <v>573</v>
       </c>
-      <c r="C326" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D326" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A327" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="B327" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C327" s="4" t="s">
+      <c r="C327" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D327" s="2" t="s">
@@ -7009,12 +7012,12 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="13" t="s">
-        <v>379</v>
+        <v>485</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C328" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D328" s="2" t="s">
@@ -7023,24 +7026,24 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="B329" s="3" t="s">
+      <c r="B330" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D329" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A330" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B330" s="9" t="s">
-        <v>136</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>6</v>
@@ -7051,13 +7054,13 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="8" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="B331" s="9" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>7</v>
@@ -7065,10 +7068,10 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="8" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B332" s="9" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>16</v>
@@ -7078,39 +7081,39 @@
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A333" s="13" t="s">
+      <c r="A333" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B333" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="B334" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="C333" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D333" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A334" s="8" t="s">
+      <c r="C334" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B334" s="9" t="s">
+      <c r="B335" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="C334" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D334" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="B335" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>6</v>
@@ -7121,26 +7124,26 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="B336" t="s">
+      <c r="B337" t="s">
         <v>614</v>
       </c>
-      <c r="C336" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D336" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A337" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="C337" s="4" t="s">
+      <c r="C337" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D337" s="2" t="s">
@@ -7149,48 +7152,62 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="B339" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C338" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D338" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A339" s="6" t="s">
+      <c r="C339" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="6" t="s">
         <v>653</v>
       </c>
-      <c r="B339" s="3" t="s">
+      <c r="B340" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="C339" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D339" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A340" s="8" t="s">
+      <c r="C340" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B340" s="9" t="s">
+      <c r="B341" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C340" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D340" s="2" t="s">
+      <c r="C341" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D341" s="2" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D291"/>
+  <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">
     <sortCondition ref="A2:A342"/>
   </sortState>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="671">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2005,6 +2005,36 @@
   </si>
   <si>
     <t>Mohan Vijayakumar</t>
+  </si>
+  <si>
+    <t>Praveen kumar Kapala</t>
+  </si>
+  <si>
+    <t>Praveen Kapala</t>
+  </si>
+  <si>
+    <t>Gokula Kannan Gopala Krishnan</t>
+  </si>
+  <si>
+    <t>Gokula Gopala Krishnan</t>
+  </si>
+  <si>
+    <t>Tom Daniel Buchanan</t>
+  </si>
+  <si>
+    <t>Tom Buchanan</t>
+  </si>
+  <si>
+    <t>Thomas Cheethaparambill varghese</t>
+  </si>
+  <si>
+    <t>Thomas Varghese</t>
+  </si>
+  <si>
+    <t>Samuel Cave</t>
+  </si>
+  <si>
+    <t>Sam Cave</t>
   </si>
 </sst>
 </file>
@@ -2423,7 +2453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D341"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -7206,6 +7236,76 @@
         <v>7</v>
       </c>
     </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="673">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2035,6 +2035,12 @@
   </si>
   <si>
     <t>Sam Cave</t>
+  </si>
+  <si>
+    <t>Syam Kumar Sasidharan Nair</t>
+  </si>
+  <si>
+    <t>Syam Kumar</t>
   </si>
 </sst>
 </file>
@@ -2453,7 +2459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D347"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" style="6" customWidth="1"/>
@@ -7306,6 +7312,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D292"/>
   <sortState ref="A2:D342">

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57189F85-ACDE-4055-8667-305BCEE5F0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2700" yWindow="1020" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="687">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2069,13 +2075,19 @@
   </si>
   <si>
     <t>Added as per Wylie request</t>
+  </si>
+  <si>
+    <t>Shahbaz Umar Jalal Bhandara</t>
+  </si>
+  <si>
+    <t>Shahbaz Bhandara</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2112,13 +2124,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2156,7 +2176,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2190,6 +2210,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2224,9 +2245,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2399,11 +2421,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D353"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D354"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2417,7 +2445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2431,7 +2459,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2445,7 +2473,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2459,7 +2487,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2473,7 +2501,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2487,7 +2515,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2501,7 +2529,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2515,7 +2543,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2529,7 +2557,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2543,7 +2571,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2557,7 +2585,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2571,7 +2599,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2585,7 +2613,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2599,7 +2627,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2641,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2627,7 +2655,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2641,7 +2669,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2655,7 +2683,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2669,7 +2697,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2683,7 +2711,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2697,7 +2725,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2711,7 +2739,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2725,7 +2753,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2739,7 +2767,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -2753,7 +2781,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -2767,7 +2795,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2781,7 +2809,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -2795,7 +2823,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2809,7 +2837,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2823,7 +2851,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2837,7 +2865,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -2851,7 +2879,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2865,7 +2893,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -2879,7 +2907,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -2893,7 +2921,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -2907,7 +2935,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -2921,7 +2949,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -2935,7 +2963,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2949,7 +2977,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -2963,7 +2991,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -2977,7 +3005,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -2991,7 +3019,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -3005,7 +3033,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -3019,7 +3047,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -3033,7 +3061,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -3047,7 +3075,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -3061,7 +3089,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -3075,7 +3103,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -3089,7 +3117,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -3103,7 +3131,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -3117,7 +3145,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3131,7 +3159,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -3145,7 +3173,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -3159,7 +3187,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -3173,7 +3201,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -3187,7 +3215,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -3201,7 +3229,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -3215,7 +3243,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -3229,7 +3257,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -3243,7 +3271,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -3257,7 +3285,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -3271,7 +3299,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -3285,7 +3313,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -3299,7 +3327,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -3313,7 +3341,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -3327,7 +3355,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -3341,7 +3369,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -3355,7 +3383,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -3369,7 +3397,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -3383,7 +3411,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -3397,7 +3425,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3411,7 +3439,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -3425,7 +3453,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -3439,7 +3467,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -3453,7 +3481,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -3467,7 +3495,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -3481,7 +3509,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -3495,7 +3523,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -3509,7 +3537,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -3523,7 +3551,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -3537,7 +3565,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3551,7 +3579,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -3565,7 +3593,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -3579,7 +3607,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -3593,7 +3621,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -3607,7 +3635,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -3621,7 +3649,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -3635,7 +3663,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -3649,7 +3677,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -3663,7 +3691,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -3677,7 +3705,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -3691,7 +3719,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -3705,7 +3733,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -3719,7 +3747,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -3733,7 +3761,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -3747,7 +3775,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -3761,7 +3789,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -3775,7 +3803,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -3789,7 +3817,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -3803,7 +3831,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -3817,7 +3845,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -3831,7 +3859,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -3845,7 +3873,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -3859,7 +3887,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -3873,7 +3901,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -3887,7 +3915,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -3901,7 +3929,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -3915,7 +3943,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -3929,7 +3957,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -3943,7 +3971,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -3957,7 +3985,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3971,7 +3999,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3985,7 +4013,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -3999,7 +4027,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -4013,7 +4041,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -4027,7 +4055,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -4041,7 +4069,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -4055,7 +4083,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -4069,7 +4097,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -4083,7 +4111,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -4097,7 +4125,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -4111,7 +4139,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -4125,7 +4153,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -4139,7 +4167,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -4153,7 +4181,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -4167,7 +4195,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -4181,7 +4209,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -4195,7 +4223,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -4209,7 +4237,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>130</v>
       </c>
@@ -4223,7 +4251,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -4237,7 +4265,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -4251,7 +4279,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>133</v>
       </c>
@@ -4265,7 +4293,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -4279,7 +4307,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -4293,7 +4321,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -4307,7 +4335,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>137</v>
       </c>
@@ -4321,7 +4349,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -4335,7 +4363,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4349,7 +4377,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -4363,7 +4391,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>141</v>
       </c>
@@ -4377,7 +4405,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>142</v>
       </c>
@@ -4391,7 +4419,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -4405,7 +4433,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -4419,7 +4447,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>145</v>
       </c>
@@ -4433,7 +4461,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>146</v>
       </c>
@@ -4447,7 +4475,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -4461,7 +4489,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -4475,7 +4503,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>149</v>
       </c>
@@ -4489,7 +4517,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -4503,7 +4531,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>151</v>
       </c>
@@ -4517,7 +4545,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -4531,7 +4559,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>153</v>
       </c>
@@ -4545,7 +4573,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -4559,7 +4587,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>155</v>
       </c>
@@ -4573,7 +4601,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>156</v>
       </c>
@@ -4587,7 +4615,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>157</v>
       </c>
@@ -4601,7 +4629,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>158</v>
       </c>
@@ -4615,7 +4643,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>159</v>
       </c>
@@ -4629,7 +4657,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -4643,7 +4671,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>161</v>
       </c>
@@ -4657,7 +4685,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>162</v>
       </c>
@@ -4671,7 +4699,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>163</v>
       </c>
@@ -4685,7 +4713,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>164</v>
       </c>
@@ -4699,7 +4727,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>165</v>
       </c>
@@ -4713,7 +4741,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -4727,7 +4755,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>167</v>
       </c>
@@ -4741,7 +4769,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>168</v>
       </c>
@@ -4755,7 +4783,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>169</v>
       </c>
@@ -4769,7 +4797,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -4783,7 +4811,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>171</v>
       </c>
@@ -4797,7 +4825,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>172</v>
       </c>
@@ -4811,7 +4839,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>173</v>
       </c>
@@ -4825,7 +4853,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>174</v>
       </c>
@@ -4839,7 +4867,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>175</v>
       </c>
@@ -4853,7 +4881,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>175</v>
       </c>
@@ -4867,7 +4895,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>176</v>
       </c>
@@ -4881,7 +4909,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>176</v>
       </c>
@@ -4895,7 +4923,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -4909,7 +4937,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -4923,7 +4951,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -4937,7 +4965,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -4951,7 +4979,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -4965,7 +4993,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -4979,7 +5007,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>183</v>
       </c>
@@ -4993,7 +5021,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -5007,7 +5035,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -5021,7 +5049,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -5035,7 +5063,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -5049,7 +5077,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -5063,7 +5091,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -5077,7 +5105,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -5091,7 +5119,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -5105,7 +5133,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -5119,7 +5147,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -5133,7 +5161,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -5147,7 +5175,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -5161,7 +5189,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -5175,7 +5203,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>197</v>
       </c>
@@ -5189,7 +5217,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -5203,7 +5231,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5217,7 +5245,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>200</v>
       </c>
@@ -5231,7 +5259,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>201</v>
       </c>
@@ -5245,7 +5273,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -5259,7 +5287,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>203</v>
       </c>
@@ -5273,7 +5301,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>204</v>
       </c>
@@ -5287,7 +5315,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>205</v>
       </c>
@@ -5301,7 +5329,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -5315,7 +5343,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>207</v>
       </c>
@@ -5329,7 +5357,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>208</v>
       </c>
@@ -5343,7 +5371,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>209</v>
       </c>
@@ -5357,7 +5385,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>210</v>
       </c>
@@ -5371,7 +5399,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>211</v>
       </c>
@@ -5385,7 +5413,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>212</v>
       </c>
@@ -5399,7 +5427,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>213</v>
       </c>
@@ -5413,7 +5441,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>214</v>
       </c>
@@ -5427,7 +5455,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>215</v>
       </c>
@@ -5441,7 +5469,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>216</v>
       </c>
@@ -5455,7 +5483,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>217</v>
       </c>
@@ -5469,7 +5497,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -5483,7 +5511,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>219</v>
       </c>
@@ -5497,7 +5525,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -5511,7 +5539,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -5525,7 +5553,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -5539,7 +5567,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>223</v>
       </c>
@@ -5553,7 +5581,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>224</v>
       </c>
@@ -5567,7 +5595,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -5581,7 +5609,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>226</v>
       </c>
@@ -5595,7 +5623,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>227</v>
       </c>
@@ -5609,7 +5637,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -5623,7 +5651,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -5637,7 +5665,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="232" spans="1:4">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>230</v>
       </c>
@@ -5651,7 +5679,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="233" spans="1:4">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>231</v>
       </c>
@@ -5665,7 +5693,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="234" spans="1:4">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>232</v>
       </c>
@@ -5679,7 +5707,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="235" spans="1:4">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -5693,7 +5721,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="236" spans="1:4">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -5707,7 +5735,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="237" spans="1:4">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>235</v>
       </c>
@@ -5721,7 +5749,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="238" spans="1:4">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>236</v>
       </c>
@@ -5735,7 +5763,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="239" spans="1:4">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -5749,7 +5777,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="240" spans="1:4">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>238</v>
       </c>
@@ -5763,7 +5791,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>239</v>
       </c>
@@ -5777,7 +5805,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>240</v>
       </c>
@@ -5791,7 +5819,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>241</v>
       </c>
@@ -5805,7 +5833,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>242</v>
       </c>
@@ -5819,7 +5847,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>243</v>
       </c>
@@ -5833,7 +5861,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -5847,7 +5875,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>245</v>
       </c>
@@ -5861,7 +5889,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>246</v>
       </c>
@@ -5875,7 +5903,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>247</v>
       </c>
@@ -5889,7 +5917,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>248</v>
       </c>
@@ -5903,7 +5931,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>249</v>
       </c>
@@ -5917,7 +5945,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -5931,7 +5959,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>251</v>
       </c>
@@ -5945,7 +5973,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>252</v>
       </c>
@@ -5959,7 +5987,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>253</v>
       </c>
@@ -5973,7 +6001,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -5987,7 +6015,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -6001,7 +6029,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>256</v>
       </c>
@@ -6015,7 +6043,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>257</v>
       </c>
@@ -6029,7 +6057,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>258</v>
       </c>
@@ -6043,7 +6071,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>259</v>
       </c>
@@ -6057,7 +6085,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="262" spans="1:4">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>260</v>
       </c>
@@ -6071,7 +6099,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="263" spans="1:4">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>261</v>
       </c>
@@ -6085,7 +6113,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="264" spans="1:4">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>262</v>
       </c>
@@ -6099,7 +6127,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="265" spans="1:4">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>263</v>
       </c>
@@ -6113,7 +6141,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="266" spans="1:4">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>264</v>
       </c>
@@ -6127,7 +6155,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="267" spans="1:4">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>265</v>
       </c>
@@ -6141,7 +6169,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="268" spans="1:4">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>266</v>
       </c>
@@ -6155,7 +6183,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="269" spans="1:4">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>267</v>
       </c>
@@ -6169,7 +6197,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="270" spans="1:4">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>268</v>
       </c>
@@ -6183,7 +6211,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>269</v>
       </c>
@@ -6197,7 +6225,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>270</v>
       </c>
@@ -6211,7 +6239,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>271</v>
       </c>
@@ -6225,7 +6253,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>272</v>
       </c>
@@ -6239,7 +6267,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>273</v>
       </c>
@@ -6253,7 +6281,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>274</v>
       </c>
@@ -6267,7 +6295,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>275</v>
       </c>
@@ -6281,7 +6309,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>276</v>
       </c>
@@ -6295,7 +6323,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>277</v>
       </c>
@@ -6309,7 +6337,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>278</v>
       </c>
@@ -6323,7 +6351,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>279</v>
       </c>
@@ -6337,7 +6365,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="282" spans="1:4">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>280</v>
       </c>
@@ -6351,7 +6379,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="283" spans="1:4">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>281</v>
       </c>
@@ -6365,7 +6393,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="284" spans="1:4">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>282</v>
       </c>
@@ -6379,7 +6407,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="285" spans="1:4">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>283</v>
       </c>
@@ -6393,7 +6421,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="286" spans="1:4">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>284</v>
       </c>
@@ -6407,7 +6435,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="287" spans="1:4">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>285</v>
       </c>
@@ -6421,7 +6449,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="288" spans="1:4">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -6435,7 +6463,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>287</v>
       </c>
@@ -6449,7 +6477,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -6463,7 +6491,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -6477,7 +6505,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -6491,7 +6519,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -6505,7 +6533,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -6519,7 +6547,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -6533,7 +6561,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -6547,7 +6575,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -6561,7 +6589,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -6575,7 +6603,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -6589,7 +6617,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -6603,7 +6631,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -6617,7 +6645,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="302" spans="1:4">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -6631,7 +6659,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="303" spans="1:4">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -6645,7 +6673,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="304" spans="1:4">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -6659,7 +6687,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>303</v>
       </c>
@@ -6673,7 +6701,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -6687,7 +6715,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -6701,7 +6729,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -6715,7 +6743,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -6729,7 +6757,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -6743,7 +6771,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -6757,7 +6785,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="312" spans="1:4">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -6771,7 +6799,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="313" spans="1:4">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -6785,7 +6813,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="314" spans="1:4">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -6799,7 +6827,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="315" spans="1:4">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -6813,7 +6841,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="316" spans="1:4">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>314</v>
       </c>
@@ -6827,7 +6855,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="317" spans="1:4">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>315</v>
       </c>
@@ -6841,7 +6869,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="318" spans="1:4">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>316</v>
       </c>
@@ -6855,7 +6883,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="319" spans="1:4">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>317</v>
       </c>
@@ -6869,7 +6897,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="320" spans="1:4">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>318</v>
       </c>
@@ -6883,7 +6911,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="321" spans="1:4">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>319</v>
       </c>
@@ -6897,7 +6925,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="322" spans="1:4">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>320</v>
       </c>
@@ -6911,7 +6939,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="323" spans="1:4">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -6925,7 +6953,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="324" spans="1:4">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -6939,7 +6967,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="325" spans="1:4">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>323</v>
       </c>
@@ -6953,7 +6981,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="326" spans="1:4">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>324</v>
       </c>
@@ -6967,7 +6995,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="327" spans="1:4">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>325</v>
       </c>
@@ -6981,7 +7009,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="328" spans="1:4">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>326</v>
       </c>
@@ -6995,7 +7023,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="329" spans="1:4">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>327</v>
       </c>
@@ -7009,7 +7037,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="330" spans="1:4">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>328</v>
       </c>
@@ -7023,7 +7051,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="331" spans="1:4">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>329</v>
       </c>
@@ -7037,7 +7065,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="332" spans="1:4">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>330</v>
       </c>
@@ -7051,7 +7079,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="333" spans="1:4">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>331</v>
       </c>
@@ -7065,7 +7093,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="334" spans="1:4">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>332</v>
       </c>
@@ -7079,7 +7107,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="335" spans="1:4">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>333</v>
       </c>
@@ -7093,7 +7121,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="336" spans="1:4">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>334</v>
       </c>
@@ -7107,7 +7135,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="337" spans="1:4">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>335</v>
       </c>
@@ -7121,7 +7149,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="338" spans="1:4">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>336</v>
       </c>
@@ -7135,7 +7163,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="339" spans="1:4">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>337</v>
       </c>
@@ -7149,7 +7177,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="340" spans="1:4">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>338</v>
       </c>
@@ -7163,7 +7191,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="341" spans="1:4">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>339</v>
       </c>
@@ -7177,7 +7205,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="342" spans="1:4">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>340</v>
       </c>
@@ -7191,7 +7219,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="343" spans="1:4">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>341</v>
       </c>
@@ -7205,7 +7233,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="344" spans="1:4">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>342</v>
       </c>
@@ -7219,7 +7247,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="345" spans="1:4">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>343</v>
       </c>
@@ -7233,7 +7261,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="346" spans="1:4">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>344</v>
       </c>
@@ -7247,7 +7275,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="347" spans="1:4">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>345</v>
       </c>
@@ -7261,7 +7289,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="348" spans="1:4">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>103</v>
       </c>
@@ -7275,7 +7303,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="349" spans="1:4">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>346</v>
       </c>
@@ -7289,7 +7317,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="350" spans="1:4">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>301</v>
       </c>
@@ -7303,7 +7331,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="351" spans="1:4">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>347</v>
       </c>
@@ -7317,7 +7345,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="352" spans="1:4">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>348</v>
       </c>
@@ -7331,7 +7359,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="353" spans="1:4">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>349</v>
       </c>
@@ -7343,6 +7371,20 @@
       </c>
       <c r="D353" t="s">
         <v>684</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>685</v>
+      </c>
+      <c r="B354" t="s">
+        <v>686</v>
+      </c>
+      <c r="C354" t="s">
+        <v>674</v>
+      </c>
+      <c r="D354" t="s">
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57189F85-ACDE-4055-8667-305BCEE5F0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A7BB18-3971-421A-9AFA-5B901517FCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1020" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="1005" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2080,7 +2080,7 @@
     <t>Shahbaz Umar Jalal Bhandara</t>
   </si>
   <si>
-    <t>Shahbaz Bhandara</t>
+    <t xml:space="preserve">Shahbaz Bhandara </t>
   </si>
 </sst>
 </file>
@@ -7375,10 +7375,10 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
+        <v>686</v>
+      </c>
+      <c r="B354" t="s">
         <v>685</v>
-      </c>
-      <c r="B354" t="s">
-        <v>686</v>
       </c>
       <c r="C354" t="s">
         <v>674</v>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A7BB18-3971-421A-9AFA-5B901517FCAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A612131-A84D-4AB2-B15E-0D295264546F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="1005" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="1725" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="689">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2081,6 +2081,12 @@
   </si>
   <si>
     <t xml:space="preserve">Shahbaz Bhandara </t>
+  </si>
+  <si>
+    <t>Jaya Surya Sukhavasi</t>
+  </si>
+  <si>
+    <t>Jaya Sukhavasi</t>
   </si>
 </sst>
 </file>
@@ -2422,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D354"/>
+  <dimension ref="A1:D355"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -7387,6 +7393,14 @@
         <v>678</v>
       </c>
     </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>688</v>
+      </c>
+      <c r="B355" t="s">
+        <v>687</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A612131-A84D-4AB2-B15E-0D295264546F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550F8473-393F-46A5-AAA2-D143F7AC8583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1725" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="25335" windowHeight="19170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="681">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -547,9 +547,6 @@
     <t>Mohamed Ismail</t>
   </si>
   <si>
-    <t>Mohammad Ahmed</t>
-  </si>
-  <si>
     <t>Mohammed Agadi</t>
   </si>
   <si>
@@ -574,9 +571,6 @@
     <t>Muhamma Ajmal</t>
   </si>
   <si>
-    <t>Muhammad Asif</t>
-  </si>
-  <si>
     <t>Muhammad Shujee</t>
   </si>
   <si>
@@ -1069,9 +1063,6 @@
     <t>Darshan Kumar</t>
   </si>
   <si>
-    <t>Anna Lunney</t>
-  </si>
-  <si>
     <t>Avi Swaroop</t>
   </si>
   <si>
@@ -1549,9 +1540,6 @@
     <t>Ismail Mohamed</t>
   </si>
   <si>
-    <t>Muhammad Ahmed</t>
-  </si>
-  <si>
     <t>Mohammed Nayeem Agadi</t>
   </si>
   <si>
@@ -1573,9 +1561,6 @@
     <t>Muhammad Ajmal</t>
   </si>
   <si>
-    <t>Muhammad Essa Asif</t>
-  </si>
-  <si>
     <t>Muhammad Shujee Ahmed</t>
   </si>
   <si>
@@ -2041,9 +2026,6 @@
     <t>Darshan Hanumanth kumar</t>
   </si>
   <si>
-    <t>Anna Lunny</t>
-  </si>
-  <si>
     <t>Verified in Database</t>
   </si>
   <si>
@@ -2068,13 +2050,7 @@
     <t>Regarded as registered for Instonians for 2026</t>
   </si>
   <si>
-    <t>Transferred from Cooke Collegians to Belfast on 15th May 2026</t>
-  </si>
-  <si>
     <t>Added for transfers</t>
-  </si>
-  <si>
-    <t>Added as per Wylie request</t>
   </si>
   <si>
     <t>Shahbaz Umar Jalal Bhandara</t>
@@ -2428,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -2456,13 +2432,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2470,13 +2446,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2484,13 +2460,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C4" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D4" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2498,13 +2474,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C5" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D5" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2512,13 +2488,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D6" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2526,13 +2502,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C7" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D7" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2540,13 +2516,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C8" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D8" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2554,13 +2530,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C9" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D9" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2568,13 +2544,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C10" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D10" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2582,13 +2558,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C11" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D11" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2596,13 +2572,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C12" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D12" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2610,13 +2586,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C13" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D13" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2624,13 +2600,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C14" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D14" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2638,13 +2614,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C15" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D15" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2652,13 +2628,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C16" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D16" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2666,13 +2642,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C17" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D17" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2680,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C18" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D18" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,13 +2670,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C19" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D19" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2708,13 +2684,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C20" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D20" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2722,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C21" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D21" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2736,13 +2712,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C22" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D22" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2750,13 +2726,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C23" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D23" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2764,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C24" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D24" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2778,13 +2754,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C25" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D25" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2792,13 +2768,13 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C26" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D26" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2806,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C27" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D27" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2820,13 +2796,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C28" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D28" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2834,13 +2810,13 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C29" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D29" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2848,13 +2824,13 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D30" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2862,13 +2838,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C31" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D31" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2876,13 +2852,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C32" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D32" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2890,13 +2866,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C33" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D33" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2904,13 +2880,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C34" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D34" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2918,13 +2894,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C35" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D35" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,13 +2908,13 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C36" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D36" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2946,13 +2922,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C37" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D37" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2960,13 +2936,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C38" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D38" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2974,13 +2950,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C39" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D39" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2988,13 +2964,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C40" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D40" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3002,13 +2978,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C41" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D41" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3016,13 +2992,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C42" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D42" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3030,13 +3006,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C43" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D43" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3044,13 +3020,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C44" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D44" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3058,13 +3034,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C45" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D45" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3072,13 +3048,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C46" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D46" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3086,13 +3062,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C47" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D47" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3100,13 +3076,13 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C48" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D48" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3114,13 +3090,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C49" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D49" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3128,13 +3104,13 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C50" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D50" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3142,13 +3118,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D51" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3156,13 +3132,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C52" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D52" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3170,13 +3146,13 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C53" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D53" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3184,13 +3160,13 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C54" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D54" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3198,13 +3174,13 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C55" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D55" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3212,13 +3188,13 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C56" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D56" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3226,13 +3202,13 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C57" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D57" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3240,13 +3216,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C58" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D58" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3254,13 +3230,13 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C59" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D59" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3268,13 +3244,13 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C60" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D60" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3282,13 +3258,13 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C61" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D61" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3296,13 +3272,13 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C62" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D62" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3310,13 +3286,13 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C63" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D63" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3324,13 +3300,13 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C64" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D64" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3338,13 +3314,13 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C65" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D65" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3352,13 +3328,13 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C66" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D66" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3366,13 +3342,13 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C67" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D67" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3380,13 +3356,13 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C68" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D68" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3394,13 +3370,13 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C69" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D69" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3408,13 +3384,13 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C70" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D70" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3422,13 +3398,13 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C71" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D71" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3436,13 +3412,13 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C72" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D72" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3450,13 +3426,13 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C73" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D73" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3464,13 +3440,13 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C74" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D74" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3478,13 +3454,13 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C75" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D75" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3492,13 +3468,13 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C76" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D76" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3506,13 +3482,13 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C77" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D77" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3520,13 +3496,13 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D78" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3537,10 +3513,10 @@
         <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D79" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3551,10 +3527,10 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D80" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3562,13 +3538,13 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C81" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D81" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3576,13 +3552,13 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C82" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D82" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3590,13 +3566,13 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C83" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D83" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3604,13 +3580,13 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C84" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D84" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3618,13 +3594,13 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C85" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D85" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3632,13 +3608,13 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C86" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D86" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3646,13 +3622,13 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C87" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D87" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3660,13 +3636,13 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C88" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D88" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3674,13 +3650,13 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C89" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D89" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3688,13 +3664,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C90" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D90" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3702,13 +3678,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C91" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D91" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3716,13 +3692,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C92" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D92" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3730,13 +3706,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C93" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D93" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3744,13 +3720,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C94" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D94" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3758,13 +3734,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C95" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D95" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3772,13 +3748,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C96" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D96" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3786,13 +3762,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C97" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D97" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3800,13 +3776,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C98" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D98" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -3814,13 +3790,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C99" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D99" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3828,13 +3804,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C100" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D100" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -3842,13 +3818,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C101" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D101" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3856,13 +3832,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C102" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D102" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -3870,13 +3846,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C103" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D103" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -3884,13 +3860,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C104" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D104" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -3898,13 +3874,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C105" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D105" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3912,13 +3888,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C106" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D106" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -3926,13 +3902,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C107" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D107" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -3940,13 +3916,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C108" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D108" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -3954,13 +3930,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C109" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D109" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -3968,13 +3944,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C110" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D110" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -3982,13 +3958,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C111" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D111" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -3996,13 +3972,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C112" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D112" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4010,13 +3986,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C113" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D113" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4024,13 +4000,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C114" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D114" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4038,13 +4014,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C115" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D115" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4052,13 +4028,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C116" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D116" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4066,13 +4042,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C117" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D117" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4080,13 +4056,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C118" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D118" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4094,13 +4070,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C119" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D119" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4108,13 +4084,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C120" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D120" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4122,13 +4098,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C121" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D121" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4136,13 +4112,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C122" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D122" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4150,13 +4126,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C123" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D123" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4167,10 +4143,10 @@
         <v>131</v>
       </c>
       <c r="C124" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D124" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4178,13 +4154,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C125" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D125" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4192,13 +4168,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C126" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D126" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4206,13 +4182,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C127" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D127" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4220,13 +4196,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C128" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D128" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -4234,13 +4210,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C129" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D129" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -4248,13 +4224,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C130" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D130" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -4262,13 +4238,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C131" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D131" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -4276,13 +4252,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C132" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D132" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4290,13 +4266,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C133" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D133" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -4304,13 +4280,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C134" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D134" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -4318,13 +4294,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C135" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D135" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -4332,13 +4308,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C136" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D136" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4346,13 +4322,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C137" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D137" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -4360,13 +4336,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C138" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D138" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -4374,13 +4350,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C139" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D139" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -4388,13 +4364,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C140" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D140" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -4402,13 +4378,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C141" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D141" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4416,13 +4392,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C142" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D142" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -4430,13 +4406,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C143" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D143" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4444,13 +4420,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C144" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D144" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4458,13 +4434,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C145" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D145" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4472,13 +4448,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C146" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D146" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4486,13 +4462,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C147" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D147" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4500,13 +4476,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C148" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D148" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4514,13 +4490,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C149" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D149" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4528,13 +4504,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C150" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D150" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4542,13 +4518,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C151" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D151" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4556,13 +4532,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C152" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D152" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4570,13 +4546,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C153" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D153" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4584,13 +4560,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C154" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D154" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4598,13 +4574,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C155" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D155" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4612,13 +4588,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C156" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D156" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4626,13 +4602,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C157" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D157" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4640,13 +4616,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C158" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D158" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4654,13 +4630,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C159" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D159" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4668,13 +4644,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C160" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D160" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4682,13 +4658,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C161" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D161" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4696,13 +4672,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C162" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D162" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4710,13 +4686,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C163" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D163" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4724,13 +4700,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C164" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D164" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4738,13 +4714,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C165" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D165" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4752,13 +4728,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C166" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D166" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4769,10 +4745,10 @@
         <v>167</v>
       </c>
       <c r="C167" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D167" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4780,13 +4756,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C168" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D168" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -4797,10 +4773,10 @@
         <v>169</v>
       </c>
       <c r="C169" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D169" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -4808,13 +4784,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C170" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D170" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -4822,13 +4798,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C171" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D171" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -4836,13 +4812,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C172" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D172" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4850,13 +4826,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C173" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D173" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -4864,13 +4840,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C174" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D174" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -4878,2407 +4854,2407 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C175" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="D175" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C176" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D176" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C177" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D177" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C178" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D178" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C179" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D179" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C180" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D180" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C181" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D181" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C182" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D182" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C183" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D183" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C184" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D184" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C185" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D185" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C186" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D186" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C187" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D187" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C188" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D188" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C189" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D189" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C190" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D190" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C191" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D191" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C192" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D192" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C193" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D193" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C194" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D194" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C195" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D195" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C196" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D196" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C197" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D197" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C198" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D198" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C199" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D199" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C200" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D200" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C201" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D201" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B202" t="s">
-        <v>533</v>
+        <v>202</v>
       </c>
       <c r="C202" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D202" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C203" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D203" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C204" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D204" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C205" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D205" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>535</v>
       </c>
       <c r="C206" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D206" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C207" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D207" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C208" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D208" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C209" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D209" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C210" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D210" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C211" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D211" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C212" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D212" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C213" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D213" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>544</v>
+        <v>373</v>
       </c>
       <c r="C214" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D214" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C215" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D215" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C216" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D216" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C217" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D217" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>376</v>
+        <v>546</v>
       </c>
       <c r="C218" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D218" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C219" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D219" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C220" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D220" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C221" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D221" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C222" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D222" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C223" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D223" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C224" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D224" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C225" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D225" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C226" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D226" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C227" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D227" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C228" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D228" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C229" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D229" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C230" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D230" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C231" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D231" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C232" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D232" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B233" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C233" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D233" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B234" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C234" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D234" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C235" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D235" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C236" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D236" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B237" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C237" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D237" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B238" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C238" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D238" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B239" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C239" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D239" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B240" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C240" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D240" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B241" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C241" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D241" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B242" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C242" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D242" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B243" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C243" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D243" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B244" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C244" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D244" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B245" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C245" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D245" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B246" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C246" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D246" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B247" t="s">
-        <v>576</v>
+        <v>508</v>
       </c>
       <c r="C247" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D247" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B248" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C248" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D248" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B249" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C249" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D249" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B250" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C250" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D250" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B251" t="s">
-        <v>512</v>
+        <v>578</v>
       </c>
       <c r="C251" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D251" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B252" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C252" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D252" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B253" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C253" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D253" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B254" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C254" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D254" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B255" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C255" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D255" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B256" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C256" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D256" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B257" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C257" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D257" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B258" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C258" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D258" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B259" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C259" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D259" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B260" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C260" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D260" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B261" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C261" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D261" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B262" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C262" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D262" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B263" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C263" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D263" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B264" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="C264" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D264" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B265" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C265" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D265" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B266" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C266" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D266" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B267" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C267" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D267" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B268" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="C268" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D268" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B269" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
       <c r="C269" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D269" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B270" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C270" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D270" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B271" t="s">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="C271" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D271" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B272" t="s">
-        <v>599</v>
+        <v>571</v>
       </c>
       <c r="C272" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D272" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B273" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C273" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D273" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B274" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C274" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D274" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B275" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="C275" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D275" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B276" t="s">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="C276" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D276" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B277" t="s">
-        <v>601</v>
+        <v>349</v>
       </c>
       <c r="C277" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D277" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B278" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C278" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D278" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B279" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C279" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D279" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B280" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C280" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D280" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B281" t="s">
-        <v>352</v>
+        <v>603</v>
       </c>
       <c r="C281" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D281" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B282" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C282" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D282" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B283" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C283" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D283" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C284" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D284" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B285" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C285" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D285" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B286" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C286" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D286" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B287" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C287" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D287" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B288" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C288" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D288" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B289" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C289" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D289" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B290" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C290" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D290" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B291" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C291" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D291" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B292" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C292" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D292" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B293" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C293" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D293" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B294" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C294" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D294" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B295" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C295" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D295" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B296" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C296" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D296" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B297" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C297" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D297" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B298" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C298" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D298" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B299" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C299" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D299" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B300" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C300" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D300" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B301" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C301" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D301" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B302" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C302" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D302" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B303" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C303" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D303" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B304" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C304" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D304" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B305" t="s">
         <v>626</v>
       </c>
       <c r="C305" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D305" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B306" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C306" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D306" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B307" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C307" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D307" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B308" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C308" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D308" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B309" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C309" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D309" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B310" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C310" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D310" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B311" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C311" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D311" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B312" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C312" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D312" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B313" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C313" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D313" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B314" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C314" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D314" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B315" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C315" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D315" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B316" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C316" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D316" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B317" t="s">
-        <v>639</v>
+        <v>491</v>
       </c>
       <c r="C317" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D317" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B318" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C318" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D318" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B319" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C319" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D319" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B320" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C320" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D320" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B321" t="s">
-        <v>494</v>
+        <v>641</v>
       </c>
       <c r="C321" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D321" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B322" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C322" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D322" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B323" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C323" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D323" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B324" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C324" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D324" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B325" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C325" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D325" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B326" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C326" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D326" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B327" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C327" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D327" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B328" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C328" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D328" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B329" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C329" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D329" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B330" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C330" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D330" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B331" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C331" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D331" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B332" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C332" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D332" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B333" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C333" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="D333" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B334" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C334" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D334" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B335" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C335" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D335" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B336" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C336" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D336" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B337" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C337" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D337" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B338" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C338" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D338" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B339" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C339" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D339" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B340" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C340" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D340" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B341" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C341" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D341" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B342" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C342" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D342" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B343" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C343" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D343" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>342</v>
+        <v>103</v>
       </c>
       <c r="B344" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C344" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D344" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C345" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D345" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="B346" t="s">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="C346" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D346" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -7286,119 +7262,49 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C347" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D347" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>103</v>
+        <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C348" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D348" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>346</v>
+        <v>678</v>
       </c>
       <c r="B349" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="C349" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="D349" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>301</v>
+        <v>680</v>
       </c>
       <c r="B350" t="s">
-        <v>626</v>
-      </c>
-      <c r="C350" t="s">
-        <v>677</v>
-      </c>
-      <c r="D350" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>347</v>
-      </c>
-      <c r="B351" t="s">
-        <v>671</v>
-      </c>
-      <c r="C351" t="s">
-        <v>677</v>
-      </c>
-      <c r="D351" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>348</v>
-      </c>
-      <c r="B352" t="s">
-        <v>672</v>
-      </c>
-      <c r="C352" t="s">
-        <v>677</v>
-      </c>
-      <c r="D352" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>349</v>
-      </c>
-      <c r="B353" t="s">
-        <v>673</v>
-      </c>
-      <c r="C353" t="s">
-        <v>677</v>
-      </c>
-      <c r="D353" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>686</v>
-      </c>
-      <c r="B354" t="s">
-        <v>685</v>
-      </c>
-      <c r="C354" t="s">
-        <v>674</v>
-      </c>
-      <c r="D354" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>688</v>
-      </c>
-      <c r="B355" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550F8473-393F-46A5-AAA2-D143F7AC8583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BC39DE-75D2-44EA-83BF-1982D29E3746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="25335" windowHeight="19170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="1725" windowWidth="30255" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="705">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2063,6 +2063,78 @@
   </si>
   <si>
     <t>Jaya Sukhavasi</t>
+  </si>
+  <si>
+    <t>Harish Rayi</t>
+  </si>
+  <si>
+    <t>Venkataharish Rayi</t>
+  </si>
+  <si>
+    <t>Kavyadeep Bhamra</t>
+  </si>
+  <si>
+    <t>Kavyadeep Singh</t>
+  </si>
+  <si>
+    <t>Josh McClune</t>
+  </si>
+  <si>
+    <t>Joshua McClune</t>
+  </si>
+  <si>
+    <t>Fergus Emmett</t>
+  </si>
+  <si>
+    <t>Frgus Emmett</t>
+  </si>
+  <si>
+    <t>Izzy Jones</t>
+  </si>
+  <si>
+    <t>Susie McCollum</t>
+  </si>
+  <si>
+    <t>Abbie Gunning</t>
+  </si>
+  <si>
+    <t>Aimee Logan</t>
+  </si>
+  <si>
+    <t>Alex Atkinson</t>
+  </si>
+  <si>
+    <t>Ellie Murray</t>
+  </si>
+  <si>
+    <t>Vismithaa Pandiaraj</t>
+  </si>
+  <si>
+    <t>Ellen Murray</t>
+  </si>
+  <si>
+    <t>Isabelle Jones</t>
+  </si>
+  <si>
+    <t>Susanna McCollum</t>
+  </si>
+  <si>
+    <t>Abigail Gunning</t>
+  </si>
+  <si>
+    <t>Aimeee Logan</t>
+  </si>
+  <si>
+    <t>Alexandra Atkinson</t>
+  </si>
+  <si>
+    <t>Vismithaa Sai Pandiaraj</t>
+  </si>
+  <si>
+    <t>Johnny Shannon</t>
+  </si>
+  <si>
+    <t>Jonny Shannon</t>
   </si>
 </sst>
 </file>
@@ -2404,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D350"/>
+  <dimension ref="A1:D362"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -7306,6 +7378,180 @@
       <c r="B350" t="s">
         <v>679</v>
       </c>
+      <c r="C350" t="s">
+        <v>668</v>
+      </c>
+      <c r="D350" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>682</v>
+      </c>
+      <c r="B351" t="s">
+        <v>681</v>
+      </c>
+      <c r="C351" t="s">
+        <v>668</v>
+      </c>
+      <c r="D351" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>684</v>
+      </c>
+      <c r="B352" t="s">
+        <v>683</v>
+      </c>
+      <c r="C352" t="s">
+        <v>668</v>
+      </c>
+      <c r="D352" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>685</v>
+      </c>
+      <c r="B353" t="s">
+        <v>686</v>
+      </c>
+      <c r="C353" t="s">
+        <v>668</v>
+      </c>
+      <c r="D353" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>687</v>
+      </c>
+      <c r="B354" t="s">
+        <v>688</v>
+      </c>
+      <c r="C354" t="s">
+        <v>668</v>
+      </c>
+      <c r="D354" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>689</v>
+      </c>
+      <c r="B355" t="s">
+        <v>697</v>
+      </c>
+      <c r="C355" t="s">
+        <v>668</v>
+      </c>
+      <c r="D355" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>690</v>
+      </c>
+      <c r="B356" t="s">
+        <v>698</v>
+      </c>
+      <c r="C356" t="s">
+        <v>668</v>
+      </c>
+      <c r="D356" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>691</v>
+      </c>
+      <c r="B357" t="s">
+        <v>699</v>
+      </c>
+      <c r="C357" t="s">
+        <v>668</v>
+      </c>
+      <c r="D357" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>692</v>
+      </c>
+      <c r="B358" t="s">
+        <v>700</v>
+      </c>
+      <c r="C358" t="s">
+        <v>668</v>
+      </c>
+      <c r="D358" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>693</v>
+      </c>
+      <c r="B359" t="s">
+        <v>701</v>
+      </c>
+      <c r="C359" t="s">
+        <v>668</v>
+      </c>
+      <c r="D359" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>694</v>
+      </c>
+      <c r="B360" t="s">
+        <v>696</v>
+      </c>
+      <c r="C360" t="s">
+        <v>668</v>
+      </c>
+      <c r="D360" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>695</v>
+      </c>
+      <c r="B361" t="s">
+        <v>702</v>
+      </c>
+      <c r="C361" t="s">
+        <v>668</v>
+      </c>
+      <c r="D361" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>703</v>
+      </c>
+      <c r="B362" t="s">
+        <v>704</v>
+      </c>
+      <c r="C362" t="s">
+        <v>668</v>
+      </c>
+      <c r="D362" t="s">
+        <v>672</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BC39DE-75D2-44EA-83BF-1982D29E3746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAB0884-8E62-449D-992D-57FFB7992437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1725" windowWidth="30255" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="729">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -1063,6 +1063,78 @@
     <t>Darshan Kumar</t>
   </si>
   <si>
+    <t xml:space="preserve">Shahbaz Bhandara </t>
+  </si>
+  <si>
+    <t>Jaya Sukhavasi</t>
+  </si>
+  <si>
+    <t>Venkataharish Rayi</t>
+  </si>
+  <si>
+    <t>Kavyadeep Singh</t>
+  </si>
+  <si>
+    <t>Josh McClune</t>
+  </si>
+  <si>
+    <t>Fergus Emmett</t>
+  </si>
+  <si>
+    <t>Izzy Jones</t>
+  </si>
+  <si>
+    <t>Susie McCollum</t>
+  </si>
+  <si>
+    <t>Abbie Gunning</t>
+  </si>
+  <si>
+    <t>Aimee Logan</t>
+  </si>
+  <si>
+    <t>Alex Atkinson</t>
+  </si>
+  <si>
+    <t>Ellie Murray</t>
+  </si>
+  <si>
+    <t>Vismithaa Pandiaraj</t>
+  </si>
+  <si>
+    <t>Johnny Shannon</t>
+  </si>
+  <si>
+    <t>Nathan McCurry</t>
+  </si>
+  <si>
+    <t>Will Noffke</t>
+  </si>
+  <si>
+    <t>Stephen Entwhistle</t>
+  </si>
+  <si>
+    <t>Thomas Vidamour</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick jnr</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick snr</t>
+  </si>
+  <si>
+    <t>Tony Louis Pathipally</t>
+  </si>
+  <si>
+    <t>Henry O'Neill</t>
+  </si>
+  <si>
+    <t>stuart COP</t>
+  </si>
+  <si>
+    <t>Akaah Vega</t>
+  </si>
+  <si>
     <t>Avi Swaroop</t>
   </si>
   <si>
@@ -2026,6 +2098,72 @@
     <t>Darshan Hanumanth kumar</t>
   </si>
   <si>
+    <t>Shahbaz Umar Jalal Bhandara</t>
+  </si>
+  <si>
+    <t>Jaya Surya Sukhavasi</t>
+  </si>
+  <si>
+    <t>Harish Rayi</t>
+  </si>
+  <si>
+    <t>Kavyadeep Bhamra</t>
+  </si>
+  <si>
+    <t>Joshua McClune</t>
+  </si>
+  <si>
+    <t>Frgus Emmett</t>
+  </si>
+  <si>
+    <t>Isabelle Jones</t>
+  </si>
+  <si>
+    <t>Susanna McCollum</t>
+  </si>
+  <si>
+    <t>Abigail Gunning</t>
+  </si>
+  <si>
+    <t>Aimeee Logan</t>
+  </si>
+  <si>
+    <t>Alexandra Atkinson</t>
+  </si>
+  <si>
+    <t>Ellen Murray</t>
+  </si>
+  <si>
+    <t>Vismithaa Sai Pandiaraj</t>
+  </si>
+  <si>
+    <t>Jonny Shannon</t>
+  </si>
+  <si>
+    <t>Nathann Mccurry</t>
+  </si>
+  <si>
+    <t>Will Noffkee</t>
+  </si>
+  <si>
+    <t>Stephen Entwistle</t>
+  </si>
+  <si>
+    <t>Vhomas Tidamour</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick</t>
+  </si>
+  <si>
+    <t>Henry O’Neill</t>
+  </si>
+  <si>
+    <t>Stuart Copeland</t>
+  </si>
+  <si>
+    <t>Akash Vega</t>
+  </si>
+  <si>
     <t>Verified in Database</t>
   </si>
   <si>
@@ -2053,88 +2191,22 @@
     <t>Added for transfers</t>
   </si>
   <si>
-    <t>Shahbaz Umar Jalal Bhandara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shahbaz Bhandara </t>
-  </si>
-  <si>
-    <t>Jaya Surya Sukhavasi</t>
-  </si>
-  <si>
-    <t>Jaya Sukhavasi</t>
-  </si>
-  <si>
-    <t>Harish Rayi</t>
-  </si>
-  <si>
-    <t>Venkataharish Rayi</t>
-  </si>
-  <si>
-    <t>Kavyadeep Bhamra</t>
-  </si>
-  <si>
-    <t>Kavyadeep Singh</t>
-  </si>
-  <si>
-    <t>Josh McClune</t>
-  </si>
-  <si>
-    <t>Joshua McClune</t>
-  </si>
-  <si>
-    <t>Fergus Emmett</t>
-  </si>
-  <si>
-    <t>Frgus Emmett</t>
-  </si>
-  <si>
-    <t>Izzy Jones</t>
-  </si>
-  <si>
-    <t>Susie McCollum</t>
-  </si>
-  <si>
-    <t>Abbie Gunning</t>
-  </si>
-  <si>
-    <t>Aimee Logan</t>
-  </si>
-  <si>
-    <t>Alex Atkinson</t>
-  </si>
-  <si>
-    <t>Ellie Murray</t>
-  </si>
-  <si>
-    <t>Vismithaa Pandiaraj</t>
-  </si>
-  <si>
-    <t>Ellen Murray</t>
-  </si>
-  <si>
-    <t>Isabelle Jones</t>
-  </si>
-  <si>
-    <t>Susanna McCollum</t>
-  </si>
-  <si>
-    <t>Abigail Gunning</t>
-  </si>
-  <si>
-    <t>Aimeee Logan</t>
-  </si>
-  <si>
-    <t>Alexandra Atkinson</t>
-  </si>
-  <si>
-    <t>Vismithaa Sai Pandiaraj</t>
-  </si>
-  <si>
-    <t>Johnny Shannon</t>
-  </si>
-  <si>
-    <t>Jonny Shannon</t>
+    <t>Added as per Wylie request (Sport80 typo fix)</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Generational suffix)</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Transliteration fix)</t>
+  </si>
+  <si>
+    <t>Added as per Wylie request (Apostrophe character fix)</t>
+  </si>
+  <si>
+    <t>Sport80 payment typo (truncated surname)</t>
+  </si>
+  <si>
+    <t>Sport80 payment typo (k/h keyboard slip)</t>
   </si>
 </sst>
 </file>
@@ -2476,13 +2548,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D362"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2504,13 +2576,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="C2" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D2" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -2518,13 +2590,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="C3" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D3" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2532,13 +2604,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D4" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2546,13 +2618,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C5" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D5" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2560,13 +2632,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="C6" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D6" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2574,13 +2646,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C7" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D7" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2588,13 +2660,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C8" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D8" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2602,13 +2674,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="C9" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D9" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2616,13 +2688,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C10" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D10" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2630,13 +2702,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D11" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -2644,13 +2716,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C12" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D12" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -2658,13 +2730,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C13" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D13" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2672,13 +2744,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="C14" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D14" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2686,13 +2758,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C15" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D15" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2700,13 +2772,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C16" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D16" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2714,13 +2786,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C17" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D17" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,13 +2800,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C18" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D18" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2742,13 +2814,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C19" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D19" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2756,13 +2828,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C20" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D20" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2770,13 +2842,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="C21" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D21" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2784,13 +2856,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C22" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D22" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2798,13 +2870,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C23" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D23" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2812,13 +2884,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C24" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D24" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2826,13 +2898,13 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C25" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D25" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2840,13 +2912,13 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D26" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2854,13 +2926,13 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C27" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D27" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2868,13 +2940,13 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="C28" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D28" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2882,13 +2954,13 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="C29" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D29" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2896,13 +2968,13 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C30" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D30" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2910,13 +2982,13 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C31" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D31" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2924,13 +2996,13 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C32" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D32" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2938,13 +3010,13 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="C33" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D33" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2952,13 +3024,13 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C34" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D34" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2966,13 +3038,13 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="C35" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D35" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2980,13 +3052,13 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C36" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D36" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2994,13 +3066,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C37" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D37" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -3008,13 +3080,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C38" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D38" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3022,13 +3094,13 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="C39" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D39" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -3036,13 +3108,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C40" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D40" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -3050,13 +3122,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C41" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D41" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -3064,13 +3136,13 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="C42" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D42" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -3078,13 +3150,13 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D43" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -3092,13 +3164,13 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="C44" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D44" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -3106,13 +3178,13 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C45" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D45" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -3120,13 +3192,13 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C46" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D46" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -3134,13 +3206,13 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="C47" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D47" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -3148,13 +3220,13 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C48" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D48" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -3162,13 +3234,13 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C49" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D49" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -3176,13 +3248,13 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="C50" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D50" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3190,13 +3262,13 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="C51" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D51" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3204,13 +3276,13 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C52" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D52" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3218,13 +3290,13 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="C53" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D53" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3232,13 +3304,13 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="C54" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D54" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3246,13 +3318,13 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="C55" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D55" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3260,13 +3332,13 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C56" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D56" t="s">
-        <v>673</v>
+        <v>719</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3274,13 +3346,13 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="C57" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D57" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3288,13 +3360,13 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C58" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D58" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3302,13 +3374,13 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="C59" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D59" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3316,13 +3388,13 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="C60" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D60" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3330,13 +3402,13 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C61" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D61" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3344,13 +3416,13 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C62" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D62" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3358,13 +3430,13 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="C63" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D63" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3372,13 +3444,13 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C64" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D64" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3386,13 +3458,13 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="C65" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D65" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3400,13 +3472,13 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C66" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D66" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3414,13 +3486,13 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C67" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D67" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3428,13 +3500,13 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C68" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D68" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3442,13 +3514,13 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C69" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D69" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3456,13 +3528,13 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C70" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D70" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3470,13 +3542,13 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="C71" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D71" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3484,13 +3556,13 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="C72" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D72" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3498,13 +3570,13 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="C73" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D73" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3512,13 +3584,13 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="C74" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D74" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3526,13 +3598,13 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="C75" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D75" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3540,13 +3612,13 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="C76" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D76" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3554,13 +3626,13 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="C77" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D77" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3568,13 +3640,13 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C78" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D78" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3585,10 +3657,10 @@
         <v>81</v>
       </c>
       <c r="C79" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D79" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3599,10 +3671,10 @@
         <v>80</v>
       </c>
       <c r="C80" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D80" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3610,13 +3682,13 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="C81" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D81" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3624,13 +3696,13 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C82" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D82" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3638,13 +3710,13 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="C83" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D83" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3652,13 +3724,13 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="C84" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D84" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3666,13 +3738,13 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="C85" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D85" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3680,13 +3752,13 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="C86" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D86" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3694,13 +3766,13 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="C87" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D87" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3708,13 +3780,13 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="C88" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D88" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3722,13 +3794,13 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C89" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D89" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3736,13 +3808,13 @@
         <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C90" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D90" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3750,13 +3822,13 @@
         <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="C91" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D91" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3764,13 +3836,13 @@
         <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="C92" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D92" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3778,13 +3850,13 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="C93" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D93" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3792,13 +3864,13 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="C94" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D94" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3806,13 +3878,13 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="C95" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D95" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3820,13 +3892,13 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="C96" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D96" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3834,13 +3906,13 @@
         <v>97</v>
       </c>
       <c r="B97" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="C97" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D97" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3848,13 +3920,13 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="C98" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D98" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -3862,13 +3934,13 @@
         <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="C99" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D99" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3876,13 +3948,13 @@
         <v>100</v>
       </c>
       <c r="B100" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="C100" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D100" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -3890,13 +3962,13 @@
         <v>101</v>
       </c>
       <c r="B101" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="C101" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D101" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3904,13 +3976,13 @@
         <v>102</v>
       </c>
       <c r="B102" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="C102" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D102" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -3918,13 +3990,13 @@
         <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="C103" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D103" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -3932,13 +4004,13 @@
         <v>104</v>
       </c>
       <c r="B104" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="C104" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D104" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -3946,13 +4018,13 @@
         <v>105</v>
       </c>
       <c r="B105" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="C105" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D105" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3960,13 +4032,13 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C106" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D106" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -3974,13 +4046,13 @@
         <v>107</v>
       </c>
       <c r="B107" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C107" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D107" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -3988,13 +4060,13 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C108" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D108" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -4002,13 +4074,13 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="C109" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D109" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -4016,13 +4088,13 @@
         <v>110</v>
       </c>
       <c r="B110" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="C110" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D110" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -4030,13 +4102,13 @@
         <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="C111" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D111" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -4044,13 +4116,13 @@
         <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="C112" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D112" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -4058,13 +4130,13 @@
         <v>113</v>
       </c>
       <c r="B113" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="C113" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D113" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -4072,13 +4144,13 @@
         <v>114</v>
       </c>
       <c r="B114" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="C114" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D114" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -4086,13 +4158,13 @@
         <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="C115" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D115" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -4100,13 +4172,13 @@
         <v>116</v>
       </c>
       <c r="B116" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="C116" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D116" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -4114,13 +4186,13 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="C117" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D117" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -4128,13 +4200,13 @@
         <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="C118" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D118" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -4142,13 +4214,13 @@
         <v>119</v>
       </c>
       <c r="B119" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="C119" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D119" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -4156,13 +4228,13 @@
         <v>120</v>
       </c>
       <c r="B120" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="C120" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D120" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -4170,13 +4242,13 @@
         <v>121</v>
       </c>
       <c r="B121" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="C121" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D121" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -4184,13 +4256,13 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="C122" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D122" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -4198,13 +4270,13 @@
         <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="C123" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D123" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -4215,10 +4287,10 @@
         <v>131</v>
       </c>
       <c r="C124" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D124" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -4226,13 +4298,13 @@
         <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="C125" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D125" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -4240,13 +4312,13 @@
         <v>126</v>
       </c>
       <c r="B126" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="C126" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D126" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -4254,13 +4326,13 @@
         <v>127</v>
       </c>
       <c r="B127" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="C127" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D127" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -4268,13 +4340,13 @@
         <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="C128" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D128" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -4282,13 +4354,13 @@
         <v>129</v>
       </c>
       <c r="B129" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="C129" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D129" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -4296,13 +4368,13 @@
         <v>130</v>
       </c>
       <c r="B130" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="C130" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D130" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -4310,13 +4382,13 @@
         <v>131</v>
       </c>
       <c r="B131" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="C131" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D131" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -4324,13 +4396,13 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="C132" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D132" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -4338,13 +4410,13 @@
         <v>133</v>
       </c>
       <c r="B133" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="C133" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D133" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -4352,13 +4424,13 @@
         <v>134</v>
       </c>
       <c r="B134" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="C134" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D134" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -4366,13 +4438,13 @@
         <v>135</v>
       </c>
       <c r="B135" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="C135" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D135" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -4380,13 +4452,13 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="C136" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D136" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -4394,13 +4466,13 @@
         <v>137</v>
       </c>
       <c r="B137" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="C137" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D137" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -4408,13 +4480,13 @@
         <v>138</v>
       </c>
       <c r="B138" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="C138" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D138" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -4422,13 +4494,13 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="C139" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D139" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
@@ -4436,13 +4508,13 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="C140" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D140" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -4450,13 +4522,13 @@
         <v>141</v>
       </c>
       <c r="B141" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="C141" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D141" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
@@ -4464,13 +4536,13 @@
         <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="C142" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D142" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -4478,13 +4550,13 @@
         <v>143</v>
       </c>
       <c r="B143" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="C143" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D143" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -4492,13 +4564,13 @@
         <v>144</v>
       </c>
       <c r="B144" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
       <c r="C144" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D144" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -4506,13 +4578,13 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="C145" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D145" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -4520,13 +4592,13 @@
         <v>146</v>
       </c>
       <c r="B146" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="C146" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D146" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -4534,13 +4606,13 @@
         <v>147</v>
       </c>
       <c r="B147" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="C147" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D147" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
@@ -4548,13 +4620,13 @@
         <v>148</v>
       </c>
       <c r="B148" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="C148" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D148" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -4562,13 +4634,13 @@
         <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
       <c r="C149" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D149" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -4576,13 +4648,13 @@
         <v>150</v>
       </c>
       <c r="B150" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="C150" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D150" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -4590,13 +4662,13 @@
         <v>151</v>
       </c>
       <c r="B151" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="C151" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D151" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -4604,13 +4676,13 @@
         <v>152</v>
       </c>
       <c r="B152" t="s">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="C152" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D152" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -4618,13 +4690,13 @@
         <v>153</v>
       </c>
       <c r="B153" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="C153" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D153" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -4632,13 +4704,13 @@
         <v>154</v>
       </c>
       <c r="B154" t="s">
-        <v>487</v>
+        <v>511</v>
       </c>
       <c r="C154" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D154" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -4646,13 +4718,13 @@
         <v>155</v>
       </c>
       <c r="B155" t="s">
-        <v>488</v>
+        <v>512</v>
       </c>
       <c r="C155" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D155" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -4660,13 +4732,13 @@
         <v>156</v>
       </c>
       <c r="B156" t="s">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="C156" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D156" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -4674,13 +4746,13 @@
         <v>157</v>
       </c>
       <c r="B157" t="s">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="C157" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D157" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -4688,13 +4760,13 @@
         <v>158</v>
       </c>
       <c r="B158" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="C158" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D158" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -4702,13 +4774,13 @@
         <v>159</v>
       </c>
       <c r="B159" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="C159" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D159" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -4716,13 +4788,13 @@
         <v>160</v>
       </c>
       <c r="B160" t="s">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="C160" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D160" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -4730,13 +4802,13 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
       <c r="C161" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D161" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
@@ -4744,13 +4816,13 @@
         <v>162</v>
       </c>
       <c r="B162" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
       <c r="C162" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D162" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -4758,13 +4830,13 @@
         <v>163</v>
       </c>
       <c r="B163" t="s">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="C163" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D163" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -4772,13 +4844,13 @@
         <v>164</v>
       </c>
       <c r="B164" t="s">
-        <v>497</v>
+        <v>521</v>
       </c>
       <c r="C164" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D164" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -4786,13 +4858,13 @@
         <v>165</v>
       </c>
       <c r="B165" t="s">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="C165" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D165" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -4800,13 +4872,13 @@
         <v>166</v>
       </c>
       <c r="B166" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="C166" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D166" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -4817,10 +4889,10 @@
         <v>167</v>
       </c>
       <c r="C167" t="s">
-        <v>670</v>
+        <v>716</v>
       </c>
       <c r="D167" t="s">
-        <v>674</v>
+        <v>720</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -4828,13 +4900,13 @@
         <v>168</v>
       </c>
       <c r="B168" t="s">
-        <v>500</v>
+        <v>524</v>
       </c>
       <c r="C168" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D168" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -4845,10 +4917,10 @@
         <v>169</v>
       </c>
       <c r="C169" t="s">
-        <v>670</v>
+        <v>716</v>
       </c>
       <c r="D169" t="s">
-        <v>675</v>
+        <v>721</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -4856,13 +4928,13 @@
         <v>170</v>
       </c>
       <c r="B170" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="C170" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D170" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -4870,13 +4942,13 @@
         <v>171</v>
       </c>
       <c r="B171" t="s">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="C171" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D171" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -4884,13 +4956,13 @@
         <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="C172" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D172" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -4898,13 +4970,13 @@
         <v>173</v>
       </c>
       <c r="B173" t="s">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="C173" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D173" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -4912,13 +4984,13 @@
         <v>174</v>
       </c>
       <c r="B174" t="s">
-        <v>505</v>
+        <v>529</v>
       </c>
       <c r="C174" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D174" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -4926,13 +4998,13 @@
         <v>175</v>
       </c>
       <c r="B175" t="s">
-        <v>506</v>
+        <v>530</v>
       </c>
       <c r="C175" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D175" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -4940,13 +5012,13 @@
         <v>176</v>
       </c>
       <c r="B176" t="s">
-        <v>507</v>
+        <v>531</v>
       </c>
       <c r="C176" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D176" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -4954,13 +5026,13 @@
         <v>177</v>
       </c>
       <c r="B177" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="C177" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D177" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -4968,13 +5040,13 @@
         <v>178</v>
       </c>
       <c r="B178" t="s">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="C178" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D178" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -4982,13 +5054,13 @@
         <v>179</v>
       </c>
       <c r="B179" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="C179" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D179" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -4996,13 +5068,13 @@
         <v>180</v>
       </c>
       <c r="B180" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="C180" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D180" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -5010,13 +5082,13 @@
         <v>181</v>
       </c>
       <c r="B181" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="C181" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D181" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -5024,13 +5096,13 @@
         <v>182</v>
       </c>
       <c r="B182" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="C182" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D182" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -5038,13 +5110,13 @@
         <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="C183" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D183" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -5052,13 +5124,13 @@
         <v>184</v>
       </c>
       <c r="B184" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="C184" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D184" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -5066,13 +5138,13 @@
         <v>185</v>
       </c>
       <c r="B185" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="C185" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D185" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -5080,13 +5152,13 @@
         <v>186</v>
       </c>
       <c r="B186" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="C186" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D186" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -5094,13 +5166,13 @@
         <v>187</v>
       </c>
       <c r="B187" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="C187" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D187" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -5108,13 +5180,13 @@
         <v>188</v>
       </c>
       <c r="B188" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="C188" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D188" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -5122,13 +5194,13 @@
         <v>189</v>
       </c>
       <c r="B189" t="s">
-        <v>519</v>
+        <v>543</v>
       </c>
       <c r="C189" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D189" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -5136,13 +5208,13 @@
         <v>190</v>
       </c>
       <c r="B190" t="s">
-        <v>520</v>
+        <v>544</v>
       </c>
       <c r="C190" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D190" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -5150,13 +5222,13 @@
         <v>191</v>
       </c>
       <c r="B191" t="s">
-        <v>521</v>
+        <v>545</v>
       </c>
       <c r="C191" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D191" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -5164,13 +5236,13 @@
         <v>192</v>
       </c>
       <c r="B192" t="s">
-        <v>522</v>
+        <v>546</v>
       </c>
       <c r="C192" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D192" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -5178,13 +5250,13 @@
         <v>193</v>
       </c>
       <c r="B193" t="s">
-        <v>523</v>
+        <v>547</v>
       </c>
       <c r="C193" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D193" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -5192,13 +5264,13 @@
         <v>194</v>
       </c>
       <c r="B194" t="s">
-        <v>524</v>
+        <v>548</v>
       </c>
       <c r="C194" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D194" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -5206,13 +5278,13 @@
         <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="C195" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D195" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -5220,13 +5292,13 @@
         <v>196</v>
       </c>
       <c r="B196" t="s">
-        <v>526</v>
+        <v>550</v>
       </c>
       <c r="C196" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D196" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -5234,13 +5306,13 @@
         <v>197</v>
       </c>
       <c r="B197" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="C197" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D197" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -5248,13 +5320,13 @@
         <v>198</v>
       </c>
       <c r="B198" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="C198" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D198" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -5262,13 +5334,13 @@
         <v>199</v>
       </c>
       <c r="B199" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="C199" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D199" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -5276,13 +5348,13 @@
         <v>200</v>
       </c>
       <c r="B200" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="C200" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D200" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
@@ -5290,13 +5362,13 @@
         <v>201</v>
       </c>
       <c r="B201" t="s">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="C201" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D201" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -5307,10 +5379,10 @@
         <v>202</v>
       </c>
       <c r="C202" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D202" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -5318,13 +5390,13 @@
         <v>203</v>
       </c>
       <c r="B203" t="s">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C203" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D203" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -5332,13 +5404,13 @@
         <v>204</v>
       </c>
       <c r="B204" t="s">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C204" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D204" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -5346,13 +5418,13 @@
         <v>205</v>
       </c>
       <c r="B205" t="s">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="C205" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D205" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -5360,13 +5432,13 @@
         <v>206</v>
       </c>
       <c r="B206" t="s">
-        <v>535</v>
+        <v>559</v>
       </c>
       <c r="C206" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D206" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -5374,13 +5446,13 @@
         <v>207</v>
       </c>
       <c r="B207" t="s">
-        <v>536</v>
+        <v>560</v>
       </c>
       <c r="C207" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D207" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -5388,13 +5460,13 @@
         <v>208</v>
       </c>
       <c r="B208" t="s">
-        <v>537</v>
+        <v>561</v>
       </c>
       <c r="C208" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D208" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -5402,13 +5474,13 @@
         <v>209</v>
       </c>
       <c r="B209" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
       <c r="C209" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D209" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -5416,13 +5488,13 @@
         <v>210</v>
       </c>
       <c r="B210" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="C210" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D210" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -5430,13 +5502,13 @@
         <v>211</v>
       </c>
       <c r="B211" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="C211" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D211" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -5444,13 +5516,13 @@
         <v>212</v>
       </c>
       <c r="B212" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="C212" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D212" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -5458,13 +5530,13 @@
         <v>213</v>
       </c>
       <c r="B213" t="s">
-        <v>542</v>
+        <v>566</v>
       </c>
       <c r="C213" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D213" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -5472,13 +5544,13 @@
         <v>214</v>
       </c>
       <c r="B214" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="C214" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D214" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -5486,13 +5558,13 @@
         <v>215</v>
       </c>
       <c r="B215" t="s">
-        <v>543</v>
+        <v>567</v>
       </c>
       <c r="C215" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D215" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -5500,13 +5572,13 @@
         <v>216</v>
       </c>
       <c r="B216" t="s">
-        <v>544</v>
+        <v>568</v>
       </c>
       <c r="C216" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D216" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -5514,13 +5586,13 @@
         <v>217</v>
       </c>
       <c r="B217" t="s">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="C217" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D217" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -5528,13 +5600,13 @@
         <v>218</v>
       </c>
       <c r="B218" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="C218" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D218" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -5542,13 +5614,13 @@
         <v>219</v>
       </c>
       <c r="B219" t="s">
-        <v>547</v>
+        <v>571</v>
       </c>
       <c r="C219" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D219" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -5556,13 +5628,13 @@
         <v>220</v>
       </c>
       <c r="B220" t="s">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="C220" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D220" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -5570,13 +5642,13 @@
         <v>221</v>
       </c>
       <c r="B221" t="s">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="C221" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D221" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -5584,13 +5656,13 @@
         <v>222</v>
       </c>
       <c r="B222" t="s">
-        <v>550</v>
+        <v>574</v>
       </c>
       <c r="C222" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D222" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -5598,13 +5670,13 @@
         <v>223</v>
       </c>
       <c r="B223" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="C223" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D223" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -5612,13 +5684,13 @@
         <v>224</v>
       </c>
       <c r="B224" t="s">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="C224" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D224" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -5626,13 +5698,13 @@
         <v>225</v>
       </c>
       <c r="B225" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="C225" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D225" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -5640,13 +5712,13 @@
         <v>226</v>
       </c>
       <c r="B226" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="C226" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D226" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -5654,13 +5726,13 @@
         <v>227</v>
       </c>
       <c r="B227" t="s">
-        <v>555</v>
+        <v>579</v>
       </c>
       <c r="C227" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D227" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -5668,13 +5740,13 @@
         <v>228</v>
       </c>
       <c r="B228" t="s">
-        <v>556</v>
+        <v>580</v>
       </c>
       <c r="C228" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D228" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -5682,13 +5754,13 @@
         <v>229</v>
       </c>
       <c r="B229" t="s">
-        <v>557</v>
+        <v>581</v>
       </c>
       <c r="C229" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D229" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -5696,13 +5768,13 @@
         <v>230</v>
       </c>
       <c r="B230" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="C230" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D230" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -5710,13 +5782,13 @@
         <v>231</v>
       </c>
       <c r="B231" t="s">
-        <v>559</v>
+        <v>583</v>
       </c>
       <c r="C231" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D231" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -5724,13 +5796,13 @@
         <v>232</v>
       </c>
       <c r="B232" t="s">
-        <v>560</v>
+        <v>584</v>
       </c>
       <c r="C232" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D232" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -5738,13 +5810,13 @@
         <v>233</v>
       </c>
       <c r="B233" t="s">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="C233" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D233" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -5752,13 +5824,13 @@
         <v>234</v>
       </c>
       <c r="B234" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="C234" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D234" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -5766,13 +5838,13 @@
         <v>235</v>
       </c>
       <c r="B235" t="s">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="C235" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D235" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -5780,13 +5852,13 @@
         <v>236</v>
       </c>
       <c r="B236" t="s">
-        <v>564</v>
+        <v>588</v>
       </c>
       <c r="C236" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D236" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -5794,13 +5866,13 @@
         <v>237</v>
       </c>
       <c r="B237" t="s">
-        <v>565</v>
+        <v>589</v>
       </c>
       <c r="C237" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D237" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -5808,13 +5880,13 @@
         <v>238</v>
       </c>
       <c r="B238" t="s">
-        <v>566</v>
+        <v>590</v>
       </c>
       <c r="C238" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D238" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -5822,13 +5894,13 @@
         <v>239</v>
       </c>
       <c r="B239" t="s">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="C239" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D239" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -5836,13 +5908,13 @@
         <v>240</v>
       </c>
       <c r="B240" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="C240" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D240" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
@@ -5850,13 +5922,13 @@
         <v>241</v>
       </c>
       <c r="B241" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="C241" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D241" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
@@ -5864,13 +5936,13 @@
         <v>242</v>
       </c>
       <c r="B242" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="C242" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D242" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -5878,13 +5950,13 @@
         <v>243</v>
       </c>
       <c r="B243" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="C243" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D243" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -5892,13 +5964,13 @@
         <v>244</v>
       </c>
       <c r="B244" t="s">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="C244" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D244" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -5906,13 +5978,13 @@
         <v>245</v>
       </c>
       <c r="B245" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="C245" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D245" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -5920,13 +5992,13 @@
         <v>246</v>
       </c>
       <c r="B246" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="C246" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D246" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -5934,13 +6006,13 @@
         <v>247</v>
       </c>
       <c r="B247" t="s">
-        <v>508</v>
+        <v>532</v>
       </c>
       <c r="C247" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D247" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
@@ -5948,13 +6020,13 @@
         <v>248</v>
       </c>
       <c r="B248" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C248" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D248" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -5962,13 +6034,13 @@
         <v>249</v>
       </c>
       <c r="B249" t="s">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="C249" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D249" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -5976,13 +6048,13 @@
         <v>250</v>
       </c>
       <c r="B250" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="C250" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D250" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -5990,13 +6062,13 @@
         <v>251</v>
       </c>
       <c r="B251" t="s">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="C251" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D251" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -6004,13 +6076,13 @@
         <v>252</v>
       </c>
       <c r="B252" t="s">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="C252" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D252" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -6018,13 +6090,13 @@
         <v>253</v>
       </c>
       <c r="B253" t="s">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="C253" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D253" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -6032,13 +6104,13 @@
         <v>254</v>
       </c>
       <c r="B254" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="C254" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D254" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -6046,13 +6118,13 @@
         <v>255</v>
       </c>
       <c r="B255" t="s">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="C255" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D255" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -6060,13 +6132,13 @@
         <v>256</v>
       </c>
       <c r="B256" t="s">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="C256" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D256" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -6074,13 +6146,13 @@
         <v>257</v>
       </c>
       <c r="B257" t="s">
-        <v>584</v>
+        <v>608</v>
       </c>
       <c r="C257" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D257" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -6088,13 +6160,13 @@
         <v>258</v>
       </c>
       <c r="B258" t="s">
-        <v>585</v>
+        <v>609</v>
       </c>
       <c r="C258" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D258" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -6102,13 +6174,13 @@
         <v>259</v>
       </c>
       <c r="B259" t="s">
-        <v>586</v>
+        <v>610</v>
       </c>
       <c r="C259" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D259" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -6116,13 +6188,13 @@
         <v>260</v>
       </c>
       <c r="B260" t="s">
-        <v>587</v>
+        <v>611</v>
       </c>
       <c r="C260" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D260" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
@@ -6130,13 +6202,13 @@
         <v>261</v>
       </c>
       <c r="B261" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="C261" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D261" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
@@ -6144,13 +6216,13 @@
         <v>262</v>
       </c>
       <c r="B262" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="C262" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D262" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -6158,13 +6230,13 @@
         <v>263</v>
       </c>
       <c r="B263" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="C263" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D263" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -6172,13 +6244,13 @@
         <v>264</v>
       </c>
       <c r="B264" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="C264" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D264" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -6186,13 +6258,13 @@
         <v>265</v>
       </c>
       <c r="B265" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="C265" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D265" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -6200,13 +6272,13 @@
         <v>266</v>
       </c>
       <c r="B266" t="s">
-        <v>592</v>
+        <v>616</v>
       </c>
       <c r="C266" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D266" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -6214,13 +6286,13 @@
         <v>267</v>
       </c>
       <c r="B267" t="s">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="C267" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D267" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -6228,13 +6300,13 @@
         <v>268</v>
       </c>
       <c r="B268" t="s">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="C268" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D268" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -6242,13 +6314,13 @@
         <v>269</v>
       </c>
       <c r="B269" t="s">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="C269" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D269" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -6256,13 +6328,13 @@
         <v>270</v>
       </c>
       <c r="B270" t="s">
-        <v>595</v>
+        <v>619</v>
       </c>
       <c r="C270" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D270" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -6270,13 +6342,13 @@
         <v>271</v>
       </c>
       <c r="B271" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="C271" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D271" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -6284,13 +6356,13 @@
         <v>272</v>
       </c>
       <c r="B272" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="C272" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D272" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -6298,13 +6370,13 @@
         <v>273</v>
       </c>
       <c r="B273" t="s">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="C273" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D273" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -6312,13 +6384,13 @@
         <v>274</v>
       </c>
       <c r="B274" t="s">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="C274" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D274" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -6326,13 +6398,13 @@
         <v>275</v>
       </c>
       <c r="B275" t="s">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="C275" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D275" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -6340,13 +6412,13 @@
         <v>276</v>
       </c>
       <c r="B276" t="s">
-        <v>599</v>
+        <v>623</v>
       </c>
       <c r="C276" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D276" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -6354,13 +6426,13 @@
         <v>277</v>
       </c>
       <c r="B277" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="C277" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D277" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -6368,13 +6440,13 @@
         <v>278</v>
       </c>
       <c r="B278" t="s">
-        <v>600</v>
+        <v>624</v>
       </c>
       <c r="C278" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D278" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -6382,13 +6454,13 @@
         <v>279</v>
       </c>
       <c r="B279" t="s">
-        <v>601</v>
+        <v>625</v>
       </c>
       <c r="C279" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D279" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -6396,13 +6468,13 @@
         <v>280</v>
       </c>
       <c r="B280" t="s">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="C280" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D280" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
@@ -6410,13 +6482,13 @@
         <v>281</v>
       </c>
       <c r="B281" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="C281" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D281" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
@@ -6424,13 +6496,13 @@
         <v>282</v>
       </c>
       <c r="B282" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
       <c r="C282" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D282" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -6438,13 +6510,13 @@
         <v>283</v>
       </c>
       <c r="B283" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="C283" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D283" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -6452,13 +6524,13 @@
         <v>284</v>
       </c>
       <c r="B284" t="s">
-        <v>606</v>
+        <v>630</v>
       </c>
       <c r="C284" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D284" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -6466,13 +6538,13 @@
         <v>285</v>
       </c>
       <c r="B285" t="s">
-        <v>607</v>
+        <v>631</v>
       </c>
       <c r="C285" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D285" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -6480,13 +6552,13 @@
         <v>286</v>
       </c>
       <c r="B286" t="s">
-        <v>608</v>
+        <v>632</v>
       </c>
       <c r="C286" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D286" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -6494,13 +6566,13 @@
         <v>287</v>
       </c>
       <c r="B287" t="s">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="C287" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D287" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -6508,13 +6580,13 @@
         <v>288</v>
       </c>
       <c r="B288" t="s">
-        <v>610</v>
+        <v>634</v>
       </c>
       <c r="C288" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D288" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -6522,13 +6594,13 @@
         <v>289</v>
       </c>
       <c r="B289" t="s">
-        <v>611</v>
+        <v>635</v>
       </c>
       <c r="C289" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D289" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -6536,13 +6608,13 @@
         <v>290</v>
       </c>
       <c r="B290" t="s">
-        <v>612</v>
+        <v>636</v>
       </c>
       <c r="C290" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D290" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -6550,13 +6622,13 @@
         <v>291</v>
       </c>
       <c r="B291" t="s">
-        <v>613</v>
+        <v>637</v>
       </c>
       <c r="C291" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D291" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -6564,13 +6636,13 @@
         <v>292</v>
       </c>
       <c r="B292" t="s">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="C292" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D292" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -6578,13 +6650,13 @@
         <v>293</v>
       </c>
       <c r="B293" t="s">
-        <v>615</v>
+        <v>639</v>
       </c>
       <c r="C293" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D293" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -6592,13 +6664,13 @@
         <v>294</v>
       </c>
       <c r="B294" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="C294" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D294" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -6606,13 +6678,13 @@
         <v>295</v>
       </c>
       <c r="B295" t="s">
-        <v>617</v>
+        <v>641</v>
       </c>
       <c r="C295" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D295" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -6620,13 +6692,13 @@
         <v>296</v>
       </c>
       <c r="B296" t="s">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="C296" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D296" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -6634,13 +6706,13 @@
         <v>297</v>
       </c>
       <c r="B297" t="s">
-        <v>619</v>
+        <v>643</v>
       </c>
       <c r="C297" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D297" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -6648,13 +6720,13 @@
         <v>298</v>
       </c>
       <c r="B298" t="s">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="C298" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D298" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -6662,13 +6734,13 @@
         <v>299</v>
       </c>
       <c r="B299" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C299" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D299" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -6676,13 +6748,13 @@
         <v>300</v>
       </c>
       <c r="B300" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="C300" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D300" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -6690,13 +6762,13 @@
         <v>301</v>
       </c>
       <c r="B301" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C301" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D301" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -6704,13 +6776,13 @@
         <v>302</v>
       </c>
       <c r="B302" t="s">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="C302" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D302" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -6718,13 +6790,13 @@
         <v>303</v>
       </c>
       <c r="B303" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="C303" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D303" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -6732,13 +6804,13 @@
         <v>304</v>
       </c>
       <c r="B304" t="s">
-        <v>625</v>
+        <v>649</v>
       </c>
       <c r="C304" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D304" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -6746,13 +6818,13 @@
         <v>305</v>
       </c>
       <c r="B305" t="s">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="C305" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D305" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,13 +6832,13 @@
         <v>306</v>
       </c>
       <c r="B306" t="s">
-        <v>627</v>
+        <v>651</v>
       </c>
       <c r="C306" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D306" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,13 +6846,13 @@
         <v>307</v>
       </c>
       <c r="B307" t="s">
-        <v>628</v>
+        <v>652</v>
       </c>
       <c r="C307" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D307" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,13 +6860,13 @@
         <v>308</v>
       </c>
       <c r="B308" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="C308" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D308" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,13 +6874,13 @@
         <v>309</v>
       </c>
       <c r="B309" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="C309" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D309" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -6816,13 +6888,13 @@
         <v>310</v>
       </c>
       <c r="B310" t="s">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="C310" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D310" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -6830,13 +6902,13 @@
         <v>311</v>
       </c>
       <c r="B311" t="s">
-        <v>632</v>
+        <v>656</v>
       </c>
       <c r="C311" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D311" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -6844,13 +6916,13 @@
         <v>312</v>
       </c>
       <c r="B312" t="s">
-        <v>633</v>
+        <v>657</v>
       </c>
       <c r="C312" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D312" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -6858,13 +6930,13 @@
         <v>313</v>
       </c>
       <c r="B313" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="C313" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D313" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -6872,13 +6944,13 @@
         <v>314</v>
       </c>
       <c r="B314" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="C314" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D314" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -6886,13 +6958,13 @@
         <v>315</v>
       </c>
       <c r="B315" t="s">
-        <v>636</v>
+        <v>660</v>
       </c>
       <c r="C315" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D315" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -6900,13 +6972,13 @@
         <v>316</v>
       </c>
       <c r="B316" t="s">
-        <v>637</v>
+        <v>661</v>
       </c>
       <c r="C316" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D316" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -6914,13 +6986,13 @@
         <v>317</v>
       </c>
       <c r="B317" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="C317" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D317" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -6928,13 +7000,13 @@
         <v>318</v>
       </c>
       <c r="B318" t="s">
-        <v>638</v>
+        <v>662</v>
       </c>
       <c r="C318" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D318" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -6942,13 +7014,13 @@
         <v>319</v>
       </c>
       <c r="B319" t="s">
-        <v>639</v>
+        <v>663</v>
       </c>
       <c r="C319" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D319" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -6956,13 +7028,13 @@
         <v>320</v>
       </c>
       <c r="B320" t="s">
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="C320" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D320" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
@@ -6970,13 +7042,13 @@
         <v>321</v>
       </c>
       <c r="B321" t="s">
-        <v>641</v>
+        <v>665</v>
       </c>
       <c r="C321" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D321" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
@@ -6984,13 +7056,13 @@
         <v>322</v>
       </c>
       <c r="B322" t="s">
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="C322" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D322" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -6998,13 +7070,13 @@
         <v>323</v>
       </c>
       <c r="B323" t="s">
-        <v>643</v>
+        <v>667</v>
       </c>
       <c r="C323" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D323" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -7012,13 +7084,13 @@
         <v>324</v>
       </c>
       <c r="B324" t="s">
-        <v>644</v>
+        <v>668</v>
       </c>
       <c r="C324" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D324" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -7026,13 +7098,13 @@
         <v>325</v>
       </c>
       <c r="B325" t="s">
-        <v>645</v>
+        <v>669</v>
       </c>
       <c r="C325" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D325" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -7040,13 +7112,13 @@
         <v>326</v>
       </c>
       <c r="B326" t="s">
-        <v>646</v>
+        <v>670</v>
       </c>
       <c r="C326" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D326" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -7054,13 +7126,13 @@
         <v>327</v>
       </c>
       <c r="B327" t="s">
-        <v>647</v>
+        <v>671</v>
       </c>
       <c r="C327" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D327" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -7068,13 +7140,13 @@
         <v>328</v>
       </c>
       <c r="B328" t="s">
-        <v>648</v>
+        <v>672</v>
       </c>
       <c r="C328" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D328" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -7082,13 +7154,13 @@
         <v>329</v>
       </c>
       <c r="B329" t="s">
-        <v>649</v>
+        <v>673</v>
       </c>
       <c r="C329" t="s">
-        <v>669</v>
+        <v>715</v>
       </c>
       <c r="D329" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -7096,13 +7168,13 @@
         <v>330</v>
       </c>
       <c r="B330" t="s">
-        <v>650</v>
+        <v>674</v>
       </c>
       <c r="C330" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D330" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -7110,13 +7182,13 @@
         <v>331</v>
       </c>
       <c r="B331" t="s">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="C331" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D331" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -7124,13 +7196,13 @@
         <v>332</v>
       </c>
       <c r="B332" t="s">
-        <v>652</v>
+        <v>676</v>
       </c>
       <c r="C332" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D332" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -7138,13 +7210,13 @@
         <v>333</v>
       </c>
       <c r="B333" t="s">
-        <v>653</v>
+        <v>677</v>
       </c>
       <c r="C333" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D333" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -7152,13 +7224,13 @@
         <v>334</v>
       </c>
       <c r="B334" t="s">
-        <v>654</v>
+        <v>678</v>
       </c>
       <c r="C334" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D334" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -7166,13 +7238,13 @@
         <v>335</v>
       </c>
       <c r="B335" t="s">
-        <v>655</v>
+        <v>679</v>
       </c>
       <c r="C335" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D335" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -7180,13 +7252,13 @@
         <v>336</v>
       </c>
       <c r="B336" t="s">
-        <v>656</v>
+        <v>680</v>
       </c>
       <c r="C336" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D336" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -7194,13 +7266,13 @@
         <v>337</v>
       </c>
       <c r="B337" t="s">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="C337" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D337" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -7208,13 +7280,13 @@
         <v>338</v>
       </c>
       <c r="B338" t="s">
-        <v>658</v>
+        <v>682</v>
       </c>
       <c r="C338" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D338" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -7222,13 +7294,13 @@
         <v>339</v>
       </c>
       <c r="B339" t="s">
-        <v>659</v>
+        <v>683</v>
       </c>
       <c r="C339" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D339" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -7236,13 +7308,13 @@
         <v>340</v>
       </c>
       <c r="B340" t="s">
-        <v>660</v>
+        <v>684</v>
       </c>
       <c r="C340" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D340" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
@@ -7250,13 +7322,13 @@
         <v>341</v>
       </c>
       <c r="B341" t="s">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="C341" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D341" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
@@ -7264,13 +7336,13 @@
         <v>342</v>
       </c>
       <c r="B342" t="s">
-        <v>662</v>
+        <v>686</v>
       </c>
       <c r="C342" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D342" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -7278,13 +7350,13 @@
         <v>343</v>
       </c>
       <c r="B343" t="s">
-        <v>663</v>
+        <v>687</v>
       </c>
       <c r="C343" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D343" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -7292,13 +7364,13 @@
         <v>103</v>
       </c>
       <c r="B344" t="s">
-        <v>664</v>
+        <v>688</v>
       </c>
       <c r="C344" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="D344" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -7306,13 +7378,13 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>665</v>
+        <v>689</v>
       </c>
       <c r="C345" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="D345" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -7320,13 +7392,13 @@
         <v>299</v>
       </c>
       <c r="B346" t="s">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="C346" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="D346" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -7334,13 +7406,13 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>666</v>
+        <v>690</v>
       </c>
       <c r="C347" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="D347" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -7348,209 +7420,349 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>667</v>
+        <v>691</v>
       </c>
       <c r="C348" t="s">
-        <v>671</v>
+        <v>717</v>
       </c>
       <c r="D348" t="s">
-        <v>676</v>
+        <v>722</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>678</v>
+        <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="C349" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D349" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>680</v>
+        <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="C350" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D350" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>682</v>
+        <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="C351" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D351" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>684</v>
+        <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="C352" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D352" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>685</v>
+        <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>686</v>
+        <v>696</v>
       </c>
       <c r="C353" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D353" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>687</v>
+        <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
       <c r="C354" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D354" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>689</v>
+        <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C355" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D355" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>690</v>
+        <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C356" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D356" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>691</v>
+        <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C357" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D357" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>692</v>
+        <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C358" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D358" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>693</v>
+        <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C359" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D359" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>694</v>
+        <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="C360" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D360" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>695</v>
+        <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C361" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D361" t="s">
-        <v>672</v>
+        <v>718</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>703</v>
+        <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C362" t="s">
-        <v>668</v>
+        <v>714</v>
       </c>
       <c r="D362" t="s">
-        <v>672</v>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>361</v>
+      </c>
+      <c r="B363" t="s">
+        <v>706</v>
+      </c>
+      <c r="C363" t="s">
+        <v>714</v>
+      </c>
+      <c r="D363" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>362</v>
+      </c>
+      <c r="B364" t="s">
+        <v>707</v>
+      </c>
+      <c r="C364" t="s">
+        <v>714</v>
+      </c>
+      <c r="D364" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>363</v>
+      </c>
+      <c r="B365" t="s">
+        <v>708</v>
+      </c>
+      <c r="C365" t="s">
+        <v>714</v>
+      </c>
+      <c r="D365" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>364</v>
+      </c>
+      <c r="B366" t="s">
+        <v>709</v>
+      </c>
+      <c r="C366" t="s">
+        <v>714</v>
+      </c>
+      <c r="D366" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>365</v>
+      </c>
+      <c r="B367" t="s">
+        <v>710</v>
+      </c>
+      <c r="C367" t="s">
+        <v>714</v>
+      </c>
+      <c r="D367" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>366</v>
+      </c>
+      <c r="B368" t="s">
+        <v>710</v>
+      </c>
+      <c r="C368" t="s">
+        <v>714</v>
+      </c>
+      <c r="D368" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>367</v>
+      </c>
+      <c r="B369" t="s">
+        <v>655</v>
+      </c>
+      <c r="C369" t="s">
+        <v>714</v>
+      </c>
+      <c r="D369" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>368</v>
+      </c>
+      <c r="B370" t="s">
+        <v>711</v>
+      </c>
+      <c r="C370" t="s">
+        <v>714</v>
+      </c>
+      <c r="D370" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>369</v>
+      </c>
+      <c r="B371" t="s">
+        <v>712</v>
+      </c>
+      <c r="C371" t="s">
+        <v>714</v>
+      </c>
+      <c r="D371" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>370</v>
+      </c>
+      <c r="B372" t="s">
+        <v>713</v>
+      </c>
+      <c r="C372" t="s">
+        <v>714</v>
+      </c>
+      <c r="D372" t="s">
+        <v>728</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCACACB-5E67-44AA-AE4F-F1295E049449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1493" uniqueCount="733">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="727">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -1120,12 +1126,6 @@
     <t>Thomas Vidamour</t>
   </si>
   <si>
-    <t>Jack Kirkpatrick jnr</t>
-  </si>
-  <si>
-    <t>Jack Kirkpatrick snr</t>
-  </si>
-  <si>
     <t>Tony Louis Pathipally</t>
   </si>
   <si>
@@ -1138,9 +1138,6 @@
     <t>Akaah Vega</t>
   </si>
   <si>
-    <t>Sam McConnell</t>
-  </si>
-  <si>
     <t>Avi Swaroop</t>
   </si>
   <si>
@@ -2155,9 +2152,6 @@
     <t>Vhomas Tidamour</t>
   </si>
   <si>
-    <t>Jack Kirkpatrick</t>
-  </si>
-  <si>
     <t>Henry O’Neill</t>
   </si>
   <si>
@@ -2167,9 +2161,6 @@
     <t>Akash Vega</t>
   </si>
   <si>
-    <t>Samuel McConnell</t>
-  </si>
-  <si>
     <t>Verified in Database</t>
   </si>
   <si>
@@ -2198,9 +2189,6 @@
   </si>
   <si>
     <t>Added as per Wylie request (Sport80 typo fix)</t>
-  </si>
-  <si>
-    <t>Added as per Wylie request (Generational suffix)</t>
   </si>
   <si>
     <t>Added as per Wylie request (Transliteration fix)</t>
@@ -2218,8 +2206,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2256,13 +2244,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2300,7 +2296,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2334,6 +2330,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2368,9 +2365,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2543,11 +2541,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G373"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G370"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2570,1085 +2577,1085 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D2" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C3" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D3" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C4" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D4" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D5" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C6" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D6" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C7" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D7" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C8" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D8" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C9" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C10" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D10" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D11" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C12" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D12" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C13" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D13" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C14" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D14" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C15" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D15" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C16" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D16" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C17" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D17" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C18" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D18" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C19" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D19" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C20" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D20" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C21" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D21" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C22" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D22" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C23" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D23" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C24" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D24" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C25" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D25" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C26" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D26" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C27" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D27" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D28" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C29" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D29" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C30" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D30" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C31" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D31" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C32" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D32" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C33" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D33" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C34" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D34" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C35" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D35" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C36" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D36" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C37" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D37" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C38" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D38" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C39" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D39" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C40" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D40" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C41" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D41" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C42" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D42" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D43" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C44" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D44" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D45" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C46" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D46" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C47" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D47" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C48" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D48" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C49" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D49" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C50" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D50" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C51" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D51" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C52" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D52" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C53" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D53" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C54" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D54" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C55" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D55" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C56" t="s">
+        <v>713</v>
+      </c>
+      <c r="D56" t="s">
         <v>718</v>
       </c>
-      <c r="D56" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C57" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D57" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C58" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D58" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C59" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D59" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C60" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D60" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C61" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D61" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C62" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D62" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C63" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D63" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C64" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D64" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C65" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D65" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C66" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D66" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C67" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D67" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C68" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D68" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C69" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D69" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C70" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D70" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C71" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D71" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C72" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D72" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C73" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D73" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C74" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D74" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C75" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D75" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C76" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D76" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C77" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D77" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C78" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D78" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -3656,13 +3663,13 @@
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D79" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -3670,615 +3677,615 @@
         <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D80" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C81" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D81" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C82" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D82" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C83" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D83" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C84" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D84" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C85" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D85" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C86" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D86" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C87" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D87" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C88" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D88" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C89" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D89" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C90" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D90" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C91" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D91" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C92" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D92" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C93" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D93" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C94" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D94" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C95" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D95" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C96" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D96" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C97" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D97" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C98" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D98" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C99" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D99" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C100" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D100" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C101" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D101" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C102" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D102" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C103" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D103" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C104" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D104" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C105" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D105" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C106" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D106" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C107" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D107" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C108" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D108" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C109" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D109" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C110" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D110" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C111" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D111" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C112" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D112" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C113" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D113" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C114" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D114" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C115" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D115" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C116" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D116" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C117" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D117" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C118" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D118" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C119" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D119" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C120" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D120" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C121" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D121" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C122" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D122" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C123" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D123" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -4286,601 +4293,601 @@
         <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D124" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C125" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D125" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C126" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D126" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C127" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D127" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C128" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D128" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C129" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D129" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C130" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D130" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C131" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D131" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C132" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D132" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C133" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D133" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C134" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D134" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C135" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D135" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C136" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D136" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C137" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D137" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C138" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D138" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C139" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D139" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C140" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D140" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C141" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D141" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C142" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D142" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>146</v>
       </c>
       <c r="B143" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C143" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D143" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>147</v>
       </c>
       <c r="B144" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C144" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D144" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>148</v>
       </c>
       <c r="B145" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C145" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D145" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C146" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D146" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>150</v>
       </c>
       <c r="B147" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C147" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D147" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>151</v>
       </c>
       <c r="B148" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C148" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D148" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>152</v>
       </c>
       <c r="B149" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C149" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D149" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C150" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D150" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>154</v>
       </c>
       <c r="B151" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C151" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D151" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C152" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D152" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>156</v>
       </c>
       <c r="B153" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C153" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D153" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>157</v>
       </c>
       <c r="B154" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C154" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D154" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>158</v>
       </c>
       <c r="B155" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C155" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D155" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>159</v>
       </c>
       <c r="B156" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C156" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D156" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>160</v>
       </c>
       <c r="B157" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C157" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D157" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>161</v>
       </c>
       <c r="B158" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C158" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D158" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>162</v>
       </c>
       <c r="B159" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C159" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D159" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>163</v>
       </c>
       <c r="B160" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C160" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D160" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C161" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D161" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C162" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D162" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>166</v>
       </c>
       <c r="B163" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C163" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D163" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>167</v>
       </c>
       <c r="B164" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C164" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D164" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>168</v>
       </c>
       <c r="B165" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C165" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D165" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C166" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D166" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -4888,27 +4895,27 @@
         <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="D167" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>171</v>
       </c>
       <c r="B168" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C168" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D168" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -4916,461 +4923,461 @@
         <v>172</v>
       </c>
       <c r="C169" t="s">
+        <v>715</v>
+      </c>
+      <c r="D169" t="s">
         <v>720</v>
       </c>
-      <c r="D169" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>173</v>
       </c>
       <c r="B170" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C170" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D170" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>174</v>
       </c>
       <c r="B171" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C171" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D171" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C172" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D172" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>176</v>
       </c>
       <c r="B173" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C173" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D173" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>177</v>
       </c>
       <c r="B174" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C174" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D174" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>178</v>
       </c>
       <c r="B175" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C175" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D175" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>179</v>
       </c>
       <c r="B176" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C176" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D176" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>180</v>
       </c>
       <c r="B177" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C177" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D177" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>181</v>
       </c>
       <c r="B178" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C178" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D178" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>182</v>
       </c>
       <c r="B179" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C179" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D179" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C180" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D180" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>184</v>
       </c>
       <c r="B181" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C181" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D181" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>185</v>
       </c>
       <c r="B182" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C182" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D182" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>186</v>
       </c>
       <c r="B183" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C183" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D183" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>187</v>
       </c>
       <c r="B184" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C184" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D184" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>188</v>
       </c>
       <c r="B185" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C185" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D185" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>189</v>
       </c>
       <c r="B186" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C186" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D186" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>190</v>
       </c>
       <c r="B187" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C187" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D187" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>191</v>
       </c>
       <c r="B188" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C188" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D188" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C189" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D189" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>193</v>
       </c>
       <c r="B190" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C190" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D190" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C191" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D191" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>195</v>
       </c>
       <c r="B192" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C192" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D192" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C193" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D193" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C194" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D194" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>198</v>
       </c>
       <c r="B195" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C195" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D195" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C196" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D196" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>200</v>
       </c>
       <c r="B197" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C197" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D197" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C198" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D198" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C199" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D199" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>203</v>
       </c>
       <c r="B200" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C200" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D200" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C201" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D201" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -5378,1287 +5385,1287 @@
         <v>205</v>
       </c>
       <c r="C202" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D202" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>206</v>
       </c>
       <c r="B203" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C203" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D203" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>207</v>
       </c>
       <c r="B204" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C204" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D204" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>208</v>
       </c>
       <c r="B205" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C205" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D205" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C206" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D206" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>210</v>
       </c>
       <c r="B207" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C207" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D207" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>211</v>
       </c>
       <c r="B208" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C208" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D208" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>212</v>
       </c>
       <c r="B209" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C209" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D209" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>213</v>
       </c>
       <c r="B210" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C210" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D210" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>214</v>
       </c>
       <c r="B211" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C211" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D211" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>215</v>
       </c>
       <c r="B212" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C212" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D212" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>216</v>
       </c>
       <c r="B213" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C213" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D213" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>217</v>
       </c>
       <c r="B214" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C214" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D214" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C215" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D215" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>219</v>
       </c>
       <c r="B216" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C216" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D216" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>220</v>
       </c>
       <c r="B217" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C217" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D217" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>221</v>
       </c>
       <c r="B218" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C218" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D218" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>222</v>
       </c>
       <c r="B219" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C219" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D219" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>223</v>
       </c>
       <c r="B220" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C220" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D220" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>224</v>
       </c>
       <c r="B221" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C221" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D221" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>225</v>
       </c>
       <c r="B222" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C222" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D222" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>226</v>
       </c>
       <c r="B223" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C223" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D223" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C224" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D224" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C225" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D225" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>229</v>
       </c>
       <c r="B226" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C226" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D226" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>230</v>
       </c>
       <c r="B227" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C227" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D227" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>231</v>
       </c>
       <c r="B228" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C228" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D228" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C229" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D229" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>233</v>
       </c>
       <c r="B230" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C230" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D230" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C231" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D231" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C232" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D232" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C233" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D233" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>237</v>
       </c>
       <c r="B234" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C234" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D234" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>238</v>
       </c>
       <c r="B235" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C235" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D235" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>239</v>
       </c>
       <c r="B236" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C236" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D236" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>240</v>
       </c>
       <c r="B237" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C237" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D237" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>241</v>
       </c>
       <c r="B238" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C238" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D238" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>242</v>
       </c>
       <c r="B239" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C239" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D239" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>243</v>
       </c>
       <c r="B240" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C240" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D240" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>244</v>
       </c>
       <c r="B241" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C241" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D241" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>245</v>
       </c>
       <c r="B242" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C242" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D242" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>246</v>
       </c>
       <c r="B243" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C243" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D243" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>247</v>
       </c>
       <c r="B244" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C244" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D244" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>248</v>
       </c>
       <c r="B245" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C245" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D245" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>249</v>
       </c>
       <c r="B246" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C246" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D246" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>250</v>
       </c>
       <c r="B247" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C247" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D247" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>251</v>
       </c>
       <c r="B248" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C248" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D248" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>252</v>
       </c>
       <c r="B249" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C249" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D249" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>253</v>
       </c>
       <c r="B250" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C250" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D250" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>254</v>
       </c>
       <c r="B251" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C251" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D251" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>255</v>
       </c>
       <c r="B252" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C252" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D252" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>256</v>
       </c>
       <c r="B253" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C253" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D253" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>257</v>
       </c>
       <c r="B254" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C254" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D254" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>258</v>
       </c>
       <c r="B255" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C255" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D255" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>259</v>
       </c>
       <c r="B256" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C256" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D256" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>260</v>
       </c>
       <c r="B257" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C257" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D257" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>261</v>
       </c>
       <c r="B258" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C258" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D258" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>262</v>
       </c>
       <c r="B259" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C259" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D259" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>263</v>
       </c>
       <c r="B260" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C260" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D260" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>264</v>
       </c>
       <c r="B261" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C261" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D261" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>265</v>
       </c>
       <c r="B262" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C262" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D262" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>266</v>
       </c>
       <c r="B263" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C263" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D263" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>267</v>
       </c>
       <c r="B264" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C264" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D264" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>268</v>
       </c>
       <c r="B265" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C265" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D265" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>269</v>
       </c>
       <c r="B266" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C266" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D266" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>270</v>
       </c>
       <c r="B267" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C267" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D267" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>271</v>
       </c>
       <c r="B268" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C268" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D268" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>272</v>
       </c>
       <c r="B269" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C269" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D269" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>273</v>
       </c>
       <c r="B270" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C270" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D270" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>274</v>
       </c>
       <c r="B271" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C271" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D271" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>275</v>
       </c>
       <c r="B272" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C272" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D272" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>276</v>
       </c>
       <c r="B273" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C273" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D273" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>277</v>
       </c>
       <c r="B274" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C274" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D274" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>278</v>
       </c>
       <c r="B275" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C275" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D275" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>279</v>
       </c>
       <c r="B276" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C276" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D276" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>280</v>
       </c>
       <c r="B277" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C277" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D277" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>281</v>
       </c>
       <c r="B278" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C278" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D278" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>282</v>
       </c>
       <c r="B279" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C279" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D279" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>283</v>
       </c>
       <c r="B280" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C280" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D280" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C281" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D281" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>285</v>
       </c>
       <c r="B282" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C282" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D282" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>286</v>
       </c>
       <c r="B283" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C283" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D283" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>287</v>
       </c>
       <c r="B284" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C284" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D284" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>288</v>
       </c>
       <c r="B285" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C285" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D285" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>289</v>
       </c>
       <c r="B286" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C286" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D286" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C287" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D287" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>291</v>
       </c>
       <c r="B288" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C288" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D288" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>292</v>
       </c>
       <c r="B289" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C289" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D289" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>293</v>
       </c>
       <c r="B290" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C290" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D290" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>294</v>
       </c>
       <c r="B291" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C291" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D291" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>295</v>
       </c>
       <c r="B292" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C292" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D292" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>296</v>
       </c>
       <c r="B293" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C293" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D293" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>297</v>
       </c>
@@ -6666,1110 +6673,1074 @@
         <v>297</v>
       </c>
       <c r="C294" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D294" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>298</v>
       </c>
       <c r="B295" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C295" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D295" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>299</v>
       </c>
       <c r="B296" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C296" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D296" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>300</v>
       </c>
       <c r="B297" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C297" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D297" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>301</v>
       </c>
       <c r="B298" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C298" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D298" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>302</v>
       </c>
       <c r="B299" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C299" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D299" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>303</v>
       </c>
       <c r="B300" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C300" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D300" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>304</v>
       </c>
       <c r="B301" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C301" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D301" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>305</v>
       </c>
       <c r="B302" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C302" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D302" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>306</v>
       </c>
       <c r="B303" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C303" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D303" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>307</v>
       </c>
       <c r="B304" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C304" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D304" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>308</v>
       </c>
       <c r="B305" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C305" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D305" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>309</v>
       </c>
       <c r="B306" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C306" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D306" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>310</v>
       </c>
       <c r="B307" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C307" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D307" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>311</v>
       </c>
       <c r="B308" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C308" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D308" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>312</v>
       </c>
       <c r="B309" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C309" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D309" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>313</v>
       </c>
       <c r="B310" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C310" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D310" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>314</v>
       </c>
       <c r="B311" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C311" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D311" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>315</v>
       </c>
       <c r="B312" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C312" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D312" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>316</v>
       </c>
       <c r="B313" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C313" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D313" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>317</v>
       </c>
       <c r="B314" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C314" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D314" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>318</v>
       </c>
       <c r="B315" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C315" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D315" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>319</v>
       </c>
       <c r="B316" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C316" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D316" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>320</v>
       </c>
       <c r="B317" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C317" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D317" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>321</v>
       </c>
       <c r="B318" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C318" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D318" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>322</v>
       </c>
       <c r="B319" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C319" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D319" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>323</v>
       </c>
       <c r="B320" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C320" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D320" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>324</v>
       </c>
       <c r="B321" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C321" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D321" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>325</v>
       </c>
       <c r="B322" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C322" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D322" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>326</v>
       </c>
       <c r="B323" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C323" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D323" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>327</v>
       </c>
       <c r="B324" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C324" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D324" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>328</v>
       </c>
       <c r="B325" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C325" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D325" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>329</v>
       </c>
       <c r="B326" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C326" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D326" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>330</v>
       </c>
       <c r="B327" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C327" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D327" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>331</v>
       </c>
       <c r="B328" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C328" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D328" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>332</v>
       </c>
       <c r="B329" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C329" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="D329" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>333</v>
       </c>
       <c r="B330" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C330" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D330" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>334</v>
       </c>
       <c r="B331" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C331" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D331" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>335</v>
       </c>
       <c r="B332" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C332" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D332" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>336</v>
       </c>
       <c r="B333" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C333" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D333" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>337</v>
       </c>
       <c r="B334" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C334" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D334" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>338</v>
       </c>
       <c r="B335" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C335" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D335" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>339</v>
       </c>
       <c r="B336" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C336" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D336" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>340</v>
       </c>
       <c r="B337" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C337" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D337" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>341</v>
       </c>
       <c r="B338" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C338" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D338" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>342</v>
       </c>
       <c r="B339" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C339" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D339" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>343</v>
       </c>
       <c r="B340" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C340" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D340" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>344</v>
       </c>
       <c r="B341" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C341" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D341" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>345</v>
       </c>
       <c r="B342" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C342" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D342" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>346</v>
       </c>
       <c r="B343" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C343" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D343" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>106</v>
       </c>
       <c r="B344" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C344" t="s">
+        <v>716</v>
+      </c>
+      <c r="D344" t="s">
         <v>721</v>
       </c>
-      <c r="D344" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>347</v>
       </c>
       <c r="B345" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C345" t="s">
+        <v>716</v>
+      </c>
+      <c r="D345" t="s">
         <v>721</v>
       </c>
-      <c r="D345" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4">
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>302</v>
       </c>
       <c r="B346" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C346" t="s">
+        <v>716</v>
+      </c>
+      <c r="D346" t="s">
         <v>721</v>
       </c>
-      <c r="D346" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4">
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>348</v>
       </c>
       <c r="B347" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C347" t="s">
+        <v>716</v>
+      </c>
+      <c r="D347" t="s">
         <v>721</v>
       </c>
-      <c r="D347" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>349</v>
       </c>
       <c r="B348" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C348" t="s">
+        <v>716</v>
+      </c>
+      <c r="D348" t="s">
         <v>721</v>
       </c>
-      <c r="D348" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4">
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>350</v>
       </c>
       <c r="B349" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C349" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D349" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>351</v>
       </c>
       <c r="B350" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C350" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D350" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>352</v>
       </c>
       <c r="B351" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C351" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D351" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>353</v>
       </c>
       <c r="B352" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C352" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D352" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>354</v>
       </c>
       <c r="B353" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C353" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D353" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>355</v>
       </c>
       <c r="B354" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C354" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D354" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>356</v>
       </c>
       <c r="B355" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C355" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D355" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>357</v>
       </c>
       <c r="B356" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C356" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D356" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>358</v>
       </c>
       <c r="B357" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C357" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D357" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>359</v>
       </c>
       <c r="B358" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C358" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D358" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>360</v>
       </c>
       <c r="B359" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C359" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D359" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>361</v>
       </c>
       <c r="B360" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C360" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D360" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>362</v>
       </c>
       <c r="B361" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C361" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D361" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>363</v>
       </c>
       <c r="B362" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C362" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D362" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>364</v>
       </c>
       <c r="B363" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C363" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D363" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>365</v>
       </c>
       <c r="B364" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C364" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D364" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>366</v>
       </c>
       <c r="B365" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C365" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D365" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>367</v>
       </c>
       <c r="B366" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C366" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D366" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>368</v>
       </c>
       <c r="B367" t="s">
-        <v>713</v>
+        <v>655</v>
       </c>
       <c r="C367" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D367" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>369</v>
       </c>
       <c r="B368" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C368" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D368" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>370</v>
       </c>
       <c r="B369" t="s">
-        <v>658</v>
+        <v>711</v>
       </c>
       <c r="C369" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D369" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>371</v>
       </c>
       <c r="B370" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C370" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D370" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4">
-      <c r="A371" t="s">
-        <v>372</v>
-      </c>
-      <c r="B371" t="s">
-        <v>715</v>
-      </c>
-      <c r="C371" t="s">
-        <v>718</v>
-      </c>
-      <c r="D371" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4">
-      <c r="A372" t="s">
-        <v>373</v>
-      </c>
-      <c r="B372" t="s">
-        <v>716</v>
-      </c>
-      <c r="C372" t="s">
-        <v>718</v>
-      </c>
-      <c r="D372" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4">
-      <c r="A373" t="s">
-        <v>374</v>
-      </c>
-      <c r="B373" t="s">
-        <v>717</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCACACB-5E67-44AA-AE4F-F1295E049449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E794E725-0835-4893-97B8-3EDDFC28A898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10740" yWindow="810" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="729">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2201,6 +2201,12 @@
   </si>
   <si>
     <t>Sport80 payment typo (k/h keyboard slip)</t>
+  </si>
+  <si>
+    <t>Sandeep Ganesh Srinivasan</t>
+  </si>
+  <si>
+    <t>Sandeep Srinivasan</t>
   </si>
 </sst>
 </file>
@@ -2542,7 +2548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G371"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -7743,6 +7749,20 @@
         <v>726</v>
       </c>
     </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>727</v>
+      </c>
+      <c r="B371" t="s">
+        <v>728</v>
+      </c>
+      <c r="C371" t="s">
+        <v>713</v>
+      </c>
+      <c r="D371" t="s">
+        <v>717</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E794E725-0835-4893-97B8-3EDDFC28A898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D963D141-C2A8-4C7A-A02A-7923B20F5945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10740" yWindow="810" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7751,10 +7751,10 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>728</v>
+      </c>
+      <c r="B371" t="s">
         <v>727</v>
-      </c>
-      <c r="B371" t="s">
-        <v>728</v>
       </c>
       <c r="C371" t="s">
         <v>713</v>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D963D141-C2A8-4C7A-A02A-7923B20F5945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B46D57-10BE-4604-9299-27A8A99BA4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10740" yWindow="810" windowWidth="25980" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17340" yWindow="2895" windowWidth="33810" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="731">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -2207,6 +2207,12 @@
   </si>
   <si>
     <t>Sandeep Srinivasan</t>
+  </si>
+  <si>
+    <t>James Magee</t>
+  </si>
+  <si>
+    <t>James Magee Snr</t>
   </si>
 </sst>
 </file>
@@ -2548,7 +2554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G371"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -7763,6 +7769,20 @@
         <v>717</v>
       </c>
     </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>729</v>
+      </c>
+      <c r="B372" t="s">
+        <v>730</v>
+      </c>
+      <c r="C372" t="s">
+        <v>713</v>
+      </c>
+      <c r="D372" t="s">
+        <v>717</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B46D57-10BE-4604-9299-27A8A99BA4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17340" yWindow="2895" windowWidth="33810" windowHeight="19590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="729">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -1138,6 +1132,12 @@
     <t>Akaah Vega</t>
   </si>
   <si>
+    <t>Sandeep Srinivasan</t>
+  </si>
+  <si>
+    <t>James Magee</t>
+  </si>
+  <si>
     <t>Avi Swaroop</t>
   </si>
   <si>
@@ -2140,12 +2140,6 @@
     <t>Jonny Shannon</t>
   </si>
   <si>
-    <t>Nathann Mccurry</t>
-  </si>
-  <si>
-    <t>Will Noffkee</t>
-  </si>
-  <si>
     <t>Stephen Entwistle</t>
   </si>
   <si>
@@ -2161,6 +2155,12 @@
     <t>Akash Vega</t>
   </si>
   <si>
+    <t>Sandeep Ganesh Srinivasan</t>
+  </si>
+  <si>
+    <t>James Magee Snr</t>
+  </si>
+  <si>
     <t>Verified in Database</t>
   </si>
   <si>
@@ -2201,25 +2201,13 @@
   </si>
   <si>
     <t>Sport80 payment typo (k/h keyboard slip)</t>
-  </si>
-  <si>
-    <t>Sandeep Ganesh Srinivasan</t>
-  </si>
-  <si>
-    <t>Sandeep Srinivasan</t>
-  </si>
-  <si>
-    <t>James Magee</t>
-  </si>
-  <si>
-    <t>James Magee Snr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2256,21 +2244,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2308,7 +2288,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2342,7 +2322,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2377,10 +2356,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2553,20 +2531,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G372"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2589,1085 +2558,1085 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C4" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D4" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C5" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D6" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C7" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D7" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C8" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D8" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C9" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D9" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C10" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D10" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C11" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D11" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C12" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D12" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C13" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D13" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D14" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C15" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D15" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C16" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D16" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C17" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D17" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C18" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D18" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D19" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C20" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D20" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C21" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D21" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C22" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D22" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C23" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D23" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C24" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D24" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C25" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D25" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C26" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D26" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C27" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D27" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C28" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D28" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C29" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D29" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C30" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D30" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C31" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D31" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C32" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D32" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C33" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D33" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C34" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D34" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C35" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D35" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C36" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D36" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C37" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D37" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C38" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D38" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C39" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D39" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C40" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D40" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C41" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D41" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C42" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D42" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C43" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D43" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C44" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D44" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C45" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D45" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C46" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D46" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C47" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D47" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C48" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D48" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C49" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D49" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C50" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D50" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C51" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D51" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C52" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D52" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C53" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D53" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C54" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D54" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C55" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D55" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C56" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D56" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C57" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D57" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C58" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D58" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C59" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D59" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C60" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D60" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C61" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D61" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C62" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D62" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C63" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D63" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C64" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D64" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C65" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D65" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C66" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D66" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C67" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D67" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C68" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D68" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C69" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D69" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C70" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D70" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C71" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D71" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C72" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D72" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C73" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D73" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C74" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D74" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C75" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D75" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C76" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D76" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C77" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D77" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C78" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D78" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -3675,13 +3644,13 @@
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D79" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -3689,615 +3658,615 @@
         <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D80" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C81" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D81" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C82" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D82" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C83" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D83" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C84" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D84" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C85" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D85" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C86" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D86" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C87" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D87" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C88" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D88" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C89" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D89" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C90" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D90" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C91" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D91" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C92" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D92" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C93" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D93" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C94" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D94" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C95" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D95" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C96" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D96" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C97" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D97" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C98" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D98" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C99" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D99" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C100" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D100" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C101" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D101" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C102" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D102" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C103" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D103" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C104" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D104" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C105" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D105" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C106" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D106" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C107" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D107" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C108" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D108" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C109" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D109" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C110" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D110" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C111" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D111" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C112" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D112" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C113" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D113" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C114" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D114" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C115" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D115" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C116" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D116" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C117" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D117" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C118" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D118" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C119" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D119" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C120" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D120" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C121" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D121" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C122" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D122" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C123" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D123" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -4305,601 +4274,601 @@
         <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D124" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C125" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D125" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C126" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D126" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C127" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D127" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C128" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D128" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C129" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D129" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C130" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D130" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C131" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D131" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C132" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D132" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C133" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D133" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C134" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D134" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C135" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D135" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C136" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D136" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C137" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D137" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C138" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D138" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C139" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D139" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C140" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D140" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C141" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D141" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C142" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D142" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
         <v>146</v>
       </c>
       <c r="B143" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C143" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D143" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
         <v>147</v>
       </c>
       <c r="B144" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C144" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D144" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
         <v>148</v>
       </c>
       <c r="B145" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C145" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D145" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
         <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C146" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D146" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>150</v>
       </c>
       <c r="B147" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C147" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D147" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>151</v>
       </c>
       <c r="B148" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C148" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D148" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>152</v>
       </c>
       <c r="B149" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C149" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D149" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
         <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C150" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D150" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
         <v>154</v>
       </c>
       <c r="B151" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C151" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D151" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C152" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D152" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>156</v>
       </c>
       <c r="B153" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C153" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D153" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
         <v>157</v>
       </c>
       <c r="B154" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C154" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D154" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
         <v>158</v>
       </c>
       <c r="B155" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C155" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D155" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>159</v>
       </c>
       <c r="B156" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C156" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D156" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
         <v>160</v>
       </c>
       <c r="B157" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C157" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D157" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>161</v>
       </c>
       <c r="B158" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C158" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D158" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>162</v>
       </c>
       <c r="B159" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C159" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D159" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
         <v>163</v>
       </c>
       <c r="B160" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C160" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D160" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
         <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C161" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D161" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C162" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D162" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>166</v>
       </c>
       <c r="B163" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C163" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D163" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
         <v>167</v>
       </c>
       <c r="B164" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C164" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D164" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>168</v>
       </c>
       <c r="B165" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C165" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D165" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C166" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D166" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -4907,27 +4876,27 @@
         <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D167" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
       <c r="A168" t="s">
         <v>171</v>
       </c>
       <c r="B168" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C168" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D168" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -4935,461 +4904,461 @@
         <v>172</v>
       </c>
       <c r="C169" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D169" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
       <c r="A170" t="s">
         <v>173</v>
       </c>
       <c r="B170" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C170" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D170" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
       <c r="A171" t="s">
         <v>174</v>
       </c>
       <c r="B171" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C171" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D171" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
       <c r="A172" t="s">
         <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C172" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D172" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173" t="s">
         <v>176</v>
       </c>
       <c r="B173" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C173" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D173" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174" t="s">
         <v>177</v>
       </c>
       <c r="B174" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C174" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D174" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
       <c r="A175" t="s">
         <v>178</v>
       </c>
       <c r="B175" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C175" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D175" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
       <c r="A176" t="s">
         <v>179</v>
       </c>
       <c r="B176" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C176" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D176" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
       <c r="A177" t="s">
         <v>180</v>
       </c>
       <c r="B177" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C177" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D177" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178" t="s">
         <v>181</v>
       </c>
       <c r="B178" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C178" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D178" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
       <c r="A179" t="s">
         <v>182</v>
       </c>
       <c r="B179" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C179" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D179" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
       <c r="A180" t="s">
         <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C180" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D180" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
       <c r="A181" t="s">
         <v>184</v>
       </c>
       <c r="B181" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C181" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D181" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
       <c r="A182" t="s">
         <v>185</v>
       </c>
       <c r="B182" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C182" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D182" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
       <c r="A183" t="s">
         <v>186</v>
       </c>
       <c r="B183" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C183" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D183" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
       <c r="A184" t="s">
         <v>187</v>
       </c>
       <c r="B184" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C184" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D184" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4">
       <c r="A185" t="s">
         <v>188</v>
       </c>
       <c r="B185" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C185" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D185" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186" t="s">
         <v>189</v>
       </c>
       <c r="B186" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C186" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D186" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
       <c r="A187" t="s">
         <v>190</v>
       </c>
       <c r="B187" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C187" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D187" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
       <c r="A188" t="s">
         <v>191</v>
       </c>
       <c r="B188" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C188" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D188" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
       <c r="A189" t="s">
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C189" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D189" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190" t="s">
         <v>193</v>
       </c>
       <c r="B190" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C190" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D190" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4">
       <c r="A191" t="s">
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C191" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D191" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
       <c r="A192" t="s">
         <v>195</v>
       </c>
       <c r="B192" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C192" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D192" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4">
       <c r="A193" t="s">
         <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C193" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D193" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4">
       <c r="A194" t="s">
         <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C194" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D194" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4">
       <c r="A195" t="s">
         <v>198</v>
       </c>
       <c r="B195" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C195" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D195" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4">
       <c r="A196" t="s">
         <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C196" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D196" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4">
       <c r="A197" t="s">
         <v>200</v>
       </c>
       <c r="B197" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C197" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D197" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4">
       <c r="A198" t="s">
         <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C198" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D198" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4">
       <c r="A199" t="s">
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C199" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D199" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4">
       <c r="A200" t="s">
         <v>203</v>
       </c>
       <c r="B200" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C200" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D200" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4">
       <c r="A201" t="s">
         <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C201" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D201" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -5397,1287 +5366,1287 @@
         <v>205</v>
       </c>
       <c r="C202" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D202" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4">
       <c r="A203" t="s">
         <v>206</v>
       </c>
       <c r="B203" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C203" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D203" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4">
       <c r="A204" t="s">
         <v>207</v>
       </c>
       <c r="B204" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C204" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D204" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4">
       <c r="A205" t="s">
         <v>208</v>
       </c>
       <c r="B205" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C205" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D205" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4">
       <c r="A206" t="s">
         <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C206" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D206" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4">
       <c r="A207" t="s">
         <v>210</v>
       </c>
       <c r="B207" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C207" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D207" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
       <c r="A208" t="s">
         <v>211</v>
       </c>
       <c r="B208" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C208" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D208" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
       <c r="A209" t="s">
         <v>212</v>
       </c>
       <c r="B209" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C209" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D209" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210" t="s">
         <v>213</v>
       </c>
       <c r="B210" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C210" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D210" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211" t="s">
         <v>214</v>
       </c>
       <c r="B211" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C211" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D211" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
       <c r="A212" t="s">
         <v>215</v>
       </c>
       <c r="B212" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C212" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D212" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
       <c r="A213" t="s">
         <v>216</v>
       </c>
       <c r="B213" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C213" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D213" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
       <c r="A214" t="s">
         <v>217</v>
       </c>
       <c r="B214" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C214" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D214" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
       <c r="A215" t="s">
         <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C215" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D215" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216" t="s">
         <v>219</v>
       </c>
       <c r="B216" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C216" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D216" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217" t="s">
         <v>220</v>
       </c>
       <c r="B217" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C217" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D217" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218" t="s">
         <v>221</v>
       </c>
       <c r="B218" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C218" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D218" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219" t="s">
         <v>222</v>
       </c>
       <c r="B219" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C219" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D219" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220" t="s">
         <v>223</v>
       </c>
       <c r="B220" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C220" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D220" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
       <c r="A221" t="s">
         <v>224</v>
       </c>
       <c r="B221" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C221" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D221" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
       <c r="A222" t="s">
         <v>225</v>
       </c>
       <c r="B222" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C222" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D222" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223" t="s">
         <v>226</v>
       </c>
       <c r="B223" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C223" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D223" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
       <c r="A224" t="s">
         <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C224" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D224" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225" t="s">
         <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C225" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D225" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226" t="s">
         <v>229</v>
       </c>
       <c r="B226" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C226" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D226" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227" t="s">
         <v>230</v>
       </c>
       <c r="B227" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C227" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D227" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228" t="s">
         <v>231</v>
       </c>
       <c r="B228" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C228" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D228" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229" t="s">
         <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C229" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D229" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230" t="s">
         <v>233</v>
       </c>
       <c r="B230" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C230" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D230" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231" t="s">
         <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C231" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D231" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232" t="s">
         <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C232" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D232" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233" t="s">
         <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C233" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D233" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234" t="s">
         <v>237</v>
       </c>
       <c r="B234" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C234" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D234" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" t="s">
         <v>238</v>
       </c>
       <c r="B235" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C235" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D235" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" t="s">
         <v>239</v>
       </c>
       <c r="B236" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C236" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D236" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" t="s">
         <v>240</v>
       </c>
       <c r="B237" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C237" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D237" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" t="s">
         <v>241</v>
       </c>
       <c r="B238" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C238" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D238" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239" t="s">
         <v>242</v>
       </c>
       <c r="B239" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C239" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D239" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" t="s">
         <v>243</v>
       </c>
       <c r="B240" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C240" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D240" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
       <c r="A241" t="s">
         <v>244</v>
       </c>
       <c r="B241" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C241" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D241" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242" t="s">
         <v>245</v>
       </c>
       <c r="B242" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C242" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D242" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243" t="s">
         <v>246</v>
       </c>
       <c r="B243" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C243" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D243" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
       <c r="A244" t="s">
         <v>247</v>
       </c>
       <c r="B244" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C244" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D244" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245" t="s">
         <v>248</v>
       </c>
       <c r="B245" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C245" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D245" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246" t="s">
         <v>249</v>
       </c>
       <c r="B246" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C246" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D246" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
       <c r="A247" t="s">
         <v>250</v>
       </c>
       <c r="B247" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C247" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D247" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
       <c r="A248" t="s">
         <v>251</v>
       </c>
       <c r="B248" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C248" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D248" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249" t="s">
         <v>252</v>
       </c>
       <c r="B249" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C249" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D249" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
       <c r="A250" t="s">
         <v>253</v>
       </c>
       <c r="B250" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C250" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D250" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251" t="s">
         <v>254</v>
       </c>
       <c r="B251" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C251" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D251" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252" t="s">
         <v>255</v>
       </c>
       <c r="B252" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C252" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D252" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
       <c r="A253" t="s">
         <v>256</v>
       </c>
       <c r="B253" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C253" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D253" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254" t="s">
         <v>257</v>
       </c>
       <c r="B254" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C254" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D254" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255" t="s">
         <v>258</v>
       </c>
       <c r="B255" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C255" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D255" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256" t="s">
         <v>259</v>
       </c>
       <c r="B256" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C256" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D256" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257" t="s">
         <v>260</v>
       </c>
       <c r="B257" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C257" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D257" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" t="s">
         <v>261</v>
       </c>
       <c r="B258" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C258" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D258" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259" t="s">
         <v>262</v>
       </c>
       <c r="B259" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C259" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D259" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260" t="s">
         <v>263</v>
       </c>
       <c r="B260" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C260" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D260" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261" t="s">
         <v>264</v>
       </c>
       <c r="B261" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C261" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D261" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262" t="s">
         <v>265</v>
       </c>
       <c r="B262" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C262" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D262" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263" t="s">
         <v>266</v>
       </c>
       <c r="B263" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C263" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D263" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264" t="s">
         <v>267</v>
       </c>
       <c r="B264" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C264" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D264" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265" t="s">
         <v>268</v>
       </c>
       <c r="B265" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C265" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D265" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266" t="s">
         <v>269</v>
       </c>
       <c r="B266" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C266" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D266" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267" t="s">
         <v>270</v>
       </c>
       <c r="B267" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C267" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D267" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268" t="s">
         <v>271</v>
       </c>
       <c r="B268" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C268" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D268" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269" t="s">
         <v>272</v>
       </c>
       <c r="B269" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C269" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D269" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270" t="s">
         <v>273</v>
       </c>
       <c r="B270" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C270" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D270" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
       <c r="A271" t="s">
         <v>274</v>
       </c>
       <c r="B271" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C271" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D271" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
       <c r="A272" t="s">
         <v>275</v>
       </c>
       <c r="B272" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C272" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D272" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
       <c r="A273" t="s">
         <v>276</v>
       </c>
       <c r="B273" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C273" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D273" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274" t="s">
         <v>277</v>
       </c>
       <c r="B274" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C274" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D274" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" t="s">
         <v>278</v>
       </c>
       <c r="B275" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C275" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D275" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276" t="s">
         <v>279</v>
       </c>
       <c r="B276" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C276" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D276" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" t="s">
         <v>280</v>
       </c>
       <c r="B277" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C277" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D277" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" t="s">
         <v>281</v>
       </c>
       <c r="B278" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C278" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D278" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" t="s">
         <v>282</v>
       </c>
       <c r="B279" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C279" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D279" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280" t="s">
         <v>283</v>
       </c>
       <c r="B280" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C280" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D280" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
       <c r="A281" t="s">
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C281" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D281" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282" t="s">
         <v>285</v>
       </c>
       <c r="B282" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C282" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D282" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283" t="s">
         <v>286</v>
       </c>
       <c r="B283" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C283" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D283" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284" t="s">
         <v>287</v>
       </c>
       <c r="B284" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C284" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D284" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
       <c r="A285" t="s">
         <v>288</v>
       </c>
       <c r="B285" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C285" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D285" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286" t="s">
         <v>289</v>
       </c>
       <c r="B286" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C286" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D286" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287" t="s">
         <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C287" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D287" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
       <c r="A288" t="s">
         <v>291</v>
       </c>
       <c r="B288" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C288" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D288" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
       <c r="A289" t="s">
         <v>292</v>
       </c>
       <c r="B289" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C289" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D289" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290" t="s">
         <v>293</v>
       </c>
       <c r="B290" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C290" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D290" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
       <c r="A291" t="s">
         <v>294</v>
       </c>
       <c r="B291" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C291" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D291" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
       <c r="A292" t="s">
         <v>295</v>
       </c>
       <c r="B292" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C292" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D292" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
       <c r="A293" t="s">
         <v>296</v>
       </c>
       <c r="B293" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C293" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D293" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
       <c r="A294" t="s">
         <v>297</v>
       </c>
@@ -6685,993 +6654,993 @@
         <v>297</v>
       </c>
       <c r="C294" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D294" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
       <c r="A295" t="s">
         <v>298</v>
       </c>
       <c r="B295" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C295" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D295" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
       <c r="A296" t="s">
         <v>299</v>
       </c>
       <c r="B296" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C296" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D296" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297" t="s">
         <v>300</v>
       </c>
       <c r="B297" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C297" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D297" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
       <c r="A298" t="s">
         <v>301</v>
       </c>
       <c r="B298" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C298" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D298" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299" t="s">
         <v>302</v>
       </c>
       <c r="B299" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C299" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D299" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300" t="s">
         <v>303</v>
       </c>
       <c r="B300" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C300" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D300" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301" t="s">
         <v>304</v>
       </c>
       <c r="B301" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C301" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D301" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302" t="s">
         <v>305</v>
       </c>
       <c r="B302" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C302" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D302" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
       <c r="A303" t="s">
         <v>306</v>
       </c>
       <c r="B303" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C303" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D303" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
       <c r="A304" t="s">
         <v>307</v>
       </c>
       <c r="B304" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C304" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D304" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
       <c r="A305" t="s">
         <v>308</v>
       </c>
       <c r="B305" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C305" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D305" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
       <c r="A306" t="s">
         <v>309</v>
       </c>
       <c r="B306" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C306" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D306" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307" t="s">
         <v>310</v>
       </c>
       <c r="B307" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C307" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D307" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308" t="s">
         <v>311</v>
       </c>
       <c r="B308" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C308" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D308" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309" t="s">
         <v>312</v>
       </c>
       <c r="B309" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C309" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D309" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310" t="s">
         <v>313</v>
       </c>
       <c r="B310" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C310" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D310" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311" t="s">
         <v>314</v>
       </c>
       <c r="B311" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C311" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D311" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
       <c r="A312" t="s">
         <v>315</v>
       </c>
       <c r="B312" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C312" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D312" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313" t="s">
         <v>316</v>
       </c>
       <c r="B313" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C313" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D313" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314" t="s">
         <v>317</v>
       </c>
       <c r="B314" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C314" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D314" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315" t="s">
         <v>318</v>
       </c>
       <c r="B315" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C315" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D315" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316" t="s">
         <v>319</v>
       </c>
       <c r="B316" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C316" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D316" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
       <c r="A317" t="s">
         <v>320</v>
       </c>
       <c r="B317" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C317" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D317" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318" t="s">
         <v>321</v>
       </c>
       <c r="B318" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C318" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D318" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319" t="s">
         <v>322</v>
       </c>
       <c r="B319" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C319" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D319" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320" t="s">
         <v>323</v>
       </c>
       <c r="B320" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C320" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D320" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321" t="s">
         <v>324</v>
       </c>
       <c r="B321" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C321" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D321" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322" t="s">
         <v>325</v>
       </c>
       <c r="B322" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C322" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D322" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323" t="s">
         <v>326</v>
       </c>
       <c r="B323" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C323" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D323" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324" t="s">
         <v>327</v>
       </c>
       <c r="B324" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C324" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D324" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325" t="s">
         <v>328</v>
       </c>
       <c r="B325" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C325" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D325" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326" t="s">
         <v>329</v>
       </c>
       <c r="B326" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C326" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D326" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327" t="s">
         <v>330</v>
       </c>
       <c r="B327" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C327" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D327" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
       <c r="A328" t="s">
         <v>331</v>
       </c>
       <c r="B328" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C328" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D328" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
       <c r="A329" t="s">
         <v>332</v>
       </c>
       <c r="B329" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C329" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D329" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330" t="s">
         <v>333</v>
       </c>
       <c r="B330" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C330" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D330" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331" t="s">
         <v>334</v>
       </c>
       <c r="B331" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C331" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D331" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
       <c r="A332" t="s">
         <v>335</v>
       </c>
       <c r="B332" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C332" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D332" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
       <c r="A333" t="s">
         <v>336</v>
       </c>
       <c r="B333" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C333" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D333" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
       <c r="A334" t="s">
         <v>337</v>
       </c>
       <c r="B334" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C334" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D334" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4">
       <c r="A335" t="s">
         <v>338</v>
       </c>
       <c r="B335" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C335" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D335" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336" t="s">
         <v>339</v>
       </c>
       <c r="B336" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C336" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D336" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
       <c r="A337" t="s">
         <v>340</v>
       </c>
       <c r="B337" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C337" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D337" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
       <c r="A338" t="s">
         <v>341</v>
       </c>
       <c r="B338" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C338" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D338" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
       <c r="A339" t="s">
         <v>342</v>
       </c>
       <c r="B339" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C339" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D339" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
       <c r="A340" t="s">
         <v>343</v>
       </c>
       <c r="B340" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C340" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D340" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
       <c r="A341" t="s">
         <v>344</v>
       </c>
       <c r="B341" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C341" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D341" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
       <c r="A342" t="s">
         <v>345</v>
       </c>
       <c r="B342" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C342" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D342" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4">
       <c r="A343" t="s">
         <v>346</v>
       </c>
       <c r="B343" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C343" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D343" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
       <c r="A344" t="s">
         <v>106</v>
       </c>
       <c r="B344" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C344" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D344" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
       <c r="A345" t="s">
         <v>347</v>
       </c>
       <c r="B345" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C345" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D345" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
       <c r="A346" t="s">
         <v>302</v>
       </c>
       <c r="B346" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C346" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D346" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
       <c r="A347" t="s">
         <v>348</v>
       </c>
       <c r="B347" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C347" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D347" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
       <c r="A348" t="s">
         <v>349</v>
       </c>
       <c r="B348" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C348" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D348" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
       <c r="A349" t="s">
         <v>350</v>
       </c>
       <c r="B349" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C349" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D349" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
       <c r="A350" t="s">
         <v>351</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C350" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D350" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
       <c r="A351" t="s">
         <v>352</v>
       </c>
       <c r="B351" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C351" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D351" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
       <c r="A352" t="s">
         <v>353</v>
       </c>
       <c r="B352" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C352" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D352" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4">
       <c r="A353" t="s">
         <v>354</v>
       </c>
       <c r="B353" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C353" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D353" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4">
       <c r="A354" t="s">
         <v>355</v>
       </c>
       <c r="B354" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C354" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D354" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4">
       <c r="A355" t="s">
         <v>356</v>
       </c>
       <c r="B355" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C355" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D355" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4">
       <c r="A356" t="s">
         <v>357</v>
       </c>
       <c r="B356" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C356" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D356" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4">
       <c r="A357" t="s">
         <v>358</v>
       </c>
       <c r="B357" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C357" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D357" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4">
       <c r="A358" t="s">
         <v>359</v>
       </c>
       <c r="B358" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C358" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D358" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4">
       <c r="A359" t="s">
         <v>360</v>
       </c>
       <c r="B359" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C359" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D359" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4">
       <c r="A360" t="s">
         <v>361</v>
       </c>
       <c r="B360" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C360" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D360" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4">
       <c r="A361" t="s">
         <v>362</v>
       </c>
       <c r="B361" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C361" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D361" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4">
       <c r="A362" t="s">
         <v>363</v>
       </c>
       <c r="B362" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C362" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D362" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4">
       <c r="A363" t="s">
         <v>364</v>
       </c>
       <c r="B363" t="s">
-        <v>706</v>
+        <v>364</v>
       </c>
       <c r="C363" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D363" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4">
       <c r="A364" t="s">
         <v>365</v>
       </c>
       <c r="B364" t="s">
-        <v>707</v>
+        <v>365</v>
       </c>
       <c r="C364" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D364" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4">
       <c r="A365" t="s">
         <v>366</v>
       </c>
@@ -7679,13 +7648,13 @@
         <v>708</v>
       </c>
       <c r="C365" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D365" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4">
       <c r="A366" t="s">
         <v>367</v>
       </c>
@@ -7693,27 +7662,27 @@
         <v>709</v>
       </c>
       <c r="C366" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D366" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4">
       <c r="A367" t="s">
         <v>368</v>
       </c>
       <c r="B367" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C367" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D367" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4">
       <c r="A368" t="s">
         <v>369</v>
       </c>
@@ -7721,13 +7690,13 @@
         <v>710</v>
       </c>
       <c r="C368" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D368" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
       <c r="A369" t="s">
         <v>370</v>
       </c>
@@ -7735,13 +7704,13 @@
         <v>711</v>
       </c>
       <c r="C369" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D369" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
       <c r="A370" t="s">
         <v>371</v>
       </c>
@@ -7749,38 +7718,38 @@
         <v>712</v>
       </c>
       <c r="C370" t="s">
+        <v>715</v>
+      </c>
+      <c r="D370" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4">
+      <c r="A371" t="s">
+        <v>372</v>
+      </c>
+      <c r="B371" t="s">
         <v>713</v>
       </c>
-      <c r="D370" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
-        <v>728</v>
-      </c>
-      <c r="B371" t="s">
-        <v>727</v>
-      </c>
       <c r="C371" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D371" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4">
       <c r="A372" t="s">
-        <v>729</v>
+        <v>373</v>
       </c>
       <c r="B372" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="C372" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D372" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="735">
   <si>
     <t>Input Name (Scorecard/Stats)</t>
   </si>
@@ -1138,6 +1138,12 @@
     <t>James Magee</t>
   </si>
   <si>
+    <t>Jack Kirkpatrick jnr</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick snr</t>
+  </si>
+  <si>
     <t>Avi Swaroop</t>
   </si>
   <si>
@@ -2161,6 +2167,12 @@
     <t>James Magee Snr</t>
   </si>
   <si>
+    <t>Jack Kirkpatrick Jnr</t>
+  </si>
+  <si>
+    <t>Jack Kirkpatrick Snr</t>
+  </si>
+  <si>
     <t>Verified in Database</t>
   </si>
   <si>
@@ -2201,6 +2213,12 @@
   </si>
   <si>
     <t>Sport80 payment typo (k/h keyboard slip)</t>
+  </si>
+  <si>
+    <t>Case normalization for Jnr suffix</t>
+  </si>
+  <si>
+    <t>Case normalization for Snr suffix</t>
   </si>
 </sst>
 </file>
@@ -2532,7 +2550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G372"/>
+  <dimension ref="A1:G374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2563,13 +2581,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D2" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2577,13 +2595,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2591,13 +2609,13 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C4" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2605,13 +2623,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2619,13 +2637,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D6" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2633,13 +2651,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D7" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2647,13 +2665,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C8" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D8" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2661,13 +2679,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D9" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2675,13 +2693,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C10" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D10" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2689,13 +2707,13 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C11" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D11" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2703,13 +2721,13 @@
         <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C12" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D12" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2717,13 +2735,13 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D13" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2731,13 +2749,13 @@
         <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C14" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2745,13 +2763,13 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C15" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D15" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2759,13 +2777,13 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C16" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D16" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2773,13 +2791,13 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C17" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D17" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2787,13 +2805,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C18" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D18" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2801,13 +2819,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C19" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D19" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2815,13 +2833,13 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C20" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D20" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2829,13 +2847,13 @@
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C21" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D21" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2843,13 +2861,13 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D22" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2857,13 +2875,13 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C23" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D23" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2871,13 +2889,13 @@
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C24" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D24" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2885,13 +2903,13 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C25" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D25" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2899,13 +2917,13 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C26" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D26" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2913,13 +2931,13 @@
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C27" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D27" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2927,13 +2945,13 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D28" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2941,13 +2959,13 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C29" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D29" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2955,13 +2973,13 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C30" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D30" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2969,13 +2987,13 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C31" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D31" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2983,13 +3001,13 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C32" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D32" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2997,13 +3015,13 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C33" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D33" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3011,13 +3029,13 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C34" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D34" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3025,13 +3043,13 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C35" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D35" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3039,13 +3057,13 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C36" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D36" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3053,13 +3071,13 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C37" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D37" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3067,13 +3085,13 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C38" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D38" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3081,13 +3099,13 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C39" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D39" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3095,13 +3113,13 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C40" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D40" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3109,13 +3127,13 @@
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C41" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D41" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3123,13 +3141,13 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C42" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D42" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3137,13 +3155,13 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C43" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D43" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3151,13 +3169,13 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D44" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3165,13 +3183,13 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D45" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3179,13 +3197,13 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C46" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D46" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3193,13 +3211,13 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C47" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D47" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3207,13 +3225,13 @@
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C48" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D48" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3221,13 +3239,13 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C49" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D49" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3235,13 +3253,13 @@
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C50" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D50" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3249,13 +3267,13 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C51" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D51" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3263,13 +3281,13 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C52" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D52" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3277,13 +3295,13 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C53" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D53" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3291,13 +3309,13 @@
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C54" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D54" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3305,13 +3323,13 @@
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C55" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D55" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3319,13 +3337,13 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C56" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D56" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3333,13 +3351,13 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C57" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D57" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3347,13 +3365,13 @@
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C58" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D58" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3361,13 +3379,13 @@
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C59" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D59" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3375,13 +3393,13 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C60" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D60" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3389,13 +3407,13 @@
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C61" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D61" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3403,13 +3421,13 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C62" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D62" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3417,13 +3435,13 @@
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C63" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D63" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3431,13 +3449,13 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C64" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D64" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3445,13 +3463,13 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C65" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D65" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3459,13 +3477,13 @@
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C66" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D66" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3473,13 +3491,13 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C67" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D67" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3487,13 +3505,13 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C68" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D68" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3501,13 +3519,13 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C69" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D69" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3515,13 +3533,13 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C70" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D70" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3529,13 +3547,13 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C71" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D71" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3543,13 +3561,13 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C72" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D72" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3557,13 +3575,13 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C73" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D73" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3571,13 +3589,13 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C74" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D74" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3585,13 +3603,13 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C75" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D75" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3599,13 +3617,13 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C76" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D76" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3613,13 +3631,13 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C77" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D77" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3627,13 +3645,13 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C78" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D78" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3644,10 +3662,10 @@
         <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D79" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3658,10 +3676,10 @@
         <v>83</v>
       </c>
       <c r="C80" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D80" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3669,13 +3687,13 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C81" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D81" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3683,13 +3701,13 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C82" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D82" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3697,13 +3715,13 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C83" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D83" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3711,13 +3729,13 @@
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C84" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D84" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3725,13 +3743,13 @@
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C85" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D85" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3739,13 +3757,13 @@
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C86" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D86" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3753,13 +3771,13 @@
         <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C87" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D87" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3767,13 +3785,13 @@
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C88" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D88" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3781,13 +3799,13 @@
         <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C89" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D89" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3795,13 +3813,13 @@
         <v>93</v>
       </c>
       <c r="B90" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C90" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D90" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3809,13 +3827,13 @@
         <v>94</v>
       </c>
       <c r="B91" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C91" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D91" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3823,13 +3841,13 @@
         <v>95</v>
       </c>
       <c r="B92" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C92" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D92" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3837,13 +3855,13 @@
         <v>96</v>
       </c>
       <c r="B93" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C93" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D93" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3851,13 +3869,13 @@
         <v>97</v>
       </c>
       <c r="B94" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C94" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D94" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3865,13 +3883,13 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C95" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D95" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3879,13 +3897,13 @@
         <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C96" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D96" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3893,13 +3911,13 @@
         <v>100</v>
       </c>
       <c r="B97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C97" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D97" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3907,13 +3925,13 @@
         <v>101</v>
       </c>
       <c r="B98" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D98" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3921,13 +3939,13 @@
         <v>102</v>
       </c>
       <c r="B99" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C99" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D99" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3935,13 +3953,13 @@
         <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C100" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D100" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3949,13 +3967,13 @@
         <v>104</v>
       </c>
       <c r="B101" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C101" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D101" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3963,13 +3981,13 @@
         <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C102" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D102" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3977,13 +3995,13 @@
         <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C103" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D103" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3991,13 +4009,13 @@
         <v>107</v>
       </c>
       <c r="B104" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C104" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D104" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4005,13 +4023,13 @@
         <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C105" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D105" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4019,13 +4037,13 @@
         <v>109</v>
       </c>
       <c r="B106" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C106" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D106" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4033,13 +4051,13 @@
         <v>110</v>
       </c>
       <c r="B107" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C107" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D107" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4047,13 +4065,13 @@
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C108" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D108" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4061,13 +4079,13 @@
         <v>112</v>
       </c>
       <c r="B109" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C109" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D109" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4075,13 +4093,13 @@
         <v>113</v>
       </c>
       <c r="B110" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C110" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D110" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4089,13 +4107,13 @@
         <v>114</v>
       </c>
       <c r="B111" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C111" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D111" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4103,13 +4121,13 @@
         <v>115</v>
       </c>
       <c r="B112" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C112" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D112" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4117,13 +4135,13 @@
         <v>116</v>
       </c>
       <c r="B113" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C113" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D113" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4131,13 +4149,13 @@
         <v>117</v>
       </c>
       <c r="B114" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C114" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D114" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4145,13 +4163,13 @@
         <v>118</v>
       </c>
       <c r="B115" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C115" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D115" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4159,13 +4177,13 @@
         <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C116" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D116" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4173,13 +4191,13 @@
         <v>120</v>
       </c>
       <c r="B117" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C117" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D117" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4187,13 +4205,13 @@
         <v>121</v>
       </c>
       <c r="B118" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C118" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D118" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4201,13 +4219,13 @@
         <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C119" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D119" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4215,13 +4233,13 @@
         <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C120" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D120" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4229,13 +4247,13 @@
         <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C121" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D121" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4243,13 +4261,13 @@
         <v>125</v>
       </c>
       <c r="B122" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C122" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D122" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4257,13 +4275,13 @@
         <v>126</v>
       </c>
       <c r="B123" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C123" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D123" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4274,10 +4292,10 @@
         <v>134</v>
       </c>
       <c r="C124" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D124" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4285,13 +4303,13 @@
         <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C125" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D125" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4299,13 +4317,13 @@
         <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C126" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D126" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4313,13 +4331,13 @@
         <v>130</v>
       </c>
       <c r="B127" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C127" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D127" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4327,13 +4345,13 @@
         <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C128" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D128" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4341,13 +4359,13 @@
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C129" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D129" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4355,13 +4373,13 @@
         <v>133</v>
       </c>
       <c r="B130" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C130" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D130" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4369,13 +4387,13 @@
         <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C131" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D131" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4383,13 +4401,13 @@
         <v>135</v>
       </c>
       <c r="B132" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C132" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D132" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4397,13 +4415,13 @@
         <v>136</v>
       </c>
       <c r="B133" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C133" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D133" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4411,13 +4429,13 @@
         <v>137</v>
       </c>
       <c r="B134" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C134" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D134" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4425,13 +4443,13 @@
         <v>138</v>
       </c>
       <c r="B135" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C135" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D135" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4439,13 +4457,13 @@
         <v>139</v>
       </c>
       <c r="B136" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C136" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D136" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4453,13 +4471,13 @@
         <v>140</v>
       </c>
       <c r="B137" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C137" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D137" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4467,13 +4485,13 @@
         <v>141</v>
       </c>
       <c r="B138" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C138" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D138" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4481,13 +4499,13 @@
         <v>142</v>
       </c>
       <c r="B139" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C139" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D139" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4495,13 +4513,13 @@
         <v>143</v>
       </c>
       <c r="B140" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C140" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D140" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4509,13 +4527,13 @@
         <v>144</v>
       </c>
       <c r="B141" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C141" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D141" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4523,13 +4541,13 @@
         <v>145</v>
       </c>
       <c r="B142" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C142" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D142" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4537,13 +4555,13 @@
         <v>146</v>
       </c>
       <c r="B143" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C143" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D143" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4551,13 +4569,13 @@
         <v>147</v>
       </c>
       <c r="B144" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C144" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D144" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4565,13 +4583,13 @@
         <v>148</v>
       </c>
       <c r="B145" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C145" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D145" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4579,13 +4597,13 @@
         <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C146" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D146" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4593,13 +4611,13 @@
         <v>150</v>
       </c>
       <c r="B147" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C147" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D147" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4607,13 +4625,13 @@
         <v>151</v>
       </c>
       <c r="B148" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C148" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D148" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4621,13 +4639,13 @@
         <v>152</v>
       </c>
       <c r="B149" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C149" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D149" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4635,13 +4653,13 @@
         <v>153</v>
       </c>
       <c r="B150" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C150" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D150" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4649,13 +4667,13 @@
         <v>154</v>
       </c>
       <c r="B151" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C151" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D151" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4663,13 +4681,13 @@
         <v>155</v>
       </c>
       <c r="B152" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C152" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D152" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4677,13 +4695,13 @@
         <v>156</v>
       </c>
       <c r="B153" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C153" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D153" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4691,13 +4709,13 @@
         <v>157</v>
       </c>
       <c r="B154" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C154" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D154" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4705,13 +4723,13 @@
         <v>158</v>
       </c>
       <c r="B155" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C155" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D155" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4719,13 +4737,13 @@
         <v>159</v>
       </c>
       <c r="B156" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C156" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D156" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4733,13 +4751,13 @@
         <v>160</v>
       </c>
       <c r="B157" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C157" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D157" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4747,13 +4765,13 @@
         <v>161</v>
       </c>
       <c r="B158" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C158" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D158" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4761,13 +4779,13 @@
         <v>162</v>
       </c>
       <c r="B159" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C159" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D159" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4775,13 +4793,13 @@
         <v>163</v>
       </c>
       <c r="B160" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C160" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D160" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4789,13 +4807,13 @@
         <v>164</v>
       </c>
       <c r="B161" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C161" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D161" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4803,13 +4821,13 @@
         <v>165</v>
       </c>
       <c r="B162" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C162" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D162" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4817,13 +4835,13 @@
         <v>166</v>
       </c>
       <c r="B163" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C163" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D163" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4831,13 +4849,13 @@
         <v>167</v>
       </c>
       <c r="B164" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C164" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D164" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4845,13 +4863,13 @@
         <v>168</v>
       </c>
       <c r="B165" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C165" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D165" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4859,13 +4877,13 @@
         <v>169</v>
       </c>
       <c r="B166" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C166" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D166" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4876,10 +4894,10 @@
         <v>170</v>
       </c>
       <c r="C167" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D167" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4887,13 +4905,13 @@
         <v>171</v>
       </c>
       <c r="B168" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C168" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D168" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4904,10 +4922,10 @@
         <v>172</v>
       </c>
       <c r="C169" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D169" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4915,13 +4933,13 @@
         <v>173</v>
       </c>
       <c r="B170" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C170" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D170" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4929,13 +4947,13 @@
         <v>174</v>
       </c>
       <c r="B171" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C171" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D171" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4943,13 +4961,13 @@
         <v>175</v>
       </c>
       <c r="B172" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C172" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D172" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4957,13 +4975,13 @@
         <v>176</v>
       </c>
       <c r="B173" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C173" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D173" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4971,13 +4989,13 @@
         <v>177</v>
       </c>
       <c r="B174" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C174" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D174" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4985,13 +5003,13 @@
         <v>178</v>
       </c>
       <c r="B175" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C175" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D175" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4999,13 +5017,13 @@
         <v>179</v>
       </c>
       <c r="B176" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C176" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D176" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5013,13 +5031,13 @@
         <v>180</v>
       </c>
       <c r="B177" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C177" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D177" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5027,13 +5045,13 @@
         <v>181</v>
       </c>
       <c r="B178" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C178" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D178" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5041,13 +5059,13 @@
         <v>182</v>
       </c>
       <c r="B179" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C179" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D179" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5055,13 +5073,13 @@
         <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C180" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D180" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5069,13 +5087,13 @@
         <v>184</v>
       </c>
       <c r="B181" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C181" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D181" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5083,13 +5101,13 @@
         <v>185</v>
       </c>
       <c r="B182" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C182" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D182" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5097,13 +5115,13 @@
         <v>186</v>
       </c>
       <c r="B183" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C183" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D183" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5111,13 +5129,13 @@
         <v>187</v>
       </c>
       <c r="B184" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C184" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D184" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5125,13 +5143,13 @@
         <v>188</v>
       </c>
       <c r="B185" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C185" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D185" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5139,13 +5157,13 @@
         <v>189</v>
       </c>
       <c r="B186" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C186" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D186" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5153,13 +5171,13 @@
         <v>190</v>
       </c>
       <c r="B187" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C187" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D187" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5167,13 +5185,13 @@
         <v>191</v>
       </c>
       <c r="B188" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C188" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D188" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5181,13 +5199,13 @@
         <v>192</v>
       </c>
       <c r="B189" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C189" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D189" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5195,13 +5213,13 @@
         <v>193</v>
       </c>
       <c r="B190" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C190" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D190" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5209,13 +5227,13 @@
         <v>194</v>
       </c>
       <c r="B191" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C191" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D191" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5223,13 +5241,13 @@
         <v>195</v>
       </c>
       <c r="B192" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C192" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D192" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5237,13 +5255,13 @@
         <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C193" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D193" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5251,13 +5269,13 @@
         <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C194" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D194" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5265,13 +5283,13 @@
         <v>198</v>
       </c>
       <c r="B195" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C195" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D195" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5279,13 +5297,13 @@
         <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C196" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D196" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5293,13 +5311,13 @@
         <v>200</v>
       </c>
       <c r="B197" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C197" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D197" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5307,13 +5325,13 @@
         <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C198" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D198" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5321,13 +5339,13 @@
         <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C199" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D199" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5335,13 +5353,13 @@
         <v>203</v>
       </c>
       <c r="B200" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C200" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D200" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5349,13 +5367,13 @@
         <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C201" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D201" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5366,10 +5384,10 @@
         <v>205</v>
       </c>
       <c r="C202" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D202" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5377,13 +5395,13 @@
         <v>206</v>
       </c>
       <c r="B203" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C203" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D203" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5391,13 +5409,13 @@
         <v>207</v>
       </c>
       <c r="B204" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C204" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D204" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5405,13 +5423,13 @@
         <v>208</v>
       </c>
       <c r="B205" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C205" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D205" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5419,13 +5437,13 @@
         <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C206" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D206" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5433,13 +5451,13 @@
         <v>210</v>
       </c>
       <c r="B207" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C207" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D207" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5447,13 +5465,13 @@
         <v>211</v>
       </c>
       <c r="B208" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C208" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D208" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5461,13 +5479,13 @@
         <v>212</v>
       </c>
       <c r="B209" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C209" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D209" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5475,13 +5493,13 @@
         <v>213</v>
       </c>
       <c r="B210" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C210" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D210" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5489,13 +5507,13 @@
         <v>214</v>
       </c>
       <c r="B211" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C211" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D211" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5503,13 +5521,13 @@
         <v>215</v>
       </c>
       <c r="B212" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C212" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D212" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5517,13 +5535,13 @@
         <v>216</v>
       </c>
       <c r="B213" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C213" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D213" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5531,13 +5549,13 @@
         <v>217</v>
       </c>
       <c r="B214" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C214" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D214" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5545,13 +5563,13 @@
         <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C215" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D215" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5559,13 +5577,13 @@
         <v>219</v>
       </c>
       <c r="B216" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C216" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D216" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5573,13 +5591,13 @@
         <v>220</v>
       </c>
       <c r="B217" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C217" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D217" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5587,13 +5605,13 @@
         <v>221</v>
       </c>
       <c r="B218" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C218" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D218" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5601,13 +5619,13 @@
         <v>222</v>
       </c>
       <c r="B219" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C219" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D219" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5615,13 +5633,13 @@
         <v>223</v>
       </c>
       <c r="B220" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C220" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D220" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5629,13 +5647,13 @@
         <v>224</v>
       </c>
       <c r="B221" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C221" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D221" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5643,13 +5661,13 @@
         <v>225</v>
       </c>
       <c r="B222" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C222" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D222" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5657,13 +5675,13 @@
         <v>226</v>
       </c>
       <c r="B223" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C223" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D223" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5671,13 +5689,13 @@
         <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C224" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D224" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5685,13 +5703,13 @@
         <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C225" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D225" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5699,13 +5717,13 @@
         <v>229</v>
       </c>
       <c r="B226" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C226" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D226" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5713,13 +5731,13 @@
         <v>230</v>
       </c>
       <c r="B227" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C227" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D227" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5727,13 +5745,13 @@
         <v>231</v>
       </c>
       <c r="B228" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C228" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D228" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5741,13 +5759,13 @@
         <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C229" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D229" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5755,13 +5773,13 @@
         <v>233</v>
       </c>
       <c r="B230" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C230" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D230" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5769,13 +5787,13 @@
         <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C231" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D231" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5783,13 +5801,13 @@
         <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C232" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D232" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5797,13 +5815,13 @@
         <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C233" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D233" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5811,13 +5829,13 @@
         <v>237</v>
       </c>
       <c r="B234" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C234" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D234" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5825,13 +5843,13 @@
         <v>238</v>
       </c>
       <c r="B235" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C235" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D235" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5839,13 +5857,13 @@
         <v>239</v>
       </c>
       <c r="B236" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C236" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D236" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5853,13 +5871,13 @@
         <v>240</v>
       </c>
       <c r="B237" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C237" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D237" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5867,13 +5885,13 @@
         <v>241</v>
       </c>
       <c r="B238" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C238" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D238" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5881,13 +5899,13 @@
         <v>242</v>
       </c>
       <c r="B239" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C239" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D239" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5895,13 +5913,13 @@
         <v>243</v>
       </c>
       <c r="B240" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C240" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D240" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5909,13 +5927,13 @@
         <v>244</v>
       </c>
       <c r="B241" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C241" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D241" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5923,13 +5941,13 @@
         <v>245</v>
       </c>
       <c r="B242" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C242" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D242" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5937,13 +5955,13 @@
         <v>246</v>
       </c>
       <c r="B243" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C243" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D243" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5951,13 +5969,13 @@
         <v>247</v>
       </c>
       <c r="B244" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C244" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D244" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5965,13 +5983,13 @@
         <v>248</v>
       </c>
       <c r="B245" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C245" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D245" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5979,13 +5997,13 @@
         <v>249</v>
       </c>
       <c r="B246" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C246" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D246" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5993,13 +6011,13 @@
         <v>250</v>
       </c>
       <c r="B247" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C247" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D247" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -6007,13 +6025,13 @@
         <v>251</v>
       </c>
       <c r="B248" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C248" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D248" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -6021,13 +6039,13 @@
         <v>252</v>
       </c>
       <c r="B249" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C249" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D249" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -6035,13 +6053,13 @@
         <v>253</v>
       </c>
       <c r="B250" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C250" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D250" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -6049,13 +6067,13 @@
         <v>254</v>
       </c>
       <c r="B251" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C251" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D251" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -6063,13 +6081,13 @@
         <v>255</v>
       </c>
       <c r="B252" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C252" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D252" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -6077,13 +6095,13 @@
         <v>256</v>
       </c>
       <c r="B253" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C253" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D253" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -6091,13 +6109,13 @@
         <v>257</v>
       </c>
       <c r="B254" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C254" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D254" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -6105,13 +6123,13 @@
         <v>258</v>
       </c>
       <c r="B255" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C255" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D255" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -6119,13 +6137,13 @@
         <v>259</v>
       </c>
       <c r="B256" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C256" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D256" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -6133,13 +6151,13 @@
         <v>260</v>
       </c>
       <c r="B257" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C257" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D257" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -6147,13 +6165,13 @@
         <v>261</v>
       </c>
       <c r="B258" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C258" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D258" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6161,13 +6179,13 @@
         <v>262</v>
       </c>
       <c r="B259" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C259" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D259" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6175,13 +6193,13 @@
         <v>263</v>
       </c>
       <c r="B260" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C260" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D260" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6189,13 +6207,13 @@
         <v>264</v>
       </c>
       <c r="B261" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C261" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D261" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -6203,13 +6221,13 @@
         <v>265</v>
       </c>
       <c r="B262" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C262" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D262" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -6217,13 +6235,13 @@
         <v>266</v>
       </c>
       <c r="B263" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C263" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D263" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6231,13 +6249,13 @@
         <v>267</v>
       </c>
       <c r="B264" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C264" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D264" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -6245,13 +6263,13 @@
         <v>268</v>
       </c>
       <c r="B265" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C265" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D265" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -6259,13 +6277,13 @@
         <v>269</v>
       </c>
       <c r="B266" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C266" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D266" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -6273,13 +6291,13 @@
         <v>270</v>
       </c>
       <c r="B267" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C267" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D267" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -6287,13 +6305,13 @@
         <v>271</v>
       </c>
       <c r="B268" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C268" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D268" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -6301,13 +6319,13 @@
         <v>272</v>
       </c>
       <c r="B269" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C269" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D269" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -6315,13 +6333,13 @@
         <v>273</v>
       </c>
       <c r="B270" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C270" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D270" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -6329,13 +6347,13 @@
         <v>274</v>
       </c>
       <c r="B271" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C271" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D271" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -6343,13 +6361,13 @@
         <v>275</v>
       </c>
       <c r="B272" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C272" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D272" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -6357,13 +6375,13 @@
         <v>276</v>
       </c>
       <c r="B273" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C273" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D273" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -6371,13 +6389,13 @@
         <v>277</v>
       </c>
       <c r="B274" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C274" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D274" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -6385,13 +6403,13 @@
         <v>278</v>
       </c>
       <c r="B275" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C275" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D275" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -6399,13 +6417,13 @@
         <v>279</v>
       </c>
       <c r="B276" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C276" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D276" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -6413,13 +6431,13 @@
         <v>280</v>
       </c>
       <c r="B277" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C277" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D277" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -6427,13 +6445,13 @@
         <v>281</v>
       </c>
       <c r="B278" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C278" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D278" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -6441,13 +6459,13 @@
         <v>282</v>
       </c>
       <c r="B279" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C279" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D279" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -6455,13 +6473,13 @@
         <v>283</v>
       </c>
       <c r="B280" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C280" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D280" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -6469,13 +6487,13 @@
         <v>284</v>
       </c>
       <c r="B281" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C281" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D281" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -6483,13 +6501,13 @@
         <v>285</v>
       </c>
       <c r="B282" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C282" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D282" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6497,13 +6515,13 @@
         <v>286</v>
       </c>
       <c r="B283" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C283" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D283" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -6511,13 +6529,13 @@
         <v>287</v>
       </c>
       <c r="B284" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C284" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D284" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -6525,13 +6543,13 @@
         <v>288</v>
       </c>
       <c r="B285" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C285" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D285" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6539,13 +6557,13 @@
         <v>289</v>
       </c>
       <c r="B286" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C286" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D286" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -6553,13 +6571,13 @@
         <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C287" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D287" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -6567,13 +6585,13 @@
         <v>291</v>
       </c>
       <c r="B288" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C288" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D288" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6581,13 +6599,13 @@
         <v>292</v>
       </c>
       <c r="B289" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C289" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D289" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6595,13 +6613,13 @@
         <v>293</v>
       </c>
       <c r="B290" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C290" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D290" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -6609,13 +6627,13 @@
         <v>294</v>
       </c>
       <c r="B291" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C291" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D291" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -6623,13 +6641,13 @@
         <v>295</v>
       </c>
       <c r="B292" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C292" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D292" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -6637,13 +6655,13 @@
         <v>296</v>
       </c>
       <c r="B293" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C293" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D293" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -6654,10 +6672,10 @@
         <v>297</v>
       </c>
       <c r="C294" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D294" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -6665,13 +6683,13 @@
         <v>298</v>
       </c>
       <c r="B295" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C295" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D295" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6679,13 +6697,13 @@
         <v>299</v>
       </c>
       <c r="B296" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C296" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D296" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6693,13 +6711,13 @@
         <v>300</v>
       </c>
       <c r="B297" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C297" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D297" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -6707,13 +6725,13 @@
         <v>301</v>
       </c>
       <c r="B298" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C298" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D298" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -6721,13 +6739,13 @@
         <v>302</v>
       </c>
       <c r="B299" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C299" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D299" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -6735,13 +6753,13 @@
         <v>303</v>
       </c>
       <c r="B300" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C300" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D300" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -6749,13 +6767,13 @@
         <v>304</v>
       </c>
       <c r="B301" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C301" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D301" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -6763,13 +6781,13 @@
         <v>305</v>
       </c>
       <c r="B302" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C302" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D302" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6777,13 +6795,13 @@
         <v>306</v>
       </c>
       <c r="B303" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C303" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D303" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -6791,13 +6809,13 @@
         <v>307</v>
       </c>
       <c r="B304" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C304" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D304" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -6805,13 +6823,13 @@
         <v>308</v>
       </c>
       <c r="B305" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C305" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D305" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6819,13 +6837,13 @@
         <v>309</v>
       </c>
       <c r="B306" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C306" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D306" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6833,13 +6851,13 @@
         <v>310</v>
       </c>
       <c r="B307" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C307" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D307" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -6847,13 +6865,13 @@
         <v>311</v>
       </c>
       <c r="B308" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C308" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D308" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6861,13 +6879,13 @@
         <v>312</v>
       </c>
       <c r="B309" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C309" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D309" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6875,13 +6893,13 @@
         <v>313</v>
       </c>
       <c r="B310" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C310" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D310" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6889,13 +6907,13 @@
         <v>314</v>
       </c>
       <c r="B311" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C311" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D311" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6903,13 +6921,13 @@
         <v>315</v>
       </c>
       <c r="B312" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C312" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D312" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6917,13 +6935,13 @@
         <v>316</v>
       </c>
       <c r="B313" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C313" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D313" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6931,13 +6949,13 @@
         <v>317</v>
       </c>
       <c r="B314" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C314" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D314" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6945,13 +6963,13 @@
         <v>318</v>
       </c>
       <c r="B315" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C315" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D315" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6959,13 +6977,13 @@
         <v>319</v>
       </c>
       <c r="B316" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C316" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D316" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6973,13 +6991,13 @@
         <v>320</v>
       </c>
       <c r="B317" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C317" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D317" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6987,13 +7005,13 @@
         <v>321</v>
       </c>
       <c r="B318" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C318" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D318" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -7001,13 +7019,13 @@
         <v>322</v>
       </c>
       <c r="B319" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C319" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D319" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -7015,13 +7033,13 @@
         <v>323</v>
       </c>
       <c r="B320" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C320" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D320" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -7029,13 +7047,13 @@
         <v>324</v>
       </c>
       <c r="B321" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C321" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D321" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -7043,13 +7061,13 @@
         <v>325</v>
       </c>
       <c r="B322" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C322" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D322" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -7057,13 +7075,13 @@
         <v>326</v>
       </c>
       <c r="B323" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C323" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D323" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -7071,13 +7089,13 @@
         <v>327</v>
       </c>
       <c r="B324" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C324" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D324" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -7085,13 +7103,13 @@
         <v>328</v>
       </c>
       <c r="B325" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C325" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D325" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -7099,13 +7117,13 @@
         <v>329</v>
       </c>
       <c r="B326" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C326" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D326" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -7113,13 +7131,13 @@
         <v>330</v>
       </c>
       <c r="B327" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C327" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D327" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -7127,13 +7145,13 @@
         <v>331</v>
       </c>
       <c r="B328" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C328" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D328" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -7141,13 +7159,13 @@
         <v>332</v>
       </c>
       <c r="B329" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C329" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D329" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -7155,13 +7173,13 @@
         <v>333</v>
       </c>
       <c r="B330" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C330" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D330" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -7169,13 +7187,13 @@
         <v>334</v>
       </c>
       <c r="B331" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C331" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D331" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -7183,13 +7201,13 @@
         <v>335</v>
       </c>
       <c r="B332" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C332" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D332" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -7197,13 +7215,13 @@
         <v>336</v>
       </c>
       <c r="B333" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C333" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D333" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -7211,13 +7229,13 @@
         <v>337</v>
       </c>
       <c r="B334" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C334" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D334" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -7225,13 +7243,13 @@
         <v>338</v>
       </c>
       <c r="B335" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C335" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D335" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -7239,13 +7257,13 @@
         <v>339</v>
       </c>
       <c r="B336" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C336" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D336" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -7253,13 +7271,13 @@
         <v>340</v>
       </c>
       <c r="B337" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C337" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D337" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -7267,13 +7285,13 @@
         <v>341</v>
       </c>
       <c r="B338" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C338" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D338" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -7281,13 +7299,13 @@
         <v>342</v>
       </c>
       <c r="B339" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C339" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D339" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -7295,13 +7313,13 @@
         <v>343</v>
       </c>
       <c r="B340" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C340" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D340" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -7309,13 +7327,13 @@
         <v>344</v>
       </c>
       <c r="B341" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C341" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D341" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -7323,13 +7341,13 @@
         <v>345</v>
       </c>
       <c r="B342" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C342" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D342" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -7337,13 +7355,13 @@
         <v>346</v>
       </c>
       <c r="B343" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C343" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D343" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -7351,13 +7369,13 @@
         <v>106</v>
       </c>
       <c r="B344" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C344" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D344" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -7365,13 +7383,13 @@
         <v>347</v>
       </c>
       <c r="B345" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C345" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D345" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -7379,13 +7397,13 @@
         <v>302</v>
       </c>
       <c r="B346" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C346" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D346" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -7393,13 +7411,13 @@
         <v>348</v>
       </c>
       <c r="B347" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C347" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D347" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -7407,13 +7425,13 @@
         <v>349</v>
       </c>
       <c r="B348" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C348" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D348" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -7421,13 +7439,13 @@
         <v>350</v>
       </c>
       <c r="B349" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C349" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D349" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -7435,13 +7453,13 @@
         <v>351</v>
       </c>
       <c r="B350" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C350" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D350" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -7449,13 +7467,13 @@
         <v>352</v>
       </c>
       <c r="B351" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C351" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D351" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -7463,13 +7481,13 @@
         <v>353</v>
       </c>
       <c r="B352" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C352" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D352" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -7477,13 +7495,13 @@
         <v>354</v>
       </c>
       <c r="B353" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C353" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D353" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -7491,13 +7509,13 @@
         <v>355</v>
       </c>
       <c r="B354" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C354" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D354" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -7505,13 +7523,13 @@
         <v>356</v>
       </c>
       <c r="B355" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C355" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D355" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -7519,13 +7537,13 @@
         <v>357</v>
       </c>
       <c r="B356" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C356" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D356" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -7533,13 +7551,13 @@
         <v>358</v>
       </c>
       <c r="B357" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C357" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D357" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -7547,13 +7565,13 @@
         <v>359</v>
       </c>
       <c r="B358" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C358" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D358" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -7561,13 +7579,13 @@
         <v>360</v>
       </c>
       <c r="B359" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C359" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D359" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -7575,13 +7593,13 @@
         <v>361</v>
       </c>
       <c r="B360" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C360" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D360" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -7589,13 +7607,13 @@
         <v>362</v>
       </c>
       <c r="B361" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C361" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D361" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -7603,13 +7621,13 @@
         <v>363</v>
       </c>
       <c r="B362" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C362" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D362" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -7620,10 +7638,10 @@
         <v>364</v>
       </c>
       <c r="C363" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D363" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7634,10 +7652,10 @@
         <v>365</v>
       </c>
       <c r="C364" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D364" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -7645,13 +7663,13 @@
         <v>366</v>
       </c>
       <c r="B365" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C365" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D365" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -7659,13 +7677,13 @@
         <v>367</v>
       </c>
       <c r="B366" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C366" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D366" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -7673,13 +7691,13 @@
         <v>368</v>
       </c>
       <c r="B367" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C367" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D367" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -7687,13 +7705,13 @@
         <v>369</v>
       </c>
       <c r="B368" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C368" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D368" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -7701,13 +7719,13 @@
         <v>370</v>
       </c>
       <c r="B369" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C369" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D369" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -7715,13 +7733,13 @@
         <v>371</v>
       </c>
       <c r="B370" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C370" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D370" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -7729,13 +7747,13 @@
         <v>372</v>
       </c>
       <c r="B371" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C371" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D371" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -7743,13 +7761,41 @@
         <v>373</v>
       </c>
       <c r="B372" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C372" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D372" t="s">
-        <v>719</v>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
+      <c r="A373" t="s">
+        <v>374</v>
+      </c>
+      <c r="B373" t="s">
+        <v>717</v>
+      </c>
+      <c r="C373" t="s">
+        <v>719</v>
+      </c>
+      <c r="D373" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
+      <c r="A374" t="s">
+        <v>375</v>
+      </c>
+      <c r="B374" t="s">
+        <v>718</v>
+      </c>
+      <c r="C374" t="s">
+        <v>719</v>
+      </c>
+      <c r="D374" t="s">
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,13 +24,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,39 +427,48 @@
   </sheetPr>
   <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Input Name (Scorecard/Stats)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Official Registered Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Ledger Status Verification</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Registered Name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>NV Play Name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -25,10 +25,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -425,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -433,7 +430,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -939,12 +936,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ananthu Ramachandran</t>
+          <t>Andy McCrea</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ananthu Parekunnel Ramachandran</t>
+          <t>Andrew McCrea</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -961,12 +958,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andy McCrea</t>
+          <t>Andy Stephens</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Andrew McCrea</t>
+          <t>Andrew Stephens</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -983,12 +980,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andy Stephens</t>
+          <t>Aneesh Sasi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Andrew Stephens</t>
+          <t>Aneesh Sasi Jayakumari</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1005,12 +1002,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aneesh Sasi</t>
+          <t>Ant Spence</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aneesh Sasi Jayakumari</t>
+          <t>Anthony Spence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1027,17 +1024,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ant Spence</t>
+          <t>Anu Krishnan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Anthony Spence</t>
+          <t>Anu Pillai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1049,17 +1046,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Anu Krishnan</t>
+          <t>AP Praveen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Anu Pillai</t>
+          <t>Praveen Angalaparameswari Punithan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1071,12 +1068,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AP Praveen</t>
+          <t>Arafat Khan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Praveen Angalaparameswari Punithan</t>
+          <t>Arafat Hussain Khan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1093,12 +1090,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Arafat Khan</t>
+          <t>Aravind Geetha</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arafat Hussain Khan</t>
+          <t>Aravind Kumar Devarajan Geetha</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1115,12 +1112,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aravind Geetha</t>
+          <t>Arbas Khan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aravind Kumar Devarajan Geetha</t>
+          <t>Arbas Khan Amarkhail</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1137,12 +1134,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Arbas Khan</t>
+          <t>Arokiaraj Rajan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arbas Khan Amarkhail</t>
+          <t>Arokiaraj Vincent Rajan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1159,12 +1156,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Arokiaraj Rajan</t>
+          <t>Artie Campbell</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Arokiaraj Vincent Rajan</t>
+          <t>Arthur Campbell</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1181,12 +1178,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Artie Campbell</t>
+          <t>Arun Aneesh</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Arthur Campbell</t>
+          <t>Arun Aneesh Kumar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1203,12 +1200,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Arun Aneesh</t>
+          <t>Arun Geethakumari</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Arun Aneesh Kumar</t>
+          <t>Arun Kumar Thulaseedharanpillai Geethakumari</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1225,12 +1222,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Arun Geethakumari</t>
+          <t>Ashley Dilbert</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Arun Kumar Thulaseedharanpillai Geethakumari</t>
+          <t>Ashley Dilbert George Thomas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1247,7 +1244,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ashley Dilbert</t>
+          <t>Ashley Thomas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1269,12 +1266,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ashley Thomas</t>
+          <t>Ashwinswamy Takoori</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ashley Dilbert George Thomas</t>
+          <t>Ashwinswamy Gurumurthy Takoori</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1291,12 +1288,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ashwinswamy Takoori</t>
+          <t>Aziz Daptari</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ashwinswamy Gurumurthy Takoori</t>
+          <t>Md Aziz Daptari</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1313,12 +1310,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aziz Daptari</t>
+          <t>Ben Cairns</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Md Aziz Daptari</t>
+          <t>Benjamin Cairns</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1335,12 +1332,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ben Cairns</t>
+          <t>Ben Calitz</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Benjamin Cairns</t>
+          <t>Benjamin Calitz</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1357,12 +1354,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ben Calitz</t>
+          <t>Ben Mackey</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Benjamin Calitz</t>
+          <t>Benjamin Mackey</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1379,12 +1376,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ben Mackey</t>
+          <t>Ben Martin</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Benjamin Mackey</t>
+          <t>Benjamin Martin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1401,12 +1398,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ben Martin</t>
+          <t>Ben Ogle</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Benjamin Martin</t>
+          <t>Bendigaid Ogle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1423,12 +1420,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ben Ogle</t>
+          <t>Benjamin King</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bendigaid Ogle</t>
+          <t>Benjamin A King</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1445,12 +1442,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Benjamin King</t>
+          <t>BENNY Varughese</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Benjamin A King</t>
+          <t>Benny Thomas Varughese</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1467,17 +1464,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BENNY Varughese</t>
+          <t>Berlinraj Swarnam</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Benny Thomas Varughese</t>
+          <t>Berlinraj Gnanamani Swarnam</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1489,17 +1486,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Berlinraj Swarnam</t>
+          <t>Bharath Allika Kunjukeetingal</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Berlinraj Gnanamani Swarnam</t>
+          <t>Bharath Mohan Allika Kunjukeetingal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1511,17 +1508,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bharath Allika Kunjukeetingal</t>
+          <t>Bilal Farooq</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bharath Mohan Allika Kunjukeetingal</t>
+          <t>Muhammad Bilal Farooq</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1533,17 +1530,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bilal Farooq</t>
+          <t>Bob Moore</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Muhammad Bilal Farooq</t>
+          <t>Robert Moore</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1555,17 +1552,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bob Moore</t>
+          <t>Bony Alexander</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Robert Moore</t>
+          <t>Bony Chacko Alexander</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1577,17 +1574,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bony Alexander</t>
+          <t>Byjo Varghese</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bony Chacko Alexander</t>
+          <t>Byjo Thomas Varghese</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1599,12 +1596,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Byjo Varghese</t>
+          <t>Byshal Varghese</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Byjo Thomas Varghese</t>
+          <t>Byshal Thomas Varghese</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1621,12 +1618,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Byshal Varghese</t>
+          <t>CA Storey</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Byshal Thomas Varghese</t>
+          <t>Colin Storey</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1643,12 +1640,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CA Storey</t>
+          <t>Callum Weir</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Colin Storey</t>
+          <t>John Weir</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1658,19 +1655,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t xml:space="preserve">this is the Derriaghy Callum Weir </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Callum Weir</t>
+          <t>Calum McCandless</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>John Weir</t>
+          <t>C McCandless</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1680,19 +1677,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">this is the Derriaghy Callum Weir </t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Calum McCandless</t>
+          <t>Charles Shannon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C McCandless</t>
+          <t>Charlie Shannon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1709,12 +1706,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Charles Shannon</t>
+          <t>Charlie Duncan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Charlie Shannon</t>
+          <t>Charles Duncan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1731,12 +1728,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Charlie Duncan</t>
+          <t>Charlie Monro</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Charles Duncan</t>
+          <t>Charles Monro</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1753,12 +1750,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Charlie Monro</t>
+          <t>Chris Dempsey</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charles Monro</t>
+          <t>Christopher Dempsey</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1775,12 +1772,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chris Dempsey</t>
+          <t>Chris Dougherty</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Christopher Dempsey</t>
+          <t>Christopher Dougherty</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1797,12 +1794,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chris Dougherty</t>
+          <t>Chris Keenan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Christopher Dougherty</t>
+          <t>Christopher Keenan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1819,12 +1816,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chris Keenan</t>
+          <t>Chris Koorts</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Christopher Keenan</t>
+          <t>Christo Koorts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1841,17 +1838,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chris Koorts</t>
+          <t>Chris Pyper</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Christo Koorts</t>
+          <t>Christopher Pyper</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1863,17 +1860,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chris Pyper</t>
+          <t>Chris Robinson</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Christopher Pyper</t>
+          <t>Christopher Robinson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1885,12 +1882,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chris Robinson</t>
+          <t>Chris Walton</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Christopher Robinson</t>
+          <t>Christopher Walton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1907,12 +1904,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chris Walton</t>
+          <t>Chris Wilson</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Christopher Walton</t>
+          <t>John Wilson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1929,17 +1926,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chris Wilson</t>
+          <t>Christoffel Phillippus Klijnhans</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>John Wilson</t>
+          <t>Cp Klijnhans</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1951,17 +1948,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Christoffel Phillippus Klijnhans</t>
+          <t>Christopher Cahoon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cp Klijnhans</t>
+          <t>Chris Cahoon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1973,12 +1970,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Christopher Cahoon</t>
+          <t>Christopher Elliott</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chris Cahoon</t>
+          <t>Chris Elliott</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1995,17 +1992,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Christopher Elliott</t>
+          <t>Christopher Whitten</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chris Elliott</t>
+          <t>Chris Whitten</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2017,17 +2014,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Christopher Whitten</t>
+          <t>CJ Van der Walt</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Chris Whitten</t>
+          <t>Cornelius Van Der Walt</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2039,12 +2036,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CJ Van der Walt</t>
+          <t>Dan Soper</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cornelius Van Der Walt</t>
+          <t>Daniel Soper</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2061,12 +2058,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dan Soper</t>
+          <t>Daniel Fletcher</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Daniel Soper</t>
+          <t>Dan Fletcher</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2083,12 +2080,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Daniel Fletcher</t>
+          <t>Daniel Greenaway</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dan Fletcher</t>
+          <t>Dan Greenaway</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2105,12 +2102,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Daniel Greenaway</t>
+          <t>Danny Cooper</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dan Greenaway</t>
+          <t>Daniel Cooper</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2127,12 +2124,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Danny Cooper</t>
+          <t>Darshan Nair</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Daniel Cooper</t>
+          <t>Darshan Dinesh Nair</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2149,12 +2146,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Darshan Nair</t>
+          <t>David O’Sullivan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Darshan Dinesh Nair</t>
+          <t>David O'Sullivan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2171,12 +2168,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>David O'Sullivan</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>David O’Sullivan</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>David O'Sullivan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2193,17 +2190,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>David O'Sullivan</t>
+          <t>Davy Glover</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>David O’Sullivan</t>
+          <t>David Glover</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2215,17 +2212,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Davy Glover</t>
+          <t>Davy Harris</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>David Glover</t>
+          <t>David Harris</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2237,17 +2234,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Davy Harris</t>
+          <t>Davy Scott</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>David Harris</t>
+          <t>David Scott</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2259,17 +2256,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Davy Scott</t>
+          <t>Dawood Khan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>David Scott</t>
+          <t>Dawood Ahmed Khan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2281,12 +2278,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dawood Khan</t>
+          <t>Dayananda Gowdappa</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dawood Ahmed Khan</t>
+          <t>Dayananda Markuli Gowdappa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2303,12 +2300,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dayananda Gowdappa</t>
+          <t>Dennis Thanivelil</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dayananda Markuli Gowdappa</t>
+          <t>Dennis Varghese Thanivelil</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2325,7 +2322,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dennis Thanivelil</t>
+          <t>Dennis Varghese</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2347,12 +2344,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dennis Varghese</t>
+          <t>Denny Andrews Abraham</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dennis Varghese Thanivelil</t>
+          <t>Denny Abraham</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2369,12 +2366,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Denny Andrews Abraham</t>
+          <t>Dhuvi Prattipati</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Denny Abraham</t>
+          <t>Dhuvi Thanik Prattipati</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2391,12 +2388,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dhuvi Prattipati</t>
+          <t>Dillu</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dhuvi Thanik Prattipati</t>
+          <t xml:space="preserve">Dhilneesh Joseph </t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2413,12 +2410,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dhuvi Prattipati</t>
+          <t>Dino James</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dhuvi Thanik Prattipati</t>
+          <t>Dino Shiju James</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2435,12 +2432,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dillu</t>
+          <t>Dushyanth Bommana</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dhilneesh Joseph </t>
+          <t>Dushyanth Reddy Bommana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2457,12 +2454,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dino James</t>
+          <t>Eddie Hawkins</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dino Shiju James</t>
+          <t>Edward Hawkins</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2479,12 +2476,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dushyanth Bommana</t>
+          <t>Eddie Wilson</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dushyanth Reddy Bommana</t>
+          <t>Edward Wilson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2501,12 +2498,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eddie Hawkins</t>
+          <t>Eli Marshall</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Edward Hawkins</t>
+          <t>Elijah Marshall</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2523,12 +2520,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Eddie Wilson</t>
+          <t>F Monson</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Edward Wilson</t>
+          <t>Finlay Monson</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2545,12 +2542,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Eli Marshall</t>
+          <t>Faizan Muhammad</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Elijah Marshall</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2567,12 +2564,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>F Monson</t>
+          <t>Felix Loebneu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Finlay Monson</t>
+          <t>Felix Loebnau</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2589,12 +2586,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Faizan Muhammad</t>
+          <t>Finn Garrett</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Muhammad Faizan</t>
+          <t>Finn Garrett Jowsey</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2611,12 +2608,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Felix Loebneu</t>
+          <t>Finn O'Hara</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Felix Loebnau</t>
+          <t>Finn Ohara</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2633,12 +2630,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Finn Garrett</t>
+          <t>Firose Abdul Rasheed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Finn Garrett Jowsey</t>
+          <t>Firose Abdul Rasheed Amila Beevi</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2655,12 +2652,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Finn O'Hara</t>
+          <t>Frazer McKane</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Finn Ohara</t>
+          <t>Frazer J McKane</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2677,12 +2674,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Firose Abdul Rasheed</t>
+          <t>Gladson David George</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Firose Abdul Rasheed Amila Beevi</t>
+          <t>Gladson George</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2699,12 +2696,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Francis Collins</t>
+          <t>Gopa Krishna</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Francis Gj Collins</t>
+          <t>Gopal Krishna Budagatla</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2721,12 +2718,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Frazer McKane</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Frazer J McKane</t>
+          <t>Gopal Krishna Budagatla</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2743,17 +2740,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gladson David George</t>
+          <t>Gopal Krishna Budagatle</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gladson George</t>
+          <t>Gopal Krishna Budagatla</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2765,12 +2762,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gopa Krishna</t>
+          <t>Gowri Arivukkarasu</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatla</t>
+          <t>Gowri Sankar Arivukkarasu</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2787,12 +2784,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Gowri Sankar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatla</t>
+          <t>Gowri Sankar Arivukkarasu</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2809,12 +2806,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatle</t>
+          <t>Gus Farrell</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatla</t>
+          <t>Angus Farrell</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2831,12 +2828,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Gowri Arivukkarasu</t>
+          <t>Hafis Siyad</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Gowri Sankar Arivukkarasu</t>
+          <t>Muhammed Hafis Siyad</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2853,12 +2850,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Gowri Sankar</t>
+          <t>Hafiz Iqbal</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gowri Sankar Arivukkarasu</t>
+          <t>Hafiz M Waqas Iqbal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2875,17 +2872,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gus Farrell</t>
+          <t>Harry Shaneesh</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Angus Farrell</t>
+          <t>Harikrishna Saneesh</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2897,12 +2894,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hafis Siyad</t>
+          <t>Haseeb Syed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Muhammed Hafis Siyad</t>
+          <t>Syed Haseeb</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2919,12 +2916,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Hafiz Iqbal</t>
+          <t>Hemanth Suma</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hafiz M Waqas Iqbal</t>
+          <t>Hemanth Swamy Ekanthappa Suma</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2941,12 +2938,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Harry Shaneesh</t>
+          <t>Henry Oliver Scott</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Harikrishna Saneesh</t>
+          <t>Henry Scott</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2963,12 +2960,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Haseeb Syed</t>
+          <t>Huzaifa Khalid</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Syed Haseeb</t>
+          <t>Syed Huzaifa Khalid</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2985,12 +2982,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hemanth Suma</t>
+          <t>Ishan Pattnaik</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Hemanth Swamy Ekanthappa Suma</t>
+          <t>Ishan Chandra Pattnaik</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3007,12 +3004,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Henry Oliver Scott</t>
+          <t>Ismail Sherzad</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Henry Scott</t>
+          <t>Ismail Ahmed Sherzad</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3029,12 +3026,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Huzaifa Khalid</t>
+          <t>J Hoffmeyr</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Syed Huzaifa Khalid</t>
+          <t>Jordaan Hofmeyr</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3051,12 +3048,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ishan Pattnaik</t>
+          <t>J jose</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ishan Chandra Pattnaik</t>
+          <t>Jibin Jose</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3073,12 +3070,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ismail Sherzad</t>
+          <t>J Shields</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ismail Ahmed Sherzad</t>
+          <t>Jonah Shields</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3095,12 +3092,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>J Hoffmeyr</t>
+          <t>J varghese</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jordaan Hofmeyr</t>
+          <t>Jeril Varghese</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3117,12 +3114,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>J jose</t>
+          <t>Jack Alexander Smyth</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jibin Jose</t>
+          <t>Jack Smyth</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3139,12 +3136,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>J Shields</t>
+          <t>Jack Hutchinson</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jonah Shields</t>
+          <t>William Hutchinson</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3161,12 +3158,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>J varghese</t>
+          <t>Jay Hunter</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jeril Varghese</t>
+          <t>Jeffrey Hunter</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3183,12 +3180,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jack Alexander Smyth</t>
+          <t>Jaydee Oliver</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jack Smyth</t>
+          <t>Oliver Jaydee</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3205,12 +3202,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jack Hutchinson</t>
+          <t>Jayden K</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>William Hutchinson</t>
+          <t>Daniel Kleynhans</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3227,12 +3224,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jay Hunter</t>
+          <t>Jayden Kleynhans</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jeffrey Hunter</t>
+          <t>Daniel Kleynhans</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3249,12 +3246,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jaydee Oliver</t>
+          <t>Jeril Varghese</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Oliver Jaydee</t>
+          <t>Jeril Puthenpurackal Varghese</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3271,12 +3268,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jayden K</t>
+          <t>Jerin Alias</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Daniel Kleynhans</t>
+          <t>Jerin Palakattu Alias</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3293,12 +3290,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jayden Kleynhans</t>
+          <t>Jez Wilmshurst</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Daniel Kleynhans</t>
+          <t>Jeremy Wilmshurst</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3315,12 +3312,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jeril Varghese</t>
+          <t>Jinso Devassykutty</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jeril Puthenpurackal Varghese</t>
+          <t>Jinso Pallicka Devassykutty</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3337,12 +3334,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Jerin Alias</t>
+          <t>Jinto Paul Kaliyadan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jerin Palakattu Alias</t>
+          <t>Jinto Kaliyadan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3359,12 +3356,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Jez Wilmshurst</t>
+          <t>Joe Keith-Cotton</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jeremy Wilmshurst</t>
+          <t>Joseph Keith-Cotton</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3381,12 +3378,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Jinso Devassykutty</t>
+          <t>John Close</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Jinso Pallicka Devassykutty</t>
+          <t>John T Close</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3403,12 +3400,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Jinto Paul Kaliyadan</t>
+          <t>John Walsh</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jinto Kaliyadan</t>
+          <t>Jonathan Walsh</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3425,12 +3422,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Joe Keith-Cotton</t>
+          <t>Jonathan Venus</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Joseph Keith-Cotton</t>
+          <t>Jay Venus</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3447,12 +3444,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>John Close</t>
+          <t>Jonny Moore</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>John T Close</t>
+          <t>Jonathan Moore</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3469,12 +3466,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>John Walsh</t>
+          <t>Josh Bates</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Jonathan Walsh</t>
+          <t>Joshua Bates</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3491,12 +3488,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jonathan Venus</t>
+          <t>Josh Corbett</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jay Venus</t>
+          <t>Joshua Corbett</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3513,12 +3510,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jonny Moore</t>
+          <t>Josh Froggatt</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Jonathan Moore</t>
+          <t>Joshua Froggatt</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3535,12 +3532,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Josh Bates</t>
+          <t>Josh Gordon</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Joshua Bates</t>
+          <t>Joshua GORDON</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3557,17 +3554,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Josh Corbett</t>
+          <t>Josh Walker</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Joshua Corbett</t>
+          <t>Joshua Walker</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3579,12 +3576,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Josh Froggatt</t>
+          <t>Josh Wilson</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Joshua Froggatt</t>
+          <t>Joshua Wilson</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3601,12 +3598,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Josh Gordon</t>
+          <t>Joshi John</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Joshua GORDON</t>
+          <t>Joshi Chavadivilla John</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3623,17 +3620,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Josh Walker</t>
+          <t>Joshua Sloan</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Joshua Walker</t>
+          <t>Joshua Adam Sloan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3645,12 +3642,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Josh Wilson</t>
+          <t>Karl Gribben</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Joshua Wilson</t>
+          <t>Karl Gribbin</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3667,12 +3664,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Joshi John</t>
+          <t>Karthik Jyothy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Joshi Chavadivilla John</t>
+          <t>Karthik Jyothy Puthoor Jyothy</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3689,12 +3686,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Joshua Sloan</t>
+          <t>Karthik Puthoor Jyothy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Joshua Adam Sloan</t>
+          <t>Karthik Jyothy Puthoor Jyothy</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3711,12 +3708,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Karl Gribben</t>
+          <t>Karthik Prasad</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Karl Gribbin</t>
+          <t>Karthik Bangalore Rajendra Prasad</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3733,12 +3730,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Karthik Jyothy</t>
+          <t>Kranthi Reddy</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Karthik Jyothy Puthoor Jyothy</t>
+          <t>Kranthi Kumar Reddy</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3755,12 +3752,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Karthik Puthoor Jyothy</t>
+          <t>Kris McNeill</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Karthik Jyothy Puthoor Jyothy</t>
+          <t>Kristofer McNeill</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3777,17 +3774,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Karthik Prasad</t>
+          <t>Lachlan Aitken</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Karthik Bangalore Rajendra Prasad</t>
+          <t>Lachy Aitken</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3799,12 +3796,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Kranthi Reddy</t>
+          <t>Lewis Buchanan</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Kranthi Kumar Reddy</t>
+          <t>Lewis David Buchanan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3821,12 +3818,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kris McNeill</t>
+          <t>Lijo Mathew Kocheriyil</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Kristofer McNeill</t>
+          <t>Lijo Mathew</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3843,17 +3840,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Lachlan Aitken</t>
+          <t>Maanvik Geddam</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lachy Aitken</t>
+          <t>Maanvik Vidhath Geddam</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3865,12 +3862,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Lewis Buchanan</t>
+          <t>Madhav Sarma</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lewis David Buchanan</t>
+          <t>Madhav Sarma Varanakkottu Unnikrishnan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3887,12 +3884,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Lijo Mathew Kocheriyil</t>
+          <t>Mahadeva Nidaghatta Shivakumar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lijo Mathew</t>
+          <t>Mahadeva Prasad Nidaghatta Shivakumar</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3909,12 +3906,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Maanvik Geddam</t>
+          <t>Mahesh Nilewar</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Maanvik Vidhath Geddam</t>
+          <t>Mahesh Dhanaji Nilewar</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3931,12 +3928,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Madhav Sarma</t>
+          <t>Mandar Hirve</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Madhav Sarma Varanakkottu Unnikrishnan</t>
+          <t>Mandar Parag Hirve</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3953,12 +3950,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Mahadeva Nidaghatta Shivakumar</t>
+          <t>Maneesha Chathuranga</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Mahadeva Prasad Nidaghatta Shivakumar</t>
+          <t>Maneesha Chathuranga Hettige Don</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3975,12 +3972,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mahesh Nilewar</t>
+          <t>Manindar Singh</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mahesh Dhanaji Nilewar</t>
+          <t>Manindra Singh</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3997,12 +3994,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Mandar Hirve</t>
+          <t>Manivannan Sivaganesh</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Mandar Parag Hirve</t>
+          <t>Sivaganesh Manivannan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4019,12 +4016,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Maneesha Chathuranga</t>
+          <t>Manoj Kumar</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Maneesha Chathuranga Hettige Don</t>
+          <t>Manoj Kumar Palaniswamy</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4041,34 +4038,34 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Manindar Singh</t>
+          <t>Mark Best</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Manindra Singh</t>
+          <t>Mark Best</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Special rule / Pending Audit</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Transferred from CI to Bangor on 2nd June 2026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Manivannan Sivaganesh</t>
+          <t>Matt Owen</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sivaganesh Manivannan</t>
+          <t>matthew owen</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4085,56 +4082,56 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Manoj Kumar</t>
+          <t>Matthew Humphreys</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Manoj Kumar Palaniswamy</t>
+          <t>Matthew Humphreys</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Special rule / Pending Audit</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Regarded as registered for Instonians for 2026</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Mark Best</t>
+          <t>Max Willmott</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Mark Best</t>
+          <t>Maxwell Willmott</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Special rule / Pending Audit</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Transferred from CI to Bangor on 2nd June 2026</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Matt Owen</t>
+          <t>Mayur Nanjundaswamy</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>matthew owen</t>
+          <t>Mayur Kalkuni Nanjundaswamy</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4151,39 +4148,39 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Matthew Humphreys</t>
+          <t>MN Payickattuvelil</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Matthew Humphreys</t>
+          <t>Moncy Ninan Payickattuvelil</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Special rule / Pending Audit</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Regarded as registered for Instonians for 2026</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Max Willmott</t>
+          <t>Mo Aahil</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Maxwell Willmott</t>
+          <t>Mohamed Aahil</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4195,12 +4192,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mayur Nanjundaswamy</t>
+          <t>Mohamed Ismail</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Mayur Kalkuni Nanjundaswamy</t>
+          <t>Ismail Mohamed</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4217,12 +4214,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MN Payickattuvelil</t>
+          <t>Mohammed Agadi</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Moncy Ninan Payickattuvelil</t>
+          <t>Mohammed Nayeem Agadi</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4239,17 +4236,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mo Aahil</t>
+          <t>Mohammed Rakeeb</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mohamed Aahil</t>
+          <t>Mohammed Faizan Rakeeb</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4261,17 +4258,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mohamed Ismail</t>
+          <t>Mohammed Sameer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ismail Mohamed</t>
+          <t>Sameer Mohd</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4283,12 +4280,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mohammed Agadi</t>
+          <t>Mohammed Sanobar</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mohammed Nayeem Agadi</t>
+          <t>Mohammed Sanobar Nedumpurakkal Sainudheen</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4305,12 +4302,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mohammed Rakeeb</t>
+          <t>Mohan Raj</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mohammed Faizan Rakeeb</t>
+          <t>Mohan Raj Vijayakumar</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4327,17 +4324,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mohammed Sameer</t>
+          <t>Mohan Vijayakumar</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sameer Mohd</t>
+          <t>Mohan Raj Vijayakumar</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4349,12 +4346,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mohammed Sanobar</t>
+          <t>Mohd Faizan</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Mohammed Sanobar Nedumpurakkal Sainudheen</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4371,12 +4368,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Mohan Raj</t>
+          <t>Muhamma Ajmal</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mohan Raj Vijayakumar</t>
+          <t>Muhammad Ajmal</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4393,17 +4390,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mohan Vijayakumar</t>
+          <t>Muhammad Shujee</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mohan Raj Vijayakumar</t>
+          <t>Muhammad Shujee Ahmed</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4415,12 +4412,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mohd Faizan</t>
+          <t>Muhammed Hussain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Muhammad Faizan</t>
+          <t>Muhammad Hussain</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4437,12 +4434,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Muhamma Ajmal</t>
+          <t>Muhammed Nazar</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Muhammad Ajmal</t>
+          <t>Muhammed Salman Nazar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4459,17 +4456,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Muhammad Shujee</t>
+          <t>Muhammed Salman</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Muhammad Shujee Ahmed</t>
+          <t>Muhammed salman Nazar</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4481,12 +4478,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Muhammed Hussain</t>
+          <t>Murali Devarapally</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Muhammad Hussain</t>
+          <t>Murali kumar Devarapally</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4503,12 +4500,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Muhammed Nazar</t>
+          <t>Muthukaruppan Paganeri</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Muhammed Salman Nazar</t>
+          <t>Muthukaruppan Subbiah Paganeri</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4525,12 +4522,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Muhammed Salman</t>
+          <t>NagaSuprasanna Nagineni</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Muhammed salman Nazar</t>
+          <t>Prasanna Nagineni</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4547,12 +4544,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Murali Devarapally</t>
+          <t>Nandeesh Nagaraju</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Murali kumar Devarapally</t>
+          <t>Nandeesh Mathahalli Nagaraju</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4569,17 +4566,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Muthukaruppan Paganeri</t>
+          <t>Nikhil Nair</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Muthukaruppan Subbiah Paganeri</t>
+          <t>Nikhil Muraleedharan Nair</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4591,12 +4588,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NagaSuprasanna Nagineni</t>
+          <t>Nithin k Babu</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Prasanna Nagineni</t>
+          <t>Nithin Babu</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4613,17 +4610,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Nandeesh Nagaraju</t>
+          <t>Olie Mann</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Nandeesh Mathahalli Nagaraju</t>
+          <t>Oliver Mann</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4635,12 +4632,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nicholas Bennett</t>
+          <t>Oliver Gibson</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Nick Bennett</t>
+          <t>Oliver S Gibson</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4657,17 +4654,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Nikhil Nair</t>
+          <t>Ollie Hull</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Nikhil Muraleedharan Nair</t>
+          <t>Oliver Hull</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4679,12 +4676,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Nithin k Babu</t>
+          <t>Ollie Hume</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Nithin Babu</t>
+          <t>Oliver Hume</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4701,12 +4698,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Olie Mann</t>
+          <t>Omar Muhammad Bhandara</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Oliver Mann</t>
+          <t>Muhammad Bhandara</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4723,12 +4720,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Oliver Gibson</t>
+          <t>P Spee</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Oliver S Gibson</t>
+          <t>Penny Speer</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4745,12 +4742,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Ollie Hull</t>
+          <t>Paddy Beverland</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Oliver Hull</t>
+          <t>Patrick Beverland</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4767,12 +4764,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ollie Hume</t>
+          <t>Paddy Carson</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Oliver Hume</t>
+          <t>Patrick Carson</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4789,17 +4786,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Omar Muhammad Bhandara</t>
+          <t>Pallav Saran</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Muhammad Bhandara</t>
+          <t>Pallav Saran</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4811,12 +4808,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>P Spee</t>
+          <t>Pankaj Pathak</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Penny Speer</t>
+          <t>Pankaj Kumar Pathak</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4833,12 +4830,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Paddy Beverland</t>
+          <t>Pat Lutton</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Patrick Beverland</t>
+          <t>Patrick Lutton</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4855,12 +4852,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Paddy Carson</t>
+          <t>Patrick Heron</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Patrick Carson</t>
+          <t>P Heron</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4877,12 +4874,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Pallav Saran</t>
+          <t>Pavan Karthik</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pallav Saran</t>
+          <t>Pavan Karthik Bade</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4899,12 +4896,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Pankaj Pathak</t>
+          <t>Peter Ward</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pankaj Kumar Pathak</t>
+          <t>Pete Ward</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4921,17 +4918,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Pat Lutton</t>
+          <t>Phil Skillen</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Patrick Lutton</t>
+          <t>Philip Skillen</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4943,17 +4940,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Patrick Heron</t>
+          <t>Phil Stewart</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>P Heron</t>
+          <t>Philip Stewart</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -4965,17 +4962,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Pavan Karthik</t>
+          <t>Philip Rodgers</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Pavan Karthik Bade</t>
+          <t>Phil Rodgers</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4987,12 +4984,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Peter Ward</t>
+          <t>Piyush Yalamanchili</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Pete Ward</t>
+          <t>Piyush Sri Siddhi Yalamanchili</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5009,17 +5006,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Phil Skillen</t>
+          <t>Poorna Shanmugam</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Philip Skillen</t>
+          <t>Poorna Kumar Shanmugam</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5031,17 +5028,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Phil Stewart</t>
+          <t>Prajin Chemmayath Gopi</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Philip Stewart</t>
+          <t>Prajin Gopi</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5053,17 +5050,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Philip Rodgers</t>
+          <t>Praveen A Punithan</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Phil Rodgers</t>
+          <t>Praveen Angalaparameswari Punithan</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5075,12 +5072,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Piyush Yalamanchili</t>
+          <t>Praveen Shashidara</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Piyush Sri Siddhi Yalamanchili</t>
+          <t>Praveen Bangalore Shashidara</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5097,12 +5094,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Poorna Shanmugam</t>
+          <t>Prithiv Raaj</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Poorna Kumar Shanmugam</t>
+          <t>Prithiv Raaj V S</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5119,12 +5116,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Prajin Chemmayath Gopi</t>
+          <t>Priyank Lakhani</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Prajin Gopi</t>
+          <t>Priyankbhai Lakhani</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5141,12 +5138,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Praveen A Punithan</t>
+          <t>PT Aston</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Praveen Angalaparameswari Punithan</t>
+          <t>Paul Aston</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5163,17 +5160,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Praveen Shashidara</t>
+          <t>Raghu Sathya</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Praveen Bangalore Shashidara</t>
+          <t>Raghuram Sathyanarayana</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5185,12 +5182,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Prithiv Raaj</t>
+          <t>Rahul Baghel</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Prithiv Raaj V S</t>
+          <t>Rahul Singh Baghel</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5207,12 +5204,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Priyank Lakhani</t>
+          <t>Rajesh Thuraiyur Moorthy</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Priyankbhai Lakhani</t>
+          <t>Rajesh Thuraiyur</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5229,12 +5226,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PT Aston</t>
+          <t>Rakeeb Raheman</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Paul Aston</t>
+          <t>Rakeeb Ahmed Tirupattur Raheman</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5251,17 +5248,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Raghu Sathya</t>
+          <t>Rakesh Singh</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Raghuram Sathyanarayana</t>
+          <t>Rakesh Kumar Singh</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5273,12 +5270,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Rahul Baghel</t>
+          <t>Rameez Hashmi</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Rahul Singh Baghel</t>
+          <t>Syed Rameez Ali Hashmi</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5295,12 +5292,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Rajesh Thuraiyur Moorthy</t>
+          <t>Randeep Singh</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Rajesh Thuraiyur</t>
+          <t>RANDEEP Singh Duggal</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5317,12 +5314,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Rakeeb Raheman</t>
+          <t>Ranju Kizhakkekutt</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Rakeeb Ahmed Tirupattur Raheman</t>
+          <t>Ranju Kizhakkekutt Mathew</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5339,12 +5336,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Rakesh Singh</t>
+          <t>Renju John</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Rakesh Kumar Singh</t>
+          <t>Renju Vadakkeparampil John</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5361,12 +5358,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Rameez Hashmi</t>
+          <t>Reuben Edmondson</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Syed Rameez Ali Hashmi</t>
+          <t>Richard Reuben Edmondson</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5383,12 +5380,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Randeep Singh</t>
+          <t>Reuben Wilson</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RANDEEP Singh Duggal</t>
+          <t>Reuben Logan-Wilson</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5405,12 +5402,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ranju Kizhakkekutt</t>
+          <t>Richard Gould Hocking</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ranju Kizhakkekutt Mathew</t>
+          <t>Richard Harry Gould Hocking</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5427,17 +5424,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Renju John</t>
+          <t>Rick McKibbin</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Renju Vadakkeparampil John</t>
+          <t>Richard Mckibbin</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5449,12 +5446,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Reuben Edmondson</t>
+          <t>Ricky Lavakumar</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Richard Reuben Edmondson</t>
+          <t>Ricky Bopanna Kanathanda Lavakumar</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5471,12 +5468,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Reuben Wilson</t>
+          <t>Rijo George</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Reuben Logan-Wilson</t>
+          <t>Rijo George Porathoor</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5493,12 +5490,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Richard Gould Hocking</t>
+          <t>Rishik Yalamanchili</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Richard Harry Gould Hocking</t>
+          <t>Rishik Sri Sai Yalamanchili</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5515,17 +5512,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Rick McKibbin</t>
+          <t>Robert Dougan</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Richard Mckibbin</t>
+          <t>Robert Wilfred Dougan</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5537,12 +5534,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Ricky Lavakumar</t>
+          <t>Roney Mathew</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ricky Bopanna Kanathanda Lavakumar</t>
+          <t>Joseph Mathew</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5559,12 +5556,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Rijo George</t>
+          <t xml:space="preserve">Ronnie Bell </t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rijo George Porathoor</t>
+          <t xml:space="preserve">Ron Bell </t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5581,12 +5578,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Rishik Yalamanchili</t>
+          <t>Ross Adair</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Rishik Sri Sai Yalamanchili</t>
+          <t>George Adair</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5603,17 +5600,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Robert Dougan</t>
+          <t>Rufi Shaikh</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Robert Wilfred Dougan</t>
+          <t>Rufi Raheel Shaikh</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5625,12 +5622,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Roney Mathew</t>
+          <t>RV John</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Joseph Mathew</t>
+          <t>Renju Vadakkeparampil john</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5647,12 +5644,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ronnie Bell </t>
+          <t>S Kashikar</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ron Bell </t>
+          <t>Suprit Kashikar</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5669,12 +5666,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ross Adair</t>
+          <t>S Malik</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>George Adair</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5691,17 +5688,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Rufi Shaikh</t>
+          <t>S Sunil kumar</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Rufi Raheel Shaikh</t>
+          <t>Sidharth Sunil Kumar Swayam Prabha</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5713,12 +5710,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RV John</t>
+          <t>Sai Darshan</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Renju Vadakkeparampil john</t>
+          <t>Sai Kruthik Darshan</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5735,12 +5732,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S Kashikar</t>
+          <t>Sairam Kondapally</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Suprit Kashikar</t>
+          <t>Sai Ram Kondapally</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5757,12 +5754,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S Malik</t>
+          <t>Sam Gilliland</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Samuel Gilliland</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5779,17 +5776,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S Sunil kumar</t>
+          <t>Sameer Mohammad</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sidharth Sunil Kumar Swayam Prabha</t>
+          <t>Sameer Mohd</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5801,12 +5798,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Sai Darshan</t>
+          <t>Samuel McMillan</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sai Kruthik Darshan</t>
+          <t>Sam Mcmillan</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5823,12 +5820,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Sairam Kondapally</t>
+          <t>Sanjeev Menon</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sai Ram Kondapally</t>
+          <t>Sanjeev Sukumaran Menon</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5845,12 +5842,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Sam Gilliland</t>
+          <t>Sarath Sasi</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Samuel Gilliland</t>
+          <t>Sharath Sadanandan</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5867,17 +5864,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Sameer Mohammad</t>
+          <t>Sarav Palaniappan</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Sameer Mohd</t>
+          <t>Saravanan Palaniappan</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -5889,12 +5886,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Samuel McMillan</t>
+          <t>Saravana Chandrasekaran</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Sam Mcmillan</t>
+          <t>Saravana Maadavan Chandrasekaran</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5911,12 +5908,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Sanjeev Menon</t>
+          <t>Sasha Sinclair</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Sanjeev Sukumaran Menon</t>
+          <t>Aleksander StClair</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5933,12 +5930,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Sarath Sasi</t>
+          <t>Sasha StClair</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sharath Sadanandan</t>
+          <t>Aleksander Stclair</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5955,12 +5952,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sarav Palaniappan</t>
+          <t>Sathish Manohar</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Saravanan Palaniappan</t>
+          <t>Sathish Kumar Manohar</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5977,12 +5974,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Saravana Chandrasekaran</t>
+          <t>Satya Edubilli</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Saravana Maadavan Chandrasekaran</t>
+          <t>Satyannarayana Edubilli</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5999,12 +5996,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Sasha Sinclair</t>
+          <t>Scott McClelland</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Aleksander StClair</t>
+          <t>Thomas McClelland</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6021,12 +6018,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sasha StClair</t>
+          <t>Sebastian Yeates</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Aleksander Stclair</t>
+          <t>Seb Yeates</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6043,12 +6040,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Sathish Manohar</t>
+          <t>Seby Best</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Sathish Kumar Manohar</t>
+          <t>Seb Best</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6065,17 +6062,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Satya Edubilli</t>
+          <t>Selvaraj Muthusivan</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Satyannarayana Edubilli</t>
+          <t>Muthusivan Selvaraj</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6087,12 +6084,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Scott McClelland</t>
+          <t>Senthilkumar Ponnuchamy</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Thomas McClelland</t>
+          <t>Selvakumar Ponnuchamy Senthil Kumar</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6109,12 +6106,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Sebastian Yeates</t>
+          <t>Senthilkumar Santhanakrishnan</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Seb Yeates</t>
+          <t>Senthil Kumar Santhana Krishnan</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6131,12 +6128,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Seby Best</t>
+          <t>Shah Ata</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Seb Best</t>
+          <t>Shah Muhammad Ata</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6153,17 +6150,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Selvaraj Muthusivan</t>
+          <t>Shahid Malik</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Muthusivan Selvaraj</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6175,12 +6172,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Senthilkumar Ponnuchamy</t>
+          <t>Shahmeer Khan</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Selvakumar Ponnuchamy Senthil Kumar</t>
+          <t>Shahmir Khan</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6197,12 +6194,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Senthilkumar Santhanakrishnan</t>
+          <t>Shakeel ahmed SHAIKH</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Senthil Kumar Santhana Krishnan</t>
+          <t>Shakeel Shaikh</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6219,12 +6216,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Shah Ata</t>
+          <t>Shami Hasan</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Shah Muhammad Ata</t>
+          <t>Shamim Hasan Sami</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6241,12 +6238,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Shahid Malik</t>
+          <t>Shankar Uthayashankar</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Uthayashankar Selvaratnam</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6263,12 +6260,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Shahmeer Khan</t>
+          <t>Shay Malik</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Shahmir Khan</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6285,12 +6282,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Shakeel ahmed SHAIKH</t>
+          <t>Sheree McAleenan</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Shakeel Shaikh</t>
+          <t>Sheree Marie McAleenan</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6307,12 +6304,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Shami Hasan</t>
+          <t>Sidharth Sunil</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Shamim Hasan Sami</t>
+          <t>Sidharth Sunil Kumar Swayam Prabha</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6329,12 +6326,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Shankar Uthayashankar</t>
+          <t>Sidharth Sunil kumar</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Uthayashankar Selvaratnam</t>
+          <t>Sidharth Sunil Kumar Swayam Prabha</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6351,12 +6348,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Shay Malik</t>
+          <t>Sidharth Suresh Kumar</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Sidharth Kumar</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6373,12 +6370,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Sheree McAleenan</t>
+          <t>Simon-Peter Maxwell</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Sheree Marie McAleenan</t>
+          <t>Simon Peter Maxwell</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6395,12 +6392,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Sidharth Sunil</t>
+          <t>SM Mitchell</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sidharth Sunil Kumar Swayam Prabha</t>
+          <t>Scott Mitchell</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6417,12 +6414,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Sidharth Sunil kumar</t>
+          <t>Sohail Khan</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Sidharth Sunil Kumar Swayam Prabha</t>
+          <t>Sohailkhan Markhail</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6439,12 +6436,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Sidharth Suresh Kumar</t>
+          <t>Soma Raman</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sidharth Kumar</t>
+          <t>Aaditya Raman Soma Sundaram</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6461,12 +6458,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Simon-Peter Maxwell</t>
+          <t>Sreejesh Nair</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Simon Peter Maxwell</t>
+          <t>Sreejesh Krishnan Nair</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6483,12 +6480,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>SM Mitchell</t>
+          <t>Sri Tummala</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Scott Mitchell</t>
+          <t>Tummala Srivinayteja</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6505,12 +6502,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Sohail Khan</t>
+          <t>Srinuvasarao Nadakuditi</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sohailkhan Markhail</t>
+          <t>Srinuvasarao N</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6527,12 +6524,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Soma Raman</t>
+          <t>Stanley John</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Aaditya Raman Soma Sundaram</t>
+          <t>Stanley Mathew John</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6549,12 +6546,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Sreejesh Nair</t>
+          <t>Steph Butler</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Sreejesh Krishnan Nair</t>
+          <t>Stephanie Butler</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6571,17 +6568,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sri Tummala</t>
+          <t>Stevie Saul</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Tummala Srivinayteja</t>
+          <t>Steven Saul</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6593,12 +6590,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Srinuvasarao Nadakuditi</t>
+          <t>Stuart Johnstone</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Srinuvasarao N</t>
+          <t>Stewart Johnston</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6615,17 +6612,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Stanley John</t>
+          <t>Subhilesh P S</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Stanley Mathew John</t>
+          <t>Subhilesh Ps</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6637,12 +6634,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Steph Butler</t>
+          <t>Sufyan Muhammad</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Stephanie Butler</t>
+          <t>Muhammad Sufyan</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6659,17 +6656,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Stevie Saul</t>
+          <t>Sumesh Mohanan</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Steven Saul</t>
+          <t>Sumesh Kumar Mohanan</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6681,12 +6678,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Stuart Johnstone</t>
+          <t>Sunson Stephenson</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Stewart Johnston</t>
+          <t>Sunson Stephen</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6703,17 +6700,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Subhilesh P S</t>
+          <t>Suresh Gopidi</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Subhilesh Ps</t>
+          <t>Suresh Reddy Gopidi</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6725,12 +6722,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Sufyan Muhammad</t>
+          <t>Surya Saneesh</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Muhammad Sufyan</t>
+          <t>Suryakrishna Saneesh</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6747,12 +6744,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Sumesh Mohanan</t>
+          <t>Surya Tummala</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Sumesh Kumar Mohanan</t>
+          <t>Surya Pavan Teja Tummala</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6769,12 +6766,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Sunson Stephenson</t>
+          <t>Syam Rajmohan</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Sunson Stephen</t>
+          <t>Syam Raj</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6791,12 +6788,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Suresh Gopidi</t>
+          <t>Talha Shah</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Suresh Reddy Gopidi</t>
+          <t>Syed Talha Ahmed Shah</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6813,12 +6810,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Surya Saneesh</t>
+          <t>Teddy McIlwaine</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Suryakrishna Saneesh</t>
+          <t>Teddy McIlwaine</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6835,17 +6832,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Surya Tummala</t>
+          <t>Thamil Maran</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Surya Pavan Teja Tummala</t>
+          <t>Thamilmaran Raju</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6857,12 +6854,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Syam Rajmohan</t>
+          <t>Thomas Copeland</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Syam Raj</t>
+          <t>Thomas Graeme Copeland</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6879,12 +6876,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Talha Shah</t>
+          <t>Thomas ET</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Syed Talha Ahmed Shah</t>
+          <t>Thomas Eapen tharkolil</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6901,12 +6898,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Teddy McIlwaine</t>
+          <t>Tim Browne</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Teddy McIlwaine</t>
+          <t>Timothy Browne</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6923,17 +6920,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Thamil Maran</t>
+          <t>Tim Scott</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Thamilmaran Raju</t>
+          <t>Timothy Scott</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6945,12 +6942,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Thomas Copeland</t>
+          <t>Timmy Evans</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Thomas Graeme Copeland</t>
+          <t>Timothy Evans</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6967,12 +6964,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Thomas ET</t>
+          <t>TJ McCavera</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Thomas Eapen tharkolil</t>
+          <t>Thomas Mccavera</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6989,12 +6986,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Tim Browne</t>
+          <t>Tom Jefferson</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Timothy Browne</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7011,12 +7008,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Tim Evans</t>
+          <t>Tom Macauley</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Timothy Evans</t>
+          <t>Thomas Macauley</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7033,12 +7030,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Tim Scott</t>
+          <t>Tom Mayes</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Timothy Scott</t>
+          <t>Thomas Mayes</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7055,12 +7052,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Timmy Evans</t>
+          <t>Tom Nicholson</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Timothy Evans</t>
+          <t>Thomas Nicholson</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7077,12 +7074,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>TJ McCavera</t>
+          <t>Tom Shearer</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Thomas Mccavera</t>
+          <t>Thomas Shearer</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7099,12 +7096,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Tom Jefferson</t>
+          <t>Tom Stevenson</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Thomas Stevenson</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7121,12 +7118,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Tom Macauley</t>
+          <t>Tony Adams</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Thomas Macauley</t>
+          <t>Anthony Adams</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7143,12 +7140,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Tom Mayes</t>
+          <t>Tony Louis</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Thomas Mayes</t>
+          <t>Tony Louis Pathippilly</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7165,12 +7162,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Tom Nicholson</t>
+          <t>Tulasi Thatavarthi</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Thomas Nicholson</t>
+          <t>Tulasi Gangadhar Thatavarthi</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7187,12 +7184,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Tom Shearer</t>
+          <t>Veerendra Nagari</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Thomas Shearer</t>
+          <t>Veerendra Babu Nagari</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7209,12 +7206,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Tom Stevenson</t>
+          <t>Veideek Agarwal</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Thomas Stevenson</t>
+          <t>Veideek Krishna Agarwal</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7231,17 +7228,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Tony Adams</t>
+          <t>Venkateswararao Jyothi</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Anthony Adams</t>
+          <t>Venkat Jyothi</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7253,12 +7250,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Tony Louis</t>
+          <t>Venky Valleri</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Tony Louis Pathippilly</t>
+          <t>Venkatesh Valleri</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7275,12 +7272,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Tulasi Thatavarthi</t>
+          <t>Vichu Cassi</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Tulasi Gangadhar Thatavarthi</t>
+          <t>Vishnu Chirayil Manoj</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7297,12 +7294,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Veerendra Nagari</t>
+          <t>Vidhath Geddam</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Veerendra Babu Nagari</t>
+          <t>Maanvik Vidhath Geddam</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7319,12 +7316,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Veideek Agarwal</t>
+          <t>Vineesh Peter</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Veideek Krishna Agarwal</t>
+          <t>Vineesh Peter Tx</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7341,17 +7338,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Venkateswararao Jyothi</t>
+          <t>Vinesh Pathiyil Varghese</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Venkat Jyothi</t>
+          <t>Vinesh Varghese</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7363,17 +7360,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Venky Valleri</t>
+          <t>Vinosh Mohandas</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Venkatesh Valleri</t>
+          <t>Vinosh Mohanadas</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7385,12 +7382,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Vichu Cassi</t>
+          <t>Vinoth Srinivasan</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Vishnu Chirayil Manoj</t>
+          <t>Vinoth Kumar Srinivasan</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7407,12 +7404,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Vidhath Geddam</t>
+          <t>Vipin Kumar</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Maanvik Vidhath Geddam</t>
+          <t>Vipin kumar Vadakkechirayil vijayan</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7429,12 +7426,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Vineesh Peter</t>
+          <t>Visakh Joseph</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Vineesh Peter Tx</t>
+          <t>Visakh peter Joseph</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7451,12 +7448,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Vinesh Pathiyil Varghese</t>
+          <t>Vishnu Korath</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Vinesh Varghese</t>
+          <t>Vishnu Viswanadh Korath</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7473,17 +7470,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vinosh Mohandas</t>
+          <t>Vishnu Prasad</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Vinosh Mohanadas</t>
+          <t>Vishnu Prasad Naduviledathu Janardhanan</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7495,12 +7492,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Vinoth Srinivasan</t>
+          <t>Vishwanatha Urs</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Vinoth Kumar Srinivasan</t>
+          <t>Vishwanatha Kemparaje Urs</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7517,12 +7514,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Vipin Kumar</t>
+          <t>Viswath Balaguru</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Vipin kumar Vadakkechirayil vijayan</t>
+          <t>Viswath Ramanujam Balaguru</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7539,17 +7536,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Visakh Joseph</t>
+          <t>Will Koorts</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Visakh peter Joseph</t>
+          <t>Willem Koorts</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -7561,17 +7558,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Vishnu Korath</t>
+          <t>Will Simpson</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Vishnu Viswanadh Korath</t>
+          <t>William Simpson</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7583,12 +7580,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Vishnu Prasad</t>
+          <t>William Park</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Vishnu Prasad Naduviledathu Janardhanan</t>
+          <t>Will Park</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7605,12 +7602,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Vishwanatha Urs</t>
+          <t>Willy Graham</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Vishwanatha Kemparaje Urs</t>
+          <t>William Graham</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7627,12 +7624,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Viswath Balaguru</t>
+          <t>Yashwanth Moluguri</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Viswath Ramanujam Balaguru</t>
+          <t>Yashwanth Kumar Moluguri</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7649,17 +7646,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Will Koorts</t>
+          <t>Zac Solomon</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Willem Koorts</t>
+          <t>Isaac Solomon</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7671,17 +7668,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Will Simpson</t>
+          <t>Zach Robinson</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>William Simpson</t>
+          <t>Zachary Robinson</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7693,12 +7690,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>William Park</t>
+          <t>Zach Watson</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Will Park</t>
+          <t>William zach Watson</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7715,12 +7712,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Willy Graham</t>
+          <t>Zafar Ali</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>William Graham</t>
+          <t>Zafar ali Zafar ali</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7737,12 +7734,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Yashwanth Moluguri</t>
+          <t>Zaheer Gondal</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Yashwanth Kumar Moluguri</t>
+          <t>Zaheer Ahmad Gondal</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7759,12 +7756,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Zac Solomon</t>
+          <t>Praveen Kapala</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Isaac Solomon</t>
+          <t>Praveen kumar Kapala</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7781,12 +7778,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Zach Robinson</t>
+          <t>Gokula Gopala Krishnan</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Zachary Robinson</t>
+          <t>Gokula Kannan Gopala Krishnan</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7803,12 +7800,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Zach Watson</t>
+          <t>Tom Buchanan</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>William zach Watson</t>
+          <t>Tom Daniel Buchanan</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7825,12 +7822,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Zafar Ali</t>
+          <t>Thomas Varghese</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Zafar ali Zafar ali</t>
+          <t>Thomas Cheethaparambill varghese</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7847,12 +7844,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Zaheer Gondal</t>
+          <t>Sam Cave</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Zaheer Ahmad Gondal</t>
+          <t>Samuel Cave</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7869,12 +7866,12 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Praveen Kapala</t>
+          <t>Syam Kumar</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Praveen kumar Kapala</t>
+          <t>Syam Kumar Sasidharan Nair</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7891,232 +7888,232 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Gokula Gopala Krishnan</t>
+          <t>Francis Collins</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Gokula Kannan Gopala Krishnan</t>
+          <t>Francis GJ Collins</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Tom Buchanan</t>
+          <t>Amal Matthew Muttathupadam</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tom Daniel Buchanan</t>
+          <t>Amal Mathew Muttathupadam</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Thomas Varghese</t>
+          <t>Tim Evans</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Thomas Cheethaparambill varghese</t>
+          <t>Timothy Evans</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Sam Cave</t>
+          <t>Harry Zimmerman</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Samuel Cave</t>
+          <t>Harry Zimmermann</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Syam Kumar</t>
+          <t>Darshan Kumar</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Syam Kumar Sasidharan Nair</t>
+          <t>Darshan Hanumanth kumar</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Francis Collins</t>
+          <t xml:space="preserve">Shahbaz Bhandara </t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Francis GJ Collins</t>
+          <t>Shahbaz Umar Jalal Bhandara</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Amal Matthew Muttathupadam</t>
+          <t>Jaya Sukhavasi</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Amal Mathew Muttathupadam</t>
+          <t>Jaya Surya Sukhavasi</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Tim Evans</t>
+          <t>Venkataharish Rayi</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Timothy Evans</t>
+          <t>Harish Rayi</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Harry Zimmerman</t>
+          <t>Kavyadeep Singh</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Harry Zimmermann</t>
+          <t>Kavyadeep Bhamra</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Darshan Kumar</t>
+          <t>Josh McClune</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Darshan Hanumanth kumar</t>
+          <t>Joshua McClune</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shahbaz Bhandara </t>
+          <t>Fergus Emmett</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Shahbaz Umar Jalal Bhandara</t>
+          <t>Frgus Emmett</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8133,12 +8130,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Jaya Sukhavasi</t>
+          <t>Izzy Jones</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Jaya Surya Sukhavasi</t>
+          <t>Isabelle Jones</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8155,12 +8152,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Venkataharish Rayi</t>
+          <t>Susie McCollum</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Harish Rayi</t>
+          <t>Susanna McCollum</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8177,12 +8174,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Kavyadeep Singh</t>
+          <t>Abbie Gunning</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Kavyadeep Bhamra</t>
+          <t>Abigail Gunning</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8199,12 +8196,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Josh McClune</t>
+          <t>Aimee Logan</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Joshua McClune</t>
+          <t>Aimeee Logan</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8221,12 +8218,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Fergus Emmett</t>
+          <t>Alex Atkinson</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Frgus Emmett</t>
+          <t>Alexandra Atkinson</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8243,12 +8240,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Izzy Jones</t>
+          <t>Ellie Murray</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Isabelle Jones</t>
+          <t>Ellen Murray</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8265,12 +8262,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Susie McCollum</t>
+          <t>Vismithaa Pandiaraj</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Susanna McCollum</t>
+          <t>Vismithaa Sai Pandiaraj</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8287,12 +8284,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Abbie Gunning</t>
+          <t>Johnny Shannon</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Abigail Gunning</t>
+          <t>Jonny Shannon</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8309,12 +8306,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Aimee Logan</t>
+          <t>Nathan McCurry</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Aimeee Logan</t>
+          <t>Nathan McCurry</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8324,19 +8321,19 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Sport80 typo fix)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Alex Atkinson</t>
+          <t>Will Noffke</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Alexandra Atkinson</t>
+          <t>Will Noffkee</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8346,19 +8343,19 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Sport80 typo fix)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ellie Murray</t>
+          <t>Stephen Entwhistle</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Ellen Murray</t>
+          <t>Stephen Entwistle</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8368,19 +8365,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Sport80 typo fix)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Vismithaa Pandiaraj</t>
+          <t>Thomas Vidamour</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Vismithaa Sai Pandiaraj</t>
+          <t>Vhomas Tidamour</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8390,19 +8387,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Sport80 typo fix)</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Johnny Shannon</t>
+          <t>Tony Louis Pathipally</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Jonny Shannon</t>
+          <t>Tony Louis Pathippilly</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8412,19 +8409,19 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Transliteration fix)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Nathan McCurry</t>
+          <t>Henry O'Neill</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nathan McCurry</t>
+          <t>Henry O’Neill</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8434,19 +8431,19 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Added as per Wylie request (Apostrophe character fix)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Will Noffke</t>
+          <t>stuart COP</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Will Noffkee</t>
+          <t>Stuart Copeland</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8456,19 +8453,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Sport80 payment typo (truncated surname)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Stephen Entwhistle</t>
+          <t>Akaah Vega</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Stephen Entwistle</t>
+          <t>Akash Vega</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8478,19 +8475,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Sport80 payment typo (k/h keyboard slip)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Thomas Vidamour</t>
+          <t>Sandeep Srinivasan</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Vhomas Tidamour</t>
+          <t>Sandeep Ganesh Srinivasan</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8500,19 +8497,19 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Tony Louis Pathipally</t>
+          <t>James Magee</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tony Louis Pathippilly</t>
+          <t>James Magee Snr</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8522,19 +8519,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Transliteration fix)</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Henry O'Neill</t>
+          <t>Jack Kirkpatrick jnr</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Henry O’Neill</t>
+          <t>Jack Kirkpatrick Jnr</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8544,19 +8541,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Apostrophe character fix)</t>
+          <t>Case normalization for Jnr suffix</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>stuart COP</t>
+          <t>Jack Kirkpatrick snr</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Stuart Copeland</t>
+          <t>Jack Kirkpatrick Snr</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8566,19 +8563,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Sport80 payment typo (truncated surname)</t>
+          <t>Case normalization for Snr suffix</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Akaah Vega</t>
+          <t>Nicholas Bennett</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Akash Vega</t>
+          <t>Nick Bennett</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8588,19 +8585,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Sport80 payment typo (k/h keyboard slip)</t>
+          <t>Added for Ards and Donaghadee CC matching</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Sandeep Srinivasan</t>
+          <t>Muhammad Asif</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Sandeep Ganesh Srinivasan</t>
+          <t>Mohammad Asif</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8610,19 +8607,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for Belfast CC matching</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>James Magee</t>
+          <t>Nidheesh Thankachan</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>James Magee Snr</t>
+          <t>Nidheesh Vakkayil Thankachan</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8632,19 +8629,19 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for Ardent Blues CC matching</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick jnr</t>
+          <t>Sam McConnell</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick Jnr</t>
+          <t>Samuel McConnell</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8654,117 +8651,81 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Case normalization for Jnr suffix</t>
+          <t>Added for Templepatrick CC matching</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick snr</t>
+          <t>Aidan O'Gormon</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick Snr</t>
+          <t>Aidan O'Gorman</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Manual Map</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Case normalization for Snr suffix</t>
+          <t>NV Play scorecard spelling variant</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Aidan O'Gorman</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Aidan O'Gormon</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Men's</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Nicholas Bennett</t>
+          <t>Aidan OGormon</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Nick Bennett</t>
+          <t>Aidan O'Gorman</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Manual Map</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Added for Ards and Donaghadee CC matching</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Muhammad Asif</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Mohammad Asif</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Verified in Database</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Added for Belfast CC matching</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Nidheesh Thankachan</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Nidheesh Vakkayil Thankachan</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Verified in Database</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>Added for Ardent Blues CC matching</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Sam McConnell</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Samuel McConnell</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Verified in Database</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>Added for Templepatrick CC matching</t>
+          <t>NV Play scorecard spelling variant without apostrophe</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aidan O'Gorman</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Aidan OGormon</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Men's</t>
         </is>
       </c>
     </row>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,6 +26,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -54,9 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,37 +441,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Input Name (Scorecard/Stats)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Official Registered Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Ledger Status Verification</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Registered Name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>NV Play Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -8328,12 +8334,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
+          <t>Will Noffkee</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
           <t>Will Noffke</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Will Noffkee</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8735,6 +8735,80 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Zach Cameron</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Zachary Cameron</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Manual Map</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>NV Play scorecard name for Zachary Cameron (CI)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Zachary Cameron</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Zach Cameron</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Zachery Cameron</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Zachary Cameron</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Manual Map</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Spelling variant for Zachary Cameron (CI)</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Zachary Cameron</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Zach Cameron</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G377"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8809,6 +8809,43 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Cameron  Kane</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Cameron Kane</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Manual Map</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>NV Play scorecard double-space variant</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Cameron Kane</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Cameron  Kane</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Added for Ards and Donaghadee CC matching</t>
+          <t>Ards &amp; Donaghadee Cricket Club (2021113018)</t>
         </is>
       </c>
     </row>
@@ -8843,6 +8843,50 @@
       <c r="G378" t="inlineStr">
         <is>
           <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Alec Stuart</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Alex Stuart</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Verified in Database</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Holywood 1881 Cricket Club (2021114359)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Sameer Mohammed</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Sameer Mohd</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Verified in Database</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Belfast Cricket Club (2021113239)</t>
         </is>
       </c>
     </row>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G380"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1646,12 +1646,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Callum Weir</t>
+          <t>Calum McCandless</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>John Weir</t>
+          <t>C McCandless</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">this is the Derriaghy Callum Weir </t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Calum McCandless</t>
+          <t>Charles Shannon</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C McCandless</t>
+          <t>Charlie Shannon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1690,12 +1690,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Charles Shannon</t>
+          <t>Charlie Duncan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charlie Shannon</t>
+          <t>Charles Duncan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1712,12 +1712,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Charlie Duncan</t>
+          <t>Charlie Monro</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Charles Duncan</t>
+          <t>Charles Monro</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Charlie Monro</t>
+          <t>Chris Dempsey</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Charles Monro</t>
+          <t>Christopher Dempsey</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1756,12 +1756,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chris Dempsey</t>
+          <t>Chris Dougherty</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Christopher Dempsey</t>
+          <t>Christopher Dougherty</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1778,12 +1778,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chris Dougherty</t>
+          <t>Chris Keenan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Christopher Dougherty</t>
+          <t>Christopher Keenan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Chris Keenan</t>
+          <t>Chris Koorts</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Christopher Keenan</t>
+          <t>Christo Koorts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1822,17 +1822,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chris Koorts</t>
+          <t>Chris Pyper</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Christo Koorts</t>
+          <t>Christopher Pyper</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1844,17 +1844,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chris Pyper</t>
+          <t>Chris Robinson</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Christopher Pyper</t>
+          <t>Christopher Robinson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1866,12 +1866,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chris Robinson</t>
+          <t>Chris Walton</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Christopher Robinson</t>
+          <t>Christopher Walton</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1888,12 +1888,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chris Walton</t>
+          <t>Chris Wilson</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Christopher Walton</t>
+          <t>John Wilson</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1910,17 +1910,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Chris Wilson</t>
+          <t>Christoffel Phillippus Klijnhans</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>John Wilson</t>
+          <t>Cp Klijnhans</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1932,17 +1932,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Christoffel Phillippus Klijnhans</t>
+          <t>Christopher Cahoon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cp Klijnhans</t>
+          <t>Chris Cahoon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Christopher Cahoon</t>
+          <t>Christopher Elliott</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chris Cahoon</t>
+          <t>Chris Elliott</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1976,17 +1976,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Christopher Elliott</t>
+          <t>Christopher Whitten</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chris Elliott</t>
+          <t>Chris Whitten</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1998,17 +1998,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Christopher Whitten</t>
+          <t>CJ Van der Walt</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Chris Whitten</t>
+          <t>Cornelius Van Der Walt</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2020,12 +2020,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CJ Van der Walt</t>
+          <t>Dan Soper</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cornelius Van Der Walt</t>
+          <t>Daniel Soper</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2042,12 +2042,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dan Soper</t>
+          <t>Daniel Fletcher</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Daniel Soper</t>
+          <t>Dan Fletcher</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2064,12 +2064,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Daniel Fletcher</t>
+          <t>Daniel Greenaway</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dan Fletcher</t>
+          <t>Dan Greenaway</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Daniel Greenaway</t>
+          <t>Danny Cooper</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dan Greenaway</t>
+          <t>Daniel Cooper</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2108,12 +2108,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Danny Cooper</t>
+          <t>Darshan Nair</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daniel Cooper</t>
+          <t>Darshan Dinesh Nair</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2130,12 +2130,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Darshan Nair</t>
+          <t>David O’Sullivan</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Darshan Dinesh Nair</t>
+          <t>David O'Sullivan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2152,12 +2152,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>David O'Sullivan</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>David O’Sullivan</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>David O'Sullivan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2174,17 +2174,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>David O'Sullivan</t>
+          <t>Davy Glover</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>David O’Sullivan</t>
+          <t>David Glover</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2196,17 +2196,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Davy Glover</t>
+          <t>Davy Harris</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>David Glover</t>
+          <t>David Harris</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2218,17 +2218,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Davy Harris</t>
+          <t>Davy Scott</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>David Harris</t>
+          <t>David Scott</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2240,17 +2240,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Davy Scott</t>
+          <t>Dawood Khan</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>David Scott</t>
+          <t>Dawood Ahmed Khan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2262,12 +2262,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Dawood Khan</t>
+          <t>Dayananda Gowdappa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dawood Ahmed Khan</t>
+          <t>Dayananda Markuli Gowdappa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2284,12 +2284,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dayananda Gowdappa</t>
+          <t>Dennis Thanivelil</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dayananda Markuli Gowdappa</t>
+          <t>Dennis Varghese Thanivelil</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dennis Thanivelil</t>
+          <t>Dennis Varghese</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2328,12 +2328,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dennis Varghese</t>
+          <t>Denny Andrews Abraham</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dennis Varghese Thanivelil</t>
+          <t>Denny Abraham</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Denny Andrews Abraham</t>
+          <t>Dhuvi Prattipati</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Denny Abraham</t>
+          <t>Dhuvi Thanik Prattipati</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2372,12 +2372,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dhuvi Prattipati</t>
+          <t>Dillu</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dhuvi Thanik Prattipati</t>
+          <t xml:space="preserve">Dhilneesh Joseph </t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2394,12 +2394,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dillu</t>
+          <t>Dino James</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dhilneesh Joseph </t>
+          <t>Dino Shiju James</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dino James</t>
+          <t>Dushyanth Bommana</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dino Shiju James</t>
+          <t>Dushyanth Reddy Bommana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2438,12 +2438,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dushyanth Bommana</t>
+          <t>Eddie Hawkins</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dushyanth Reddy Bommana</t>
+          <t>Edward Hawkins</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2460,12 +2460,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Eddie Hawkins</t>
+          <t>Eddie Wilson</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Edward Hawkins</t>
+          <t>Edward Wilson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2482,12 +2482,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Eddie Wilson</t>
+          <t>Eli Marshall</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Edward Wilson</t>
+          <t>Elijah Marshall</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2504,12 +2504,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Eli Marshall</t>
+          <t>F Monson</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Elijah Marshall</t>
+          <t>Finlay Monson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2526,12 +2526,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>F Monson</t>
+          <t>Faizan Muhammad</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Finlay Monson</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2548,12 +2548,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Faizan Muhammad</t>
+          <t>Felix Loebneu</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Muhammad Faizan</t>
+          <t>Felix Loebnau</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2570,12 +2570,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Felix Loebneu</t>
+          <t>Finn Garrett</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Felix Loebnau</t>
+          <t>Finn Garrett Jowsey</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2592,12 +2592,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Finn Garrett</t>
+          <t>Finn O'Hara</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Finn Garrett Jowsey</t>
+          <t>Finn Ohara</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2614,12 +2614,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Finn O'Hara</t>
+          <t>Firose Abdul Rasheed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Finn Ohara</t>
+          <t>Firose Abdul Rasheed Amila Beevi</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2636,12 +2636,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Firose Abdul Rasheed</t>
+          <t>Frazer McKane</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Firose Abdul Rasheed Amila Beevi</t>
+          <t>Frazer J McKane</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Frazer McKane</t>
+          <t>Gladson David George</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Frazer J McKane</t>
+          <t>Gladson George</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2680,12 +2680,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gladson David George</t>
+          <t>Gopa Krishna</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Gladson George</t>
+          <t>Gopal Krishna Budagatla</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gopa Krishna</t>
+          <t>Gopal Krishna</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gopal Krishna</t>
+          <t>Gopal Krishna Budagatle</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2746,17 +2746,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatle</t>
+          <t>Gowri Arivukkarasu</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Gopal Krishna Budagatla</t>
+          <t>Gowri Sankar Arivukkarasu</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gowri Arivukkarasu</t>
+          <t>Gowri Sankar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2790,17 +2790,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Gowri Sankar</t>
+          <t>Gus Farrell</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gowri Sankar Arivukkarasu</t>
+          <t>Angus Farrell</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2812,17 +2812,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gus Farrell</t>
+          <t>Hafis Siyad</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Angus Farrell</t>
+          <t>Muhammed Hafis Siyad</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Hafis Siyad</t>
+          <t>Hafiz Iqbal</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Muhammed Hafis Siyad</t>
+          <t>Hafiz M Waqas Iqbal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2856,12 +2856,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hafiz Iqbal</t>
+          <t>Harry Shaneesh</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hafiz M Waqas Iqbal</t>
+          <t>Harikrishna Saneesh</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2878,12 +2878,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Harry Shaneesh</t>
+          <t>Haseeb Syed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Harikrishna Saneesh</t>
+          <t>Syed Haseeb</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2900,12 +2900,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Haseeb Syed</t>
+          <t>Hemanth Suma</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Syed Haseeb</t>
+          <t>Hemanth Swamy Ekanthappa Suma</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2922,12 +2922,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Hemanth Suma</t>
+          <t>Henry Oliver Scott</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Hemanth Swamy Ekanthappa Suma</t>
+          <t>Henry Scott</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2944,12 +2944,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Henry Oliver Scott</t>
+          <t>Huzaifa Khalid</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Henry Scott</t>
+          <t>Syed Huzaifa Khalid</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2966,12 +2966,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Huzaifa Khalid</t>
+          <t>Ishan Pattnaik</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Syed Huzaifa Khalid</t>
+          <t>Ishan Chandra Pattnaik</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ishan Pattnaik</t>
+          <t>Ismail Sherzad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ishan Chandra Pattnaik</t>
+          <t>Ismail Ahmed Sherzad</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3010,12 +3010,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ismail Sherzad</t>
+          <t>J Hoffmeyr</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ismail Ahmed Sherzad</t>
+          <t>Jordaan Hofmeyr</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>J Hoffmeyr</t>
+          <t>J jose</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jordaan Hofmeyr</t>
+          <t>Jibin Jose</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3054,12 +3054,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>J jose</t>
+          <t>J Shields</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jibin Jose</t>
+          <t>Jonah Shields</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3076,12 +3076,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>J Shields</t>
+          <t>J varghese</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jonah Shields</t>
+          <t>Jeril Varghese</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3098,12 +3098,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>J varghese</t>
+          <t>Jack Alexander Smyth</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jeril Varghese</t>
+          <t>Jack Smyth</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3120,12 +3120,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jack Alexander Smyth</t>
+          <t>Jack Hutchinson</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jack Smyth</t>
+          <t>William Hutchinson</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3142,12 +3142,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jack Hutchinson</t>
+          <t>Jay Hunter</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>William Hutchinson</t>
+          <t>Jeffrey Hunter</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3164,12 +3164,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Jay Hunter</t>
+          <t>Jaydee Oliver</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jeffrey Hunter</t>
+          <t>Oliver Jaydee</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3186,12 +3186,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jaydee Oliver</t>
+          <t>Jayden K</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Oliver Jaydee</t>
+          <t>Daniel Kleynhans</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jayden K</t>
+          <t>Jayden Kleynhans</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3230,12 +3230,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jayden Kleynhans</t>
+          <t>Jeril Varghese</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Daniel Kleynhans</t>
+          <t>Jeril Puthenpurackal Varghese</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jeril Varghese</t>
+          <t>Jerin Alias</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jeril Puthenpurackal Varghese</t>
+          <t>Jerin Palakattu Alias</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3274,12 +3274,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jerin Alias</t>
+          <t>Jez Wilmshurst</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jerin Palakattu Alias</t>
+          <t>Jeremy Wilmshurst</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3296,12 +3296,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jez Wilmshurst</t>
+          <t>Jinso Devassykutty</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jeremy Wilmshurst</t>
+          <t>Jinso Pallicka Devassykutty</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3318,12 +3318,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jinso Devassykutty</t>
+          <t>Jinto Paul Kaliyadan</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jinso Pallicka Devassykutty</t>
+          <t>Jinto Kaliyadan</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3340,12 +3340,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Jinto Paul Kaliyadan</t>
+          <t>Joe Keith-Cotton</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jinto Kaliyadan</t>
+          <t>Joseph Keith-Cotton</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3362,12 +3362,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Joe Keith-Cotton</t>
+          <t>John Close</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Joseph Keith-Cotton</t>
+          <t>John T Close</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3384,12 +3384,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>John Close</t>
+          <t>John Walsh</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>John T Close</t>
+          <t>Jonathan Walsh</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>John Walsh</t>
+          <t>Jonathan Venus</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jonathan Walsh</t>
+          <t>Jay Venus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3428,12 +3428,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Jonathan Venus</t>
+          <t>Jonny Moore</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jay Venus</t>
+          <t>Jonathan Moore</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3450,12 +3450,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Jonny Moore</t>
+          <t>Josh Bates</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jonathan Moore</t>
+          <t>Joshua Bates</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3472,12 +3472,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Josh Bates</t>
+          <t>Josh Corbett</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Joshua Bates</t>
+          <t>Joshua Corbett</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3494,12 +3494,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Josh Corbett</t>
+          <t>Josh Froggatt</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Joshua Corbett</t>
+          <t>Joshua Froggatt</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3516,12 +3516,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Josh Froggatt</t>
+          <t>Josh Gordon</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Joshua Froggatt</t>
+          <t>Joshua GORDON</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3538,17 +3538,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Josh Gordon</t>
+          <t>Josh Walker</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Joshua GORDON</t>
+          <t>Joshua Walker</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3560,17 +3560,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Josh Walker</t>
+          <t>Josh Wilson</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Joshua Walker</t>
+          <t>Joshua Wilson</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Josh Wilson</t>
+          <t>Joshi John</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Joshua Wilson</t>
+          <t>Joshi Chavadivilla John</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3604,12 +3604,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Joshi John</t>
+          <t>Joshua Sloan</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Joshi Chavadivilla John</t>
+          <t>Joshua Adam Sloan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3626,12 +3626,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Joshua Sloan</t>
+          <t>Karl Gribben</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Joshua Adam Sloan</t>
+          <t>Karl Gribbin</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3648,12 +3648,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Karl Gribben</t>
+          <t>Karthik Jyothy</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Karl Gribbin</t>
+          <t>Karthik Jyothy Puthoor Jyothy</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3670,7 +3670,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Karthik Jyothy</t>
+          <t>Karthik Puthoor Jyothy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3692,12 +3692,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Karthik Puthoor Jyothy</t>
+          <t>Karthik Prasad</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Karthik Jyothy Puthoor Jyothy</t>
+          <t>Karthik Bangalore Rajendra Prasad</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Karthik Prasad</t>
+          <t>Kranthi Reddy</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Karthik Bangalore Rajendra Prasad</t>
+          <t>Kranthi Kumar Reddy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3736,12 +3736,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Kranthi Reddy</t>
+          <t>Kris McNeill</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Kranthi Kumar Reddy</t>
+          <t>Kristofer McNeill</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3758,17 +3758,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kris McNeill</t>
+          <t>Lachlan Aitken</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kristofer McNeill</t>
+          <t>Lachy Aitken</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3780,17 +3780,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Lachlan Aitken</t>
+          <t>Lewis Buchanan</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Lachy Aitken</t>
+          <t>Lewis David Buchanan</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3802,12 +3802,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Lewis Buchanan</t>
+          <t>Lijo Mathew Kocheriyil</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lewis David Buchanan</t>
+          <t>Lijo Mathew</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3824,12 +3824,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Lijo Mathew Kocheriyil</t>
+          <t>Maanvik Geddam</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lijo Mathew</t>
+          <t>Maanvik Vidhath Geddam</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3846,12 +3846,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Maanvik Geddam</t>
+          <t>Madhav Sarma</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Maanvik Vidhath Geddam</t>
+          <t>Madhav Sarma Varanakkottu Unnikrishnan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3868,12 +3868,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Madhav Sarma</t>
+          <t>Mahadeva Nidaghatta Shivakumar</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Madhav Sarma Varanakkottu Unnikrishnan</t>
+          <t>Mahadeva Prasad Nidaghatta Shivakumar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3890,12 +3890,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mahadeva Nidaghatta Shivakumar</t>
+          <t>Mahesh Nilewar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mahadeva Prasad Nidaghatta Shivakumar</t>
+          <t>Mahesh Dhanaji Nilewar</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3912,12 +3912,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Mahesh Nilewar</t>
+          <t>Mandar Hirve</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mahesh Dhanaji Nilewar</t>
+          <t>Mandar Parag Hirve</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3934,12 +3934,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Mandar Hirve</t>
+          <t>Maneesha Chathuranga</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Mandar Parag Hirve</t>
+          <t>Maneesha Chathuranga Hettige Don</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Maneesha Chathuranga</t>
+          <t>Manindar Singh</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Maneesha Chathuranga Hettige Don</t>
+          <t>Manindra Singh</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3978,12 +3978,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Manindar Singh</t>
+          <t>Manivannan Sivaganesh</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Manindra Singh</t>
+          <t>Sivaganesh Manivannan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4000,12 +4000,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Manivannan Sivaganesh</t>
+          <t>Manoj Kumar</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Sivaganesh Manivannan</t>
+          <t>Manoj Kumar Palaniswamy</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4022,100 +4022,100 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Manoj Kumar</t>
+          <t>Mark Best</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Manoj Kumar Palaniswamy</t>
+          <t>Mark Best</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Special rule / Pending Audit</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Transferred from CI to Bangor on 2nd June 2026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Mark Best</t>
+          <t>Matt Owen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Mark Best</t>
+          <t>matthew owen</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Special rule / Pending Audit</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Transferred from CI to Bangor on 2nd June 2026</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Matt Owen</t>
+          <t>Matthew Humphreys</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>matthew owen</t>
+          <t>Matthew Humphreys</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Special rule / Pending Audit</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Regarded as registered for Instonians for 2026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Matthew Humphreys</t>
+          <t>Max Willmott</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Matthew Humphreys</t>
+          <t>Maxwell Willmott</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Special rule / Pending Audit</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Regarded as registered for Instonians for 2026</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Max Willmott</t>
+          <t>Mayur Nanjundaswamy</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Maxwell Willmott</t>
+          <t>Mayur Kalkuni Nanjundaswamy</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4132,12 +4132,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mayur Nanjundaswamy</t>
+          <t>MN Payickattuvelil</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Mayur Kalkuni Nanjundaswamy</t>
+          <t>Moncy Ninan Payickattuvelil</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4154,17 +4154,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MN Payickattuvelil</t>
+          <t>Mo Aahil</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Moncy Ninan Payickattuvelil</t>
+          <t>Mohamed Aahil</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4176,17 +4176,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mo Aahil</t>
+          <t>Mohamed Ismail</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Mohamed Aahil</t>
+          <t>Ismail Mohamed</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4198,12 +4198,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mohamed Ismail</t>
+          <t>Mohammed Agadi</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ismail Mohamed</t>
+          <t>Mohammed Nayeem Agadi</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4220,12 +4220,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mohammed Agadi</t>
+          <t>Mohammed Rakeeb</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Mohammed Nayeem Agadi</t>
+          <t>Mohammed Faizan Rakeeb</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4242,17 +4242,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mohammed Rakeeb</t>
+          <t>Mohammed Sameer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mohammed Faizan Rakeeb</t>
+          <t>Sameer Mohd</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4264,17 +4264,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mohammed Sameer</t>
+          <t>Mohammed Sanobar</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sameer Mohd</t>
+          <t>Mohammed Sanobar Nedumpurakkal Sainudheen</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4286,12 +4286,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mohammed Sanobar</t>
+          <t>Mohan Raj</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mohammed Sanobar Nedumpurakkal Sainudheen</t>
+          <t>Mohan Raj Vijayakumar</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4308,7 +4308,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mohan Raj</t>
+          <t>Mohan Vijayakumar</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4330,12 +4330,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mohan Vijayakumar</t>
+          <t>Mohd Faizan</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Mohan Raj Vijayakumar</t>
+          <t>Muhammad Faizan</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4352,12 +4352,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Mohd Faizan</t>
+          <t>Muhamma Ajmal</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Muhammad Faizan</t>
+          <t>Muhammad Ajmal</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4374,17 +4374,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Muhamma Ajmal</t>
+          <t>Muhammad Shujee</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Muhammad Ajmal</t>
+          <t>Muhammad Shujee Ahmed</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4396,17 +4396,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Muhammad Shujee</t>
+          <t>Muhammed Hussain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Muhammad Shujee Ahmed</t>
+          <t>Muhammad Hussain</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4418,12 +4418,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Muhammed Hussain</t>
+          <t>Muhammed Nazar</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Muhammad Hussain</t>
+          <t>Muhammed Salman Nazar</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4440,12 +4440,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Muhammed Nazar</t>
+          <t>Muhammed Salman</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Muhammed Salman Nazar</t>
+          <t>Muhammed salman Nazar</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4462,12 +4462,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Muhammed Salman</t>
+          <t>Murali Devarapally</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Muhammed salman Nazar</t>
+          <t>Murali kumar Devarapally</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4484,12 +4484,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Murali Devarapally</t>
+          <t>Muthukaruppan Paganeri</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Murali kumar Devarapally</t>
+          <t>Muthukaruppan Subbiah Paganeri</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4506,12 +4506,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Muthukaruppan Paganeri</t>
+          <t>NagaSuprasanna Nagineni</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Muthukaruppan Subbiah Paganeri</t>
+          <t>Prasanna Nagineni</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4528,12 +4528,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NagaSuprasanna Nagineni</t>
+          <t>Nandeesh Nagaraju</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Prasanna Nagineni</t>
+          <t>Nandeesh Mathahalli Nagaraju</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4550,17 +4550,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nandeesh Nagaraju</t>
+          <t>Nikhil Nair</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Nandeesh Mathahalli Nagaraju</t>
+          <t>Nikhil Muraleedharan Nair</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4572,17 +4572,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Nikhil Nair</t>
+          <t>Nithin k Babu</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nikhil Muraleedharan Nair</t>
+          <t>Nithin Babu</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4594,17 +4594,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nithin k Babu</t>
+          <t>Olie Mann</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Nithin Babu</t>
+          <t>Oliver Mann</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4616,17 +4616,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Olie Mann</t>
+          <t>Oliver Gibson</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Oliver Mann</t>
+          <t>Oliver S Gibson</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4638,12 +4638,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Oliver Gibson</t>
+          <t>Ollie Hull</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Oliver S Gibson</t>
+          <t>Oliver Hull</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4660,12 +4660,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ollie Hull</t>
+          <t>Ollie Hume</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Oliver Hull</t>
+          <t>Oliver Hume</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4682,17 +4682,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ollie Hume</t>
+          <t>Omar Muhammad Bhandara</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Oliver Hume</t>
+          <t>Muhammad Bhandara</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4704,17 +4704,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Omar Muhammad Bhandara</t>
+          <t>P Spee</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Muhammad Bhandara</t>
+          <t>Penny Speer</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4726,12 +4726,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>P Spee</t>
+          <t>Paddy Beverland</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Penny Speer</t>
+          <t>Patrick Beverland</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4748,12 +4748,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Paddy Beverland</t>
+          <t>Paddy Carson</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Patrick Beverland</t>
+          <t>Patrick Carson</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4770,12 +4770,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Paddy Carson</t>
+          <t>Pallav Saran</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Patrick Carson</t>
+          <t>Pallav Saran</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4792,12 +4792,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Pallav Saran</t>
+          <t>Pankaj Pathak</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Pallav Saran</t>
+          <t>Pankaj Kumar Pathak</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4814,12 +4814,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Pankaj Pathak</t>
+          <t>Pat Lutton</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Pankaj Kumar Pathak</t>
+          <t>Patrick Lutton</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4836,12 +4836,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Pat Lutton</t>
+          <t>Patrick Heron</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Patrick Lutton</t>
+          <t>P Heron</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4858,12 +4858,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Patrick Heron</t>
+          <t>Pavan Karthik</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>P Heron</t>
+          <t>Pavan Karthik Bade</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4880,12 +4880,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Pavan Karthik</t>
+          <t>Peter Ward</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Pavan Karthik Bade</t>
+          <t>Pete Ward</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4902,17 +4902,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Peter Ward</t>
+          <t>Phil Skillen</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pete Ward</t>
+          <t>Philip Skillen</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4924,12 +4924,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Phil Skillen</t>
+          <t>Phil Stewart</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Philip Skillen</t>
+          <t>Philip Stewart</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4946,12 +4946,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Phil Stewart</t>
+          <t>Philip Rodgers</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Philip Stewart</t>
+          <t>Phil Rodgers</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4968,17 +4968,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Philip Rodgers</t>
+          <t>Piyush Yalamanchili</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Phil Rodgers</t>
+          <t>Piyush Sri Siddhi Yalamanchili</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4990,12 +4990,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Piyush Yalamanchili</t>
+          <t>Poorna Shanmugam</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Piyush Sri Siddhi Yalamanchili</t>
+          <t>Poorna Kumar Shanmugam</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Poorna Shanmugam</t>
+          <t>Prajin Chemmayath Gopi</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Poorna Kumar Shanmugam</t>
+          <t>Prajin Gopi</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5034,12 +5034,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Prajin Chemmayath Gopi</t>
+          <t>Praveen A Punithan</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Prajin Gopi</t>
+          <t>Praveen Angalaparameswari Punithan</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5056,12 +5056,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Praveen A Punithan</t>
+          <t>Praveen Shashidara</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Praveen Angalaparameswari Punithan</t>
+          <t>Praveen Bangalore Shashidara</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5078,12 +5078,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Praveen Shashidara</t>
+          <t>Prithiv Raaj</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Praveen Bangalore Shashidara</t>
+          <t>Prithiv Raaj V S</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5100,12 +5100,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Prithiv Raaj</t>
+          <t>Priyank Lakhani</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Prithiv Raaj V S</t>
+          <t>Priyankbhai Lakhani</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5122,12 +5122,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Priyank Lakhani</t>
+          <t>PT Aston</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Priyankbhai Lakhani</t>
+          <t>Paul Aston</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5144,17 +5144,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PT Aston</t>
+          <t>Raghu Sathya</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Paul Aston</t>
+          <t>Raghuram Sathyanarayana</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5166,17 +5166,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Raghu Sathya</t>
+          <t>Rahul Baghel</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Raghuram Sathyanarayana</t>
+          <t>Rahul Singh Baghel</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5188,12 +5188,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Rahul Baghel</t>
+          <t>Rajesh Thuraiyur Moorthy</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Rahul Singh Baghel</t>
+          <t>Rajesh Thuraiyur</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5210,12 +5210,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Rajesh Thuraiyur Moorthy</t>
+          <t>Rakeeb Raheman</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Rajesh Thuraiyur</t>
+          <t>Rakeeb Ahmed Tirupattur Raheman</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5232,12 +5232,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Rakeeb Raheman</t>
+          <t>Rakesh Singh</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Rakeeb Ahmed Tirupattur Raheman</t>
+          <t>Rakesh Kumar Singh</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5254,12 +5254,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Rakesh Singh</t>
+          <t>Rameez Hashmi</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Rakesh Kumar Singh</t>
+          <t>Syed Rameez Ali Hashmi</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5276,12 +5276,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Rameez Hashmi</t>
+          <t>Randeep Singh</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Syed Rameez Ali Hashmi</t>
+          <t>RANDEEP Singh Duggal</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5298,12 +5298,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Randeep Singh</t>
+          <t>Ranju Kizhakkekutt</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RANDEEP Singh Duggal</t>
+          <t>Ranju Kizhakkekutt Mathew</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5320,12 +5320,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ranju Kizhakkekutt</t>
+          <t>Renju John</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ranju Kizhakkekutt Mathew</t>
+          <t>Renju Vadakkeparampil John</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5342,12 +5342,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Renju John</t>
+          <t>Reuben Edmondson</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Renju Vadakkeparampil John</t>
+          <t>Richard Reuben Edmondson</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5364,12 +5364,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Reuben Edmondson</t>
+          <t>Reuben Wilson</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Richard Reuben Edmondson</t>
+          <t>Reuben Logan-Wilson</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5386,12 +5386,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Reuben Wilson</t>
+          <t>Richard Gould Hocking</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Reuben Logan-Wilson</t>
+          <t>Richard Harry Gould Hocking</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5408,17 +5408,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Richard Gould Hocking</t>
+          <t>Rick McKibbin</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Richard Harry Gould Hocking</t>
+          <t>Richard Mckibbin</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5430,17 +5430,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Rick McKibbin</t>
+          <t>Ricky Lavakumar</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Richard Mckibbin</t>
+          <t>Ricky Bopanna Kanathanda Lavakumar</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5452,12 +5452,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Ricky Lavakumar</t>
+          <t>Rijo George</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ricky Bopanna Kanathanda Lavakumar</t>
+          <t>Rijo George Porathoor</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5474,12 +5474,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Rijo George</t>
+          <t>Rishik Yalamanchili</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Rijo George Porathoor</t>
+          <t>Rishik Sri Sai Yalamanchili</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5496,12 +5496,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Rishik Yalamanchili</t>
+          <t>Robert Dougan</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Rishik Sri Sai Yalamanchili</t>
+          <t>Robert Wilfred Dougan</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5518,12 +5518,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Robert Dougan</t>
+          <t>Roney Mathew</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Robert Wilfred Dougan</t>
+          <t>Joseph Mathew</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5540,12 +5540,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Roney Mathew</t>
+          <t xml:space="preserve">Ronnie Bell </t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Joseph Mathew</t>
+          <t xml:space="preserve">Ron Bell </t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5562,12 +5562,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ronnie Bell </t>
+          <t>Ross Adair</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ron Bell </t>
+          <t>George Adair</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5584,17 +5584,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ross Adair</t>
+          <t>Rufi Shaikh</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>George Adair</t>
+          <t>Rufi Raheel Shaikh</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5606,17 +5606,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Rufi Shaikh</t>
+          <t>RV John</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Rufi Raheel Shaikh</t>
+          <t>Renju Vadakkeparampil john</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5628,12 +5628,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RV John</t>
+          <t>S Kashikar</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Renju Vadakkeparampil john</t>
+          <t>Suprit Kashikar</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5650,12 +5650,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S Kashikar</t>
+          <t>S Malik</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Suprit Kashikar</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5672,12 +5672,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S Malik</t>
+          <t>S Sunil kumar</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Sidharth Sunil Kumar Swayam Prabha</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5694,12 +5694,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S Sunil kumar</t>
+          <t>Sai Darshan</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Sidharth Sunil Kumar Swayam Prabha</t>
+          <t>Sai Kruthik Darshan</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5716,12 +5716,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Sai Darshan</t>
+          <t>Sairam Kondapally</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Sai Kruthik Darshan</t>
+          <t>Sai Ram Kondapally</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5738,12 +5738,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Sairam Kondapally</t>
+          <t>Sam Gilliland</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Sai Ram Kondapally</t>
+          <t>Samuel Gilliland</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5760,17 +5760,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Sam Gilliland</t>
+          <t>Sameer Mohammad</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Samuel Gilliland</t>
+          <t>Sameer Mohd</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5782,17 +5782,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Sameer Mohammad</t>
+          <t>Samuel McMillan</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Sameer Mohd</t>
+          <t>Sam Mcmillan</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5804,12 +5804,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Samuel McMillan</t>
+          <t>Sanjeev Menon</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Sam Mcmillan</t>
+          <t>Sanjeev Sukumaran Menon</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5826,12 +5826,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Sanjeev Menon</t>
+          <t>Sarath Sasi</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Sanjeev Sukumaran Menon</t>
+          <t>Sharath Sadanandan</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5848,12 +5848,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Sarath Sasi</t>
+          <t>Sarav Palaniappan</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Sharath Sadanandan</t>
+          <t>Saravanan Palaniappan</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5870,12 +5870,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Sarav Palaniappan</t>
+          <t>Saravana Chandrasekaran</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Saravanan Palaniappan</t>
+          <t>Saravana Maadavan Chandrasekaran</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5892,12 +5892,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Saravana Chandrasekaran</t>
+          <t>Sasha Sinclair</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Saravana Maadavan Chandrasekaran</t>
+          <t>Aleksander StClair</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5914,12 +5914,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Sasha Sinclair</t>
+          <t>Sasha StClair</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Aleksander StClair</t>
+          <t>Aleksander Stclair</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5936,12 +5936,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Sasha StClair</t>
+          <t>Sathish Manohar</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Aleksander Stclair</t>
+          <t>Sathish Kumar Manohar</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5958,12 +5958,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sathish Manohar</t>
+          <t>Satya Edubilli</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Sathish Kumar Manohar</t>
+          <t>Satyannarayana Edubilli</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5980,12 +5980,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Satya Edubilli</t>
+          <t>Scott McClelland</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Satyannarayana Edubilli</t>
+          <t>Thomas McClelland</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6002,12 +6002,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Scott McClelland</t>
+          <t>Sebastian Yeates</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Thomas McClelland</t>
+          <t>Seb Yeates</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6024,12 +6024,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sebastian Yeates</t>
+          <t>Seby Best</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Seb Yeates</t>
+          <t>Seb Best</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6046,17 +6046,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Seby Best</t>
+          <t>Selvaraj Muthusivan</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Seb Best</t>
+          <t>Muthusivan Selvaraj</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6068,17 +6068,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Selvaraj Muthusivan</t>
+          <t>Senthilkumar Ponnuchamy</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Muthusivan Selvaraj</t>
+          <t>Selvakumar Ponnuchamy Senthil Kumar</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6090,12 +6090,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Senthilkumar Ponnuchamy</t>
+          <t>Senthilkumar Santhanakrishnan</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Selvakumar Ponnuchamy Senthil Kumar</t>
+          <t>Senthil Kumar Santhana Krishnan</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6112,12 +6112,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Senthilkumar Santhanakrishnan</t>
+          <t>Shah Ata</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Senthil Kumar Santhana Krishnan</t>
+          <t>Shah Muhammad Ata</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6134,12 +6134,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Shah Ata</t>
+          <t>Shahid Malik</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Shah Muhammad Ata</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6156,12 +6156,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Shahid Malik</t>
+          <t>Shahmeer Khan</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Shahmir Khan</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6178,12 +6178,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Shahmeer Khan</t>
+          <t>Shakeel ahmed SHAIKH</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Shahmir Khan</t>
+          <t>Shakeel Shaikh</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Shakeel ahmed SHAIKH</t>
+          <t>Shami Hasan</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Shakeel Shaikh</t>
+          <t>Shamim Hasan Sami</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6222,12 +6222,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Shami Hasan</t>
+          <t>Shankar Uthayashankar</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Shamim Hasan Sami</t>
+          <t>Uthayashankar Selvaratnam</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6244,12 +6244,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Shankar Uthayashankar</t>
+          <t>Shay Malik</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Uthayashankar Selvaratnam</t>
+          <t>Shahid Nadeem</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6266,12 +6266,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Shay Malik</t>
+          <t>Sheree McAleenan</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Shahid Nadeem</t>
+          <t>Sheree Marie McAleenan</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6288,12 +6288,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Sheree McAleenan</t>
+          <t>Sidharth Sunil</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Sheree Marie McAleenan</t>
+          <t>Sidharth Sunil Kumar Swayam Prabha</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6310,7 +6310,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Sidharth Sunil</t>
+          <t>Sidharth Sunil kumar</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6332,12 +6332,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Sidharth Sunil kumar</t>
+          <t>Sidharth Suresh Kumar</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Sidharth Sunil Kumar Swayam Prabha</t>
+          <t>Sidharth Kumar</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6354,12 +6354,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Sidharth Suresh Kumar</t>
+          <t>Simon-Peter Maxwell</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Sidharth Kumar</t>
+          <t>Simon Peter Maxwell</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6376,12 +6376,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Simon-Peter Maxwell</t>
+          <t>SM Mitchell</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Simon Peter Maxwell</t>
+          <t>Scott Mitchell</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6398,12 +6398,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SM Mitchell</t>
+          <t>Sohail Khan</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Scott Mitchell</t>
+          <t>Sohailkhan Markhail</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6420,12 +6420,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Sohail Khan</t>
+          <t>Soma Raman</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Sohailkhan Markhail</t>
+          <t>Aaditya Raman Soma Sundaram</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6442,12 +6442,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Soma Raman</t>
+          <t>Sreejesh Nair</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Aaditya Raman Soma Sundaram</t>
+          <t>Sreejesh Krishnan Nair</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6464,12 +6464,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Sreejesh Nair</t>
+          <t>Sri Tummala</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Sreejesh Krishnan Nair</t>
+          <t>Tummala Srivinayteja</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6486,12 +6486,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Sri Tummala</t>
+          <t>Srinuvasarao Nadakuditi</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Tummala Srivinayteja</t>
+          <t>Srinuvasarao N</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6508,12 +6508,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Srinuvasarao Nadakuditi</t>
+          <t>Stanley John</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Srinuvasarao N</t>
+          <t>Stanley Mathew John</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6530,12 +6530,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Stanley John</t>
+          <t>Steph Butler</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Stanley Mathew John</t>
+          <t>Stephanie Butler</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6552,17 +6552,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Steph Butler</t>
+          <t>Stevie Saul</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Stephanie Butler</t>
+          <t>Steven Saul</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6574,17 +6574,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Stevie Saul</t>
+          <t>Stuart Johnstone</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Steven Saul</t>
+          <t>Stewart Johnston</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6596,17 +6596,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Stuart Johnstone</t>
+          <t>Subhilesh P S</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Stewart Johnston</t>
+          <t>Subhilesh Ps</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6618,17 +6618,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Subhilesh P S</t>
+          <t>Sufyan Muhammad</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Subhilesh Ps</t>
+          <t>Muhammad Sufyan</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6640,12 +6640,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Sufyan Muhammad</t>
+          <t>Sumesh Mohanan</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Muhammad Sufyan</t>
+          <t>Sumesh Kumar Mohanan</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6662,12 +6662,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Sumesh Mohanan</t>
+          <t>Sunson Stephenson</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sumesh Kumar Mohanan</t>
+          <t>Sunson Stephen</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6684,12 +6684,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Sunson Stephenson</t>
+          <t>Suresh Gopidi</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Sunson Stephen</t>
+          <t>Suresh Reddy Gopidi</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6706,12 +6706,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Suresh Gopidi</t>
+          <t>Surya Saneesh</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Suresh Reddy Gopidi</t>
+          <t>Suryakrishna Saneesh</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6728,12 +6728,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Surya Saneesh</t>
+          <t>Surya Tummala</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Suryakrishna Saneesh</t>
+          <t>Surya Pavan Teja Tummala</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6750,12 +6750,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Surya Tummala</t>
+          <t>Syam Rajmohan</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Surya Pavan Teja Tummala</t>
+          <t>Syam Raj</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Syam Rajmohan</t>
+          <t>Talha Shah</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Syam Raj</t>
+          <t>Syed Talha Ahmed Shah</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6794,12 +6794,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Talha Shah</t>
+          <t>Teddy McIlwaine</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Syed Talha Ahmed Shah</t>
+          <t>Teddy McIlwaine</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6816,17 +6816,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Teddy McIlwaine</t>
+          <t>Thamil Maran</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Teddy McIlwaine</t>
+          <t>Thamilmaran Raju</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6838,17 +6838,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Thamil Maran</t>
+          <t>Thomas Copeland</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Thamilmaran Raju</t>
+          <t>Thomas Graeme Copeland</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6860,12 +6860,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Thomas Copeland</t>
+          <t>Thomas ET</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Thomas Graeme Copeland</t>
+          <t>Thomas Eapen tharkolil</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6882,12 +6882,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Thomas ET</t>
+          <t>Tim Browne</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Thomas Eapen tharkolil</t>
+          <t>Timothy Browne</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6904,12 +6904,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Tim Browne</t>
+          <t>Tim Scott</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Timothy Browne</t>
+          <t>Timothy Scott</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6926,12 +6926,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Tim Scott</t>
+          <t>Timmy Evans</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Timothy Scott</t>
+          <t>Timothy Evans</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6948,12 +6948,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Timmy Evans</t>
+          <t>TJ McCavera</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Timothy Evans</t>
+          <t>Thomas Mccavera</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6970,12 +6970,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TJ McCavera</t>
+          <t>Tom Jefferson</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Thomas Mccavera</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6992,12 +6992,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Tom Jefferson</t>
+          <t>Tom Macauley</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Thomas Macauley</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7014,12 +7014,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Tom Macauley</t>
+          <t>Tom Mayes</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Thomas Macauley</t>
+          <t>Thomas Mayes</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7036,12 +7036,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Tom Mayes</t>
+          <t>Tom Nicholson</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Thomas Mayes</t>
+          <t>Thomas Nicholson</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7058,12 +7058,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Tom Nicholson</t>
+          <t>Tom Shearer</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Thomas Nicholson</t>
+          <t>Thomas Shearer</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7080,12 +7080,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Tom Shearer</t>
+          <t>Tom Stevenson</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Thomas Shearer</t>
+          <t>Thomas Stevenson</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7102,12 +7102,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Tom Stevenson</t>
+          <t>Tony Adams</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Thomas Stevenson</t>
+          <t>Anthony Adams</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7124,12 +7124,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Tony Adams</t>
+          <t>Tony Louis</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Anthony Adams</t>
+          <t>Tony Louis Pathippilly</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7146,12 +7146,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Tony Louis</t>
+          <t>Tulasi Thatavarthi</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Tony Louis Pathippilly</t>
+          <t>Tulasi Gangadhar Thatavarthi</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7168,12 +7168,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Tulasi Thatavarthi</t>
+          <t>Veerendra Nagari</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Tulasi Gangadhar Thatavarthi</t>
+          <t>Veerendra Babu Nagari</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7190,12 +7190,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Veerendra Nagari</t>
+          <t>Veideek Agarwal</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Veerendra Babu Nagari</t>
+          <t>Veideek Krishna Agarwal</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7212,17 +7212,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Veideek Agarwal</t>
+          <t>Venkateswararao Jyothi</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Veideek Krishna Agarwal</t>
+          <t>Venkat Jyothi</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7234,17 +7234,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Venkateswararao Jyothi</t>
+          <t>Venky Valleri</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Venkat Jyothi</t>
+          <t>Venkatesh Valleri</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7256,12 +7256,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Venky Valleri</t>
+          <t>Vichu Cassi</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Venkatesh Valleri</t>
+          <t>Vishnu Chirayil Manoj</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7278,12 +7278,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Vichu Cassi</t>
+          <t>Vidhath Geddam</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Vishnu Chirayil Manoj</t>
+          <t>Maanvik Vidhath Geddam</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7300,12 +7300,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Vidhath Geddam</t>
+          <t>Vineesh Peter</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Maanvik Vidhath Geddam</t>
+          <t>Vineesh Peter Tx</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7322,12 +7322,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Vineesh Peter</t>
+          <t>Vinesh Pathiyil Varghese</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Vineesh Peter Tx</t>
+          <t>Vinesh Varghese</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7344,17 +7344,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Vinesh Pathiyil Varghese</t>
+          <t>Vinosh Mohandas</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Vinesh Varghese</t>
+          <t>Vinosh Mohanadas</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7366,17 +7366,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Vinosh Mohandas</t>
+          <t>Vinoth Srinivasan</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Vinosh Mohanadas</t>
+          <t>Vinoth Kumar Srinivasan</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7388,12 +7388,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Vinoth Srinivasan</t>
+          <t>Vipin Kumar</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Vinoth Kumar Srinivasan</t>
+          <t>Vipin kumar Vadakkechirayil vijayan</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7410,12 +7410,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Vipin Kumar</t>
+          <t>Visakh Joseph</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Vipin kumar Vadakkechirayil vijayan</t>
+          <t>Visakh peter Joseph</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7432,12 +7432,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Visakh Joseph</t>
+          <t>Vishnu Korath</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Visakh peter Joseph</t>
+          <t>Vishnu Viswanadh Korath</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7454,12 +7454,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Vishnu Korath</t>
+          <t>Vishnu Prasad</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Vishnu Viswanadh Korath</t>
+          <t>Vishnu Prasad Naduviledathu Janardhanan</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7476,12 +7476,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vishnu Prasad</t>
+          <t>Vishwanatha Urs</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Vishnu Prasad Naduviledathu Janardhanan</t>
+          <t>Vishwanatha Kemparaje Urs</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7498,12 +7498,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Vishwanatha Urs</t>
+          <t>Viswath Balaguru</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Vishwanatha Kemparaje Urs</t>
+          <t>Viswath Ramanujam Balaguru</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7520,17 +7520,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Viswath Balaguru</t>
+          <t>Will Koorts</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Viswath Ramanujam Balaguru</t>
+          <t>Willem Koorts</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Verified (Flipped Mapping)</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7542,12 +7542,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Will Koorts</t>
+          <t>Will Simpson</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Willem Koorts</t>
+          <t>William Simpson</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7564,17 +7564,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Will Simpson</t>
+          <t>William Park</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>William Simpson</t>
+          <t>Will Park</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Verified (Flipped Mapping)</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7586,12 +7586,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>William Park</t>
+          <t>Willy Graham</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Will Park</t>
+          <t>William Graham</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7608,12 +7608,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Willy Graham</t>
+          <t>Yashwanth Moluguri</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>William Graham</t>
+          <t>Yashwanth Kumar Moluguri</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7630,12 +7630,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Yashwanth Moluguri</t>
+          <t>Zac Solomon</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Yashwanth Kumar Moluguri</t>
+          <t>Isaac Solomon</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7652,12 +7652,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Zac Solomon</t>
+          <t>Zach Robinson</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Isaac Solomon</t>
+          <t>Zachary Robinson</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7674,12 +7674,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Zach Robinson</t>
+          <t>Zach Watson</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Zachary Robinson</t>
+          <t>William zach Watson</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7696,12 +7696,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Zach Watson</t>
+          <t>Zafar Ali</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>William zach Watson</t>
+          <t>Zafar ali Zafar ali</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7718,12 +7718,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Zafar Ali</t>
+          <t>Zaheer Gondal</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Zafar ali Zafar ali</t>
+          <t>Zaheer Ahmad Gondal</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7740,12 +7740,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Zaheer Gondal</t>
+          <t>Praveen Kapala</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Zaheer Ahmad Gondal</t>
+          <t>Praveen kumar Kapala</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7762,12 +7762,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Praveen Kapala</t>
+          <t>Gokula Gopala Krishnan</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Praveen kumar Kapala</t>
+          <t>Gokula Kannan Gopala Krishnan</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7784,12 +7784,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Gokula Gopala Krishnan</t>
+          <t>Tom Buchanan</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Gokula Kannan Gopala Krishnan</t>
+          <t>Tom Daniel Buchanan</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7806,12 +7806,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Tom Buchanan</t>
+          <t>Thomas Varghese</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Tom Daniel Buchanan</t>
+          <t>Thomas Cheethaparambill varghese</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7828,12 +7828,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Thomas Varghese</t>
+          <t>Sam Cave</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Thomas Cheethaparambill varghese</t>
+          <t>Samuel Cave</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7850,12 +7850,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Sam Cave</t>
+          <t>Syam Kumar</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Samuel Cave</t>
+          <t>Syam Kumar Sasidharan Nair</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7872,34 +7872,34 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Syam Kumar</t>
+          <t>Francis Collins</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Syam Kumar Sasidharan Nair</t>
+          <t>Francis GJ Collins</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added for transfers</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Francis Collins</t>
+          <t>Amal Matthew Muttathupadam</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Francis GJ Collins</t>
+          <t>Amal Mathew Muttathupadam</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7916,12 +7916,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Amal Matthew Muttathupadam</t>
+          <t>Tim Evans</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Amal Mathew Muttathupadam</t>
+          <t>Timothy Evans</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7938,12 +7938,12 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Tim Evans</t>
+          <t>Harry Zimmerman</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Timothy Evans</t>
+          <t>Harry Zimmermann</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7960,12 +7960,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Harry Zimmerman</t>
+          <t>Darshan Kumar</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Harry Zimmermann</t>
+          <t>Darshan Hanumanth kumar</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7982,34 +7982,34 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Darshan Kumar</t>
+          <t xml:space="preserve">Shahbaz Bhandara </t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Darshan Hanumanth kumar</t>
+          <t>Shahbaz Umar Jalal Bhandara</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Added for transfers</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shahbaz Bhandara </t>
+          <t>Jaya Sukhavasi</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Shahbaz Umar Jalal Bhandara</t>
+          <t>Jaya Surya Sukhavasi</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -8026,12 +8026,12 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Jaya Sukhavasi</t>
+          <t>Venkataharish Rayi</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Jaya Surya Sukhavasi</t>
+          <t>Harish Rayi</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8048,12 +8048,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Venkataharish Rayi</t>
+          <t>Kavyadeep Singh</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Harish Rayi</t>
+          <t>Kavyadeep Bhamra</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8070,12 +8070,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Kavyadeep Singh</t>
+          <t>Josh McClune</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Kavyadeep Bhamra</t>
+          <t>Joshua McClune</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8092,12 +8092,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Josh McClune</t>
+          <t>Fergus Emmett</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Joshua McClune</t>
+          <t>Frgus Emmett</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8114,12 +8114,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Fergus Emmett</t>
+          <t>Izzy Jones</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Frgus Emmett</t>
+          <t>Isabelle Jones</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8136,12 +8136,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Izzy Jones</t>
+          <t>Susie McCollum</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Isabelle Jones</t>
+          <t>Susanna McCollum</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8158,12 +8158,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Susie McCollum</t>
+          <t>Abbie Gunning</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Susanna McCollum</t>
+          <t>Abigail Gunning</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8180,12 +8180,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Abbie Gunning</t>
+          <t>Aimee Logan</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Abigail Gunning</t>
+          <t>Aimeee Logan</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8202,12 +8202,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Aimee Logan</t>
+          <t>Alex Atkinson</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Aimeee Logan</t>
+          <t>Alexandra Atkinson</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8224,12 +8224,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Alex Atkinson</t>
+          <t>Ellie Murray</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Alexandra Atkinson</t>
+          <t>Ellen Murray</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8246,12 +8246,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ellie Murray</t>
+          <t>Vismithaa Pandiaraj</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Ellen Murray</t>
+          <t>Vismithaa Sai Pandiaraj</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8268,12 +8268,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Vismithaa Pandiaraj</t>
+          <t>Johnny Shannon</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Vismithaa Sai Pandiaraj</t>
+          <t>Jonny Shannon</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8290,12 +8290,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Johnny Shannon</t>
+          <t>Nathan McCurry</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Jonny Shannon</t>
+          <t>Nathan McCurry</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8305,19 +8305,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Added as per Wylie request (Sport80 typo fix)</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nathan McCurry</t>
+          <t>Stephen Entwhistle</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Nathan McCurry</t>
+          <t>Stephen Entwistle</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8334,12 +8334,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Will Noffkee</t>
+          <t>Thomas Vidamour</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Will Noffke</t>
+          <t>Vhomas Tidamour</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8356,12 +8356,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Stephen Entwhistle</t>
+          <t>Tony Louis Pathipally</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Stephen Entwistle</t>
+          <t>Tony Louis Pathippilly</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Added as per Wylie request (Transliteration fix)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Thomas Vidamour</t>
+          <t>Henry O'Neill</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Vhomas Tidamour</t>
+          <t>Henry O’Neill</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8393,19 +8393,19 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Sport80 typo fix)</t>
+          <t>Added as per Wylie request (Apostrophe character fix)</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Tony Louis Pathipally</t>
+          <t>stuart COP</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Tony Louis Pathippilly</t>
+          <t>Stuart Copeland</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8415,19 +8415,19 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Transliteration fix)</t>
+          <t>Sport80 payment typo (truncated surname)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Henry O'Neill</t>
+          <t>Akaah Vega</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Henry O’Neill</t>
+          <t>Akash Vega</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8437,19 +8437,19 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Added as per Wylie request (Apostrophe character fix)</t>
+          <t>Sport80 payment typo (k/h keyboard slip)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>stuart COP</t>
+          <t>Sandeep Srinivasan</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Stuart Copeland</t>
+          <t>Sandeep Ganesh Srinivasan</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8459,19 +8459,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Sport80 payment typo (truncated surname)</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Akaah Vega</t>
+          <t>James Magee</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Akash Vega</t>
+          <t>James Magee Snr</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8481,19 +8481,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Sport80 payment typo (k/h keyboard slip)</t>
+          <t>Standard baseline mapping rule</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Sandeep Srinivasan</t>
+          <t>Jack Kirkpatrick jnr</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Sandeep Ganesh Srinivasan</t>
+          <t>Jack Kirkpatrick Jnr</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8503,19 +8503,19 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Case normalization for Jnr suffix</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>James Magee</t>
+          <t>Jack Kirkpatrick snr</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>James Magee Snr</t>
+          <t>Jack Kirkpatrick Snr</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8525,19 +8525,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Standard baseline mapping rule</t>
+          <t>Case normalization for Snr suffix</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick jnr</t>
+          <t>Nicholas Bennett</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick Jnr</t>
+          <t>Nick Bennett</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8547,19 +8547,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Case normalization for Jnr suffix</t>
+          <t>Ards &amp; Donaghadee Cricket Club (2021113018)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick snr</t>
+          <t>Muhammad Asif</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Jack Kirkpatrick Snr</t>
+          <t>Mohammad Asif</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8569,19 +8569,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Case normalization for Snr suffix</t>
+          <t>Added for Belfast CC matching</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Nicholas Bennett</t>
+          <t>Nidheesh Thankachan</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Nick Bennett</t>
+          <t>Nidheesh Vakkayil Thankachan</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8591,19 +8591,19 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Ards &amp; Donaghadee Cricket Club (2021113018)</t>
+          <t>Added for Ardent Blues CC matching</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Muhammad Asif</t>
+          <t>Sam McConnell</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Mohammad Asif</t>
+          <t>Samuel McConnell</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8613,63 +8613,93 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Added for Belfast CC matching</t>
+          <t>Added for Templepatrick CC matching</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Nidheesh Thankachan</t>
+          <t>Aidan O'Gormon</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Nidheesh Vakkayil Thankachan</t>
+          <t>Aidan O'Gorman</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Manual Map</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Added for Ardent Blues CC matching</t>
+          <t>NV Play scorecard spelling variant</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Aidan O'Gorman</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Aidan O'Gormon</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Men's</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Sam McConnell</t>
+          <t>Aidan OGormon</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Samuel McConnell</t>
+          <t>Aidan O'Gorman</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Verified in Database</t>
+          <t>Manual Map</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Added for Templepatrick CC matching</t>
+          <t>NV Play scorecard spelling variant without apostrophe</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Aidan O'Gorman</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Aidan OGormon</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Men's</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Aidan O'Gormon</t>
+          <t>Zach Cameron</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Aidan O'Gorman</t>
+          <t>Zachary Cameron</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8679,17 +8709,17 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>NV Play scorecard spelling variant</t>
+          <t>NV Play scorecard name for Zachary Cameron (CI)</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aidan O'Gorman</t>
+          <t>Zachary Cameron</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Aidan O'Gormon</t>
+          <t>Zach Cameron</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -8701,12 +8731,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Aidan OGormon</t>
+          <t>Zachery Cameron</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Aidan O'Gorman</t>
+          <t>Zachary Cameron</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8716,17 +8746,17 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>NV Play scorecard spelling variant without apostrophe</t>
+          <t>Spelling variant for Zachary Cameron (CI)</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aidan O'Gorman</t>
+          <t>Zachary Cameron</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Aidan OGormon</t>
+          <t>Zach Cameron</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -8738,12 +8768,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Zach Cameron</t>
+          <t>Cameron  Kane</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Zachary Cameron</t>
+          <t>Cameron Kane</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8753,17 +8783,17 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>NV Play scorecard name for Zachary Cameron (CI)</t>
+          <t>NV Play scorecard double-space variant</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Zachary Cameron</t>
+          <t>Cameron Kane</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Zach Cameron</t>
+          <t>Cameron  Kane</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -8775,116 +8805,42 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Zachery Cameron</t>
+          <t>Alec Stuart</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Zachary Cameron</t>
+          <t>Alex Stuart</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Manual Map</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Spelling variant for Zachary Cameron (CI)</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>Zachary Cameron</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Zach Cameron</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>Men's</t>
+          <t>Holywood 1881 Cricket Club (2021114359)</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Cameron  Kane</t>
+          <t>Sameer Mohammed</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Cameron Kane</t>
+          <t>Sameer Mohd</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Manual Map</t>
+          <t>Verified in Database</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
-        <is>
-          <t>NV Play scorecard double-space variant</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Cameron Kane</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Cameron  Kane</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>Men's</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Alec Stuart</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Alex Stuart</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Verified in Database</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>Holywood 1881 Cricket Club (2021114359)</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Sameer Mohammed</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Sameer Mohd</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Verified in Database</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
         <is>
           <t>Belfast Cricket Club (2021113239)</t>
         </is>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -59,10 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,50 +435,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Input Name (Scorecard/Stats)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Official Registered Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Ledger Status Verification</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Registered Name</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>NV Play Name</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
@@ -8843,6 +8850,228 @@
       <c r="D378" t="inlineStr">
         <is>
           <t>Belfast Cricket Club (2021113239)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Frazer Mitchell</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Fraser Mitchell</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Sport80 name spelt Fraser Mitchell</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Fraser Mitchell</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Frazer Mitchell</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Issac Wilkinson</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Isaac Wilkinson</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NV Play scorecard spelling error (Issac -&gt; Isaac)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Isaac Wilkinson</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Issac Wilkinson</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Kurian Saji</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Kurian Saji Thoonkuzhy</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Sport80 ID 3000003357 - Full registered name is Kurian Saji Thoonkuzhy</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Kurian Saji Thoonkuzhy</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Kurian Saji</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Manjush Cherian</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Manjush George Cherian</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Sport80 ID 2021118070 - Full registered name Manjush George Cherian</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Manjush George Cherian</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Manjush Cherian</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Mohammed Asif</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Mohammad Asif</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Sport80 ID 2021113652 - Registered name Mohammad Asif</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Mohammad Asif</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Mohammed Asif</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Philip Vidamour</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Phil Vidamour</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Sport80 ID 3000003260 - Registered name is Phil Vidamour</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Phil Vidamour</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Philip Vidamour</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Men's</t>
         </is>
       </c>
     </row>

--- a/2. NCU_Validated_Aliases_Master.xlsx
+++ b/2. NCU_Validated_Aliases_Master.xlsx
@@ -435,13 +435,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G384"/>
+  <dimension ref="A1:G388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="107" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -9075,6 +9075,154 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Ali Quadri</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Mubashir Ali</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Sport80 ID 2021113650 - Payer contact is MR M M A QUADRI (Cooke Collegians CC)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Mubashir Ali</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Ali Quadri</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Josh Hall</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Joshua Hall</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Sport80 ID 2021123550 / 534 - Donacloney Mill CC</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Joshua Hall</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Josh Hall</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Ashley Murray</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>William Murray</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Parent Ashley Murray paid £5 youth fee for William Murray (Carrickfergus CC)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>William Murray</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Ashley Murray</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Nathan Samuel</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Nathan Knox</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Sport80 revenue export used First + Middle name Nathan Samuel for Nathan Samuel Knox (Donacloney Mill CC)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Nathan Knox</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Nathan Samuel</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Men's</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
